--- a/Quality.xlsx
+++ b/Quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ppgclindia-my.sharepoint.com/personal/bikram_mohapatra_ppgcl_co_in/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rake Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{830ED6A4-BAD4-467E-8E50-6E0FA33BBE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23FBAB3-3095-40F0-8F5E-24714C004086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY-26" sheetId="11" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -251,7 +249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]dd\-mm\-yyyy;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -958,45 +956,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95EA2AF0-D9E1-4EEF-BD8A-1442FA3E80E4}">
   <dimension ref="A1:AJ122"/>
-  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="6.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="1.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="10.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="10.7109375" style="1"/>
+    <col min="34" max="34" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="10.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="15" customHeight="1">
+    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1036,7 +1034,7 @@
       <c r="AI1" s="36"/>
       <c r="AJ1" s="37"/>
     </row>
-    <row r="2" spans="1:36" ht="15" customHeight="1">
+    <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1092,7 +1090,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="15.75">
+    <row r="3" spans="1:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
         <v>1</v>
       </c>
@@ -1176,7 +1174,7 @@
       <c r="AI3" s="47"/>
       <c r="AJ3" s="48"/>
     </row>
-    <row r="4" spans="1:36" ht="60.75">
+    <row r="4" spans="1:36" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>8</v>
       </c>
@@ -1280,7 +1278,7 @@
       </c>
       <c r="AJ4" s="49"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="24">
         <v>16</v>
       </c>
@@ -1390,7 +1388,7 @@
         <v>3310</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="24">
         <v>18</v>
       </c>
@@ -1500,7 +1498,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="24">
         <v>20</v>
       </c>
@@ -1610,7 +1608,7 @@
         <v>3340</v>
       </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="24">
         <v>22</v>
       </c>
@@ -1720,7 +1718,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="24">
         <v>25</v>
       </c>
@@ -1830,7 +1828,7 @@
         <v>3229</v>
       </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="24">
         <v>26</v>
       </c>
@@ -1940,7 +1938,7 @@
         <v>3804</v>
       </c>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="24">
         <v>28</v>
       </c>
@@ -2050,7 +2048,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="24">
         <v>29</v>
       </c>
@@ -2160,7 +2158,7 @@
         <v>3332</v>
       </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="24">
         <v>30</v>
       </c>
@@ -2270,7 +2268,7 @@
         <v>3048</v>
       </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="24">
         <v>34</v>
       </c>
@@ -2380,7 +2378,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="24">
         <v>35</v>
       </c>
@@ -2490,7 +2488,7 @@
         <v>3727</v>
       </c>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="24">
         <v>36</v>
       </c>
@@ -2600,7 +2598,7 @@
         <v>2928</v>
       </c>
     </row>
-    <row r="17" spans="1:36">
+    <row r="17" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="24">
         <v>37</v>
       </c>
@@ -2710,7 +2708,7 @@
         <v>3891</v>
       </c>
     </row>
-    <row r="18" spans="1:36">
+    <row r="18" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="24">
         <v>41</v>
       </c>
@@ -2820,7 +2818,7 @@
         <v>3085</v>
       </c>
     </row>
-    <row r="19" spans="1:36">
+    <row r="19" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="24">
         <v>44</v>
       </c>
@@ -2930,7 +2928,7 @@
         <v>3152</v>
       </c>
     </row>
-    <row r="20" spans="1:36">
+    <row r="20" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="24">
         <v>45</v>
       </c>
@@ -3040,7 +3038,7 @@
         <v>3412</v>
       </c>
     </row>
-    <row r="21" spans="1:36">
+    <row r="21" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="24">
         <v>46</v>
       </c>
@@ -3150,7 +3148,7 @@
         <v>3722</v>
       </c>
     </row>
-    <row r="22" spans="1:36">
+    <row r="22" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="24">
         <v>49</v>
       </c>
@@ -3260,7 +3258,7 @@
         <v>2818</v>
       </c>
     </row>
-    <row r="23" spans="1:36">
+    <row r="23" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="24">
         <v>50</v>
       </c>
@@ -3370,7 +3368,7 @@
         <v>3757</v>
       </c>
     </row>
-    <row r="24" spans="1:36">
+    <row r="24" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="24">
         <v>51</v>
       </c>
@@ -3480,7 +3478,7 @@
         <v>3255</v>
       </c>
     </row>
-    <row r="25" spans="1:36">
+    <row r="25" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="24">
         <v>53</v>
       </c>
@@ -3590,7 +3588,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="26" spans="1:36">
+    <row r="26" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="24">
         <v>55</v>
       </c>
@@ -3700,7 +3698,7 @@
         <v>2827</v>
       </c>
     </row>
-    <row r="27" spans="1:36">
+    <row r="27" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="24">
         <v>56</v>
       </c>
@@ -3810,7 +3808,7 @@
         <v>2816</v>
       </c>
     </row>
-    <row r="28" spans="1:36">
+    <row r="28" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="24">
         <v>58</v>
       </c>
@@ -3920,7 +3918,7 @@
         <v>4011</v>
       </c>
     </row>
-    <row r="29" spans="1:36">
+    <row r="29" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="24">
         <v>60</v>
       </c>
@@ -4030,7 +4028,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="30" spans="1:36">
+    <row r="30" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="24">
         <v>61</v>
       </c>
@@ -4140,7 +4138,7 @@
         <v>3184</v>
       </c>
     </row>
-    <row r="31" spans="1:36">
+    <row r="31" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="24">
         <v>62</v>
       </c>
@@ -4250,7 +4248,7 @@
         <v>3315</v>
       </c>
     </row>
-    <row r="32" spans="1:36">
+    <row r="32" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="24">
         <v>63</v>
       </c>
@@ -4360,7 +4358,7 @@
         <v>4130</v>
       </c>
     </row>
-    <row r="33" spans="1:36">
+    <row r="33" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="24">
         <v>65</v>
       </c>
@@ -4470,7 +4468,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="34" spans="1:36">
+    <row r="34" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="24">
         <v>66</v>
       </c>
@@ -4580,7 +4578,7 @@
         <v>3963</v>
       </c>
     </row>
-    <row r="35" spans="1:36">
+    <row r="35" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="24">
         <v>67</v>
       </c>
@@ -4690,7 +4688,7 @@
         <v>3360</v>
       </c>
     </row>
-    <row r="36" spans="1:36">
+    <row r="36" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="24">
         <v>68</v>
       </c>
@@ -4800,7 +4798,7 @@
         <v>3409</v>
       </c>
     </row>
-    <row r="37" spans="1:36">
+    <row r="37" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="24">
         <v>69</v>
       </c>
@@ -4910,7 +4908,7 @@
         <v>3305</v>
       </c>
     </row>
-    <row r="38" spans="1:36">
+    <row r="38" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="24">
         <v>70</v>
       </c>
@@ -5020,7 +5018,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="39" spans="1:36">
+    <row r="39" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="24">
         <v>72</v>
       </c>
@@ -5130,7 +5128,7 @@
         <v>3904</v>
       </c>
     </row>
-    <row r="40" spans="1:36">
+    <row r="40" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="24">
         <v>73</v>
       </c>
@@ -5240,7 +5238,7 @@
         <v>3256</v>
       </c>
     </row>
-    <row r="41" spans="1:36">
+    <row r="41" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="24">
         <v>76</v>
       </c>
@@ -5350,7 +5348,7 @@
         <v>4154</v>
       </c>
     </row>
-    <row r="42" spans="1:36">
+    <row r="42" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="24">
         <v>77</v>
       </c>
@@ -5460,7 +5458,7 @@
         <v>2853</v>
       </c>
     </row>
-    <row r="43" spans="1:36">
+    <row r="43" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="24">
         <v>78</v>
       </c>
@@ -5570,7 +5568,7 @@
         <v>3038</v>
       </c>
     </row>
-    <row r="44" spans="1:36">
+    <row r="44" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="24">
         <v>79</v>
       </c>
@@ -5680,7 +5678,7 @@
         <v>3335</v>
       </c>
     </row>
-    <row r="45" spans="1:36">
+    <row r="45" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="24">
         <v>80</v>
       </c>
@@ -5790,7 +5788,7 @@
         <v>3281</v>
       </c>
     </row>
-    <row r="46" spans="1:36">
+    <row r="46" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="24">
         <v>82</v>
       </c>
@@ -5900,7 +5898,7 @@
         <v>3308</v>
       </c>
     </row>
-    <row r="47" spans="1:36">
+    <row r="47" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="24">
         <v>84</v>
       </c>
@@ -6010,7 +6008,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="48" spans="1:36">
+    <row r="48" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="24">
         <v>85</v>
       </c>
@@ -6120,7 +6118,7 @@
         <v>3004</v>
       </c>
     </row>
-    <row r="49" spans="1:36">
+    <row r="49" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="24">
         <v>86</v>
       </c>
@@ -6230,7 +6228,7 @@
         <v>3254</v>
       </c>
     </row>
-    <row r="50" spans="1:36">
+    <row r="50" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="24">
         <v>87</v>
       </c>
@@ -6340,7 +6338,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="51" spans="1:36">
+    <row r="51" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="24">
         <v>89</v>
       </c>
@@ -6450,7 +6448,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="52" spans="1:36">
+    <row r="52" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="24">
         <v>90</v>
       </c>
@@ -6560,7 +6558,7 @@
         <v>3008</v>
       </c>
     </row>
-    <row r="53" spans="1:36">
+    <row r="53" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="24">
         <v>93</v>
       </c>
@@ -6670,7 +6668,7 @@
         <v>3578</v>
       </c>
     </row>
-    <row r="54" spans="1:36">
+    <row r="54" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="24">
         <v>94</v>
       </c>
@@ -6780,7 +6778,7 @@
         <v>3240</v>
       </c>
     </row>
-    <row r="55" spans="1:36">
+    <row r="55" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="24">
         <v>96</v>
       </c>
@@ -6890,7 +6888,7 @@
         <v>3489</v>
       </c>
     </row>
-    <row r="56" spans="1:36">
+    <row r="56" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="24">
         <v>97</v>
       </c>
@@ -7000,7 +6998,7 @@
         <v>3047</v>
       </c>
     </row>
-    <row r="57" spans="1:36">
+    <row r="57" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="24">
         <v>98</v>
       </c>
@@ -7110,7 +7108,7 @@
         <v>4076</v>
       </c>
     </row>
-    <row r="58" spans="1:36">
+    <row r="58" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="24">
         <v>99</v>
       </c>
@@ -7220,7 +7218,7 @@
         <v>4240</v>
       </c>
     </row>
-    <row r="59" spans="1:36">
+    <row r="59" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="24">
         <v>100</v>
       </c>
@@ -7330,7 +7328,7 @@
         <v>3530</v>
       </c>
     </row>
-    <row r="60" spans="1:36">
+    <row r="60" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="24">
         <v>103</v>
       </c>
@@ -7440,7 +7438,7 @@
         <v>4205</v>
       </c>
     </row>
-    <row r="61" spans="1:36">
+    <row r="61" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="24">
         <v>104</v>
       </c>
@@ -7550,7 +7548,7 @@
         <v>3508</v>
       </c>
     </row>
-    <row r="62" spans="1:36">
+    <row r="62" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="24">
         <v>105</v>
       </c>
@@ -7660,7 +7658,7 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="63" spans="1:36">
+    <row r="63" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="24">
         <v>106</v>
       </c>
@@ -7770,7 +7768,7 @@
         <v>4259</v>
       </c>
     </row>
-    <row r="64" spans="1:36">
+    <row r="64" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="24">
         <v>108</v>
       </c>
@@ -7880,7 +7878,7 @@
         <v>3312</v>
       </c>
     </row>
-    <row r="65" spans="1:36">
+    <row r="65" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="24">
         <v>109</v>
       </c>
@@ -7990,7 +7988,7 @@
         <v>3904</v>
       </c>
     </row>
-    <row r="66" spans="1:36">
+    <row r="66" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="24">
         <v>110</v>
       </c>
@@ -8100,7 +8098,7 @@
         <v>4077</v>
       </c>
     </row>
-    <row r="67" spans="1:36">
+    <row r="67" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="24">
         <v>111</v>
       </c>
@@ -8210,7 +8208,7 @@
         <v>3430</v>
       </c>
     </row>
-    <row r="68" spans="1:36">
+    <row r="68" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="24">
         <v>112</v>
       </c>
@@ -8320,7 +8318,7 @@
         <v>3413</v>
       </c>
     </row>
-    <row r="69" spans="1:36">
+    <row r="69" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="24">
         <v>113</v>
       </c>
@@ -8430,7 +8428,7 @@
         <v>3557</v>
       </c>
     </row>
-    <row r="70" spans="1:36">
+    <row r="70" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="24">
         <v>115</v>
       </c>
@@ -8540,7 +8538,7 @@
         <v>3540</v>
       </c>
     </row>
-    <row r="71" spans="1:36">
+    <row r="71" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="24">
         <v>117</v>
       </c>
@@ -8650,7 +8648,7 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="72" spans="1:36">
+    <row r="72" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="24">
         <v>119</v>
       </c>
@@ -8760,7 +8758,7 @@
         <v>4237</v>
       </c>
     </row>
-    <row r="73" spans="1:36">
+    <row r="73" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="24">
         <v>120</v>
       </c>
@@ -8870,7 +8868,7 @@
         <v>3947</v>
       </c>
     </row>
-    <row r="74" spans="1:36">
+    <row r="74" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="24">
         <v>121</v>
       </c>
@@ -8980,7 +8978,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="75" spans="1:36">
+    <row r="75" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="24">
         <v>125</v>
       </c>
@@ -9090,7 +9088,7 @@
         <v>3957</v>
       </c>
     </row>
-    <row r="76" spans="1:36">
+    <row r="76" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="24">
         <v>126</v>
       </c>
@@ -9200,7 +9198,7 @@
         <v>3905</v>
       </c>
     </row>
-    <row r="77" spans="1:36">
+    <row r="77" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="24">
         <v>127</v>
       </c>
@@ -9310,7 +9308,7 @@
         <v>3384</v>
       </c>
     </row>
-    <row r="78" spans="1:36">
+    <row r="78" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="24">
         <v>128</v>
       </c>
@@ -9420,7 +9418,7 @@
         <v>3510</v>
       </c>
     </row>
-    <row r="79" spans="1:36">
+    <row r="79" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="24">
         <v>129</v>
       </c>
@@ -9530,7 +9528,7 @@
         <v>3131</v>
       </c>
     </row>
-    <row r="80" spans="1:36">
+    <row r="80" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="24">
         <v>131</v>
       </c>
@@ -9640,7 +9638,7 @@
         <v>3832</v>
       </c>
     </row>
-    <row r="81" spans="1:36">
+    <row r="81" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="24">
         <v>132</v>
       </c>
@@ -9750,7 +9748,7 @@
         <v>3655</v>
       </c>
     </row>
-    <row r="82" spans="1:36">
+    <row r="82" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="24">
         <v>135</v>
       </c>
@@ -9860,7 +9858,7 @@
         <v>3730</v>
       </c>
     </row>
-    <row r="83" spans="1:36">
+    <row r="83" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="24">
         <v>136</v>
       </c>
@@ -9970,7 +9968,7 @@
         <v>3178</v>
       </c>
     </row>
-    <row r="84" spans="1:36">
+    <row r="84" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="24">
         <v>137</v>
       </c>
@@ -10080,7 +10078,7 @@
         <v>3654</v>
       </c>
     </row>
-    <row r="85" spans="1:36">
+    <row r="85" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="24">
         <v>138</v>
       </c>
@@ -10190,7 +10188,7 @@
         <v>3653</v>
       </c>
     </row>
-    <row r="86" spans="1:36">
+    <row r="86" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="24">
         <v>139</v>
       </c>
@@ -10300,7 +10298,7 @@
         <v>4066</v>
       </c>
     </row>
-    <row r="87" spans="1:36">
+    <row r="87" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="24">
         <v>140</v>
       </c>
@@ -10410,7 +10408,7 @@
         <v>3196</v>
       </c>
     </row>
-    <row r="88" spans="1:36">
+    <row r="88" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="24">
         <v>141</v>
       </c>
@@ -10520,7 +10518,7 @@
         <v>3398</v>
       </c>
     </row>
-    <row r="89" spans="1:36">
+    <row r="89" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A89" s="24">
         <v>142</v>
       </c>
@@ -10630,7 +10628,7 @@
         <v>3457</v>
       </c>
     </row>
-    <row r="90" spans="1:36">
+    <row r="90" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="24">
         <v>143</v>
       </c>
@@ -10740,7 +10738,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="91" spans="1:36">
+    <row r="91" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A91" s="24">
         <v>146</v>
       </c>
@@ -10850,7 +10848,7 @@
         <v>3465</v>
       </c>
     </row>
-    <row r="92" spans="1:36">
+    <row r="92" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A92" s="24">
         <v>147</v>
       </c>
@@ -10960,7 +10958,7 @@
         <v>3593</v>
       </c>
     </row>
-    <row r="93" spans="1:36" ht="15" customHeight="1">
+    <row r="93" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="24">
         <v>149</v>
       </c>
@@ -11070,7 +11068,7 @@
         <v>3890</v>
       </c>
     </row>
-    <row r="94" spans="1:36" ht="15" customHeight="1">
+    <row r="94" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="24">
         <v>150</v>
       </c>
@@ -11180,7 +11178,7 @@
         <v>3342</v>
       </c>
     </row>
-    <row r="95" spans="1:36" ht="15" customHeight="1">
+    <row r="95" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="24">
         <v>151</v>
       </c>
@@ -11290,7 +11288,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="96" spans="1:36" ht="15" customHeight="1">
+    <row r="96" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="24">
         <v>152</v>
       </c>
@@ -11400,7 +11398,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="97" spans="1:36" ht="15" customHeight="1">
+    <row r="97" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="24">
         <v>153</v>
       </c>
@@ -11510,7 +11508,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="98" spans="1:36" ht="15" customHeight="1">
+    <row r="98" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="24">
         <v>154</v>
       </c>
@@ -11620,7 +11618,7 @@
         <v>3615</v>
       </c>
     </row>
-    <row r="99" spans="1:36" ht="15" customHeight="1">
+    <row r="99" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="24">
         <v>156</v>
       </c>
@@ -11730,7 +11728,7 @@
         <v>3481</v>
       </c>
     </row>
-    <row r="100" spans="1:36" ht="15" customHeight="1">
+    <row r="100" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="24">
         <v>157</v>
       </c>
@@ -11840,7 +11838,7 @@
         <v>3640</v>
       </c>
     </row>
-    <row r="101" spans="1:36" ht="15" customHeight="1">
+    <row r="101" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="24">
         <v>159</v>
       </c>
@@ -11950,7 +11948,7 @@
         <v>3167</v>
       </c>
     </row>
-    <row r="102" spans="1:36" ht="15" customHeight="1">
+    <row r="102" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="24">
         <v>161</v>
       </c>
@@ -12060,7 +12058,7 @@
         <v>3934</v>
       </c>
     </row>
-    <row r="103" spans="1:36" ht="15" customHeight="1">
+    <row r="103" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="24">
         <v>162</v>
       </c>
@@ -12170,7 +12168,7 @@
         <v>4148</v>
       </c>
     </row>
-    <row r="104" spans="1:36" ht="15" customHeight="1">
+    <row r="104" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="24">
         <v>164</v>
       </c>
@@ -12280,7 +12278,7 @@
         <v>3112</v>
       </c>
     </row>
-    <row r="105" spans="1:36" ht="15" customHeight="1">
+    <row r="105" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="24">
         <v>166</v>
       </c>
@@ -12390,7 +12388,7 @@
         <v>3383</v>
       </c>
     </row>
-    <row r="106" spans="1:36" ht="15" customHeight="1">
+    <row r="106" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="24">
         <v>167</v>
       </c>
@@ -12500,7 +12498,7 @@
         <v>4119</v>
       </c>
     </row>
-    <row r="107" spans="1:36" ht="15" customHeight="1">
+    <row r="107" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="24">
         <v>169</v>
       </c>
@@ -12610,7 +12608,7 @@
         <v>2980</v>
       </c>
     </row>
-    <row r="108" spans="1:36" ht="15" customHeight="1">
+    <row r="108" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="24">
         <v>170</v>
       </c>
@@ -12720,7 +12718,7 @@
         <v>3515</v>
       </c>
     </row>
-    <row r="109" spans="1:36" ht="15" customHeight="1">
+    <row r="109" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="24">
         <v>172</v>
       </c>
@@ -12830,7 +12828,7 @@
         <v>3341</v>
       </c>
     </row>
-    <row r="110" spans="1:36" ht="15" customHeight="1">
+    <row r="110" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="24">
         <v>173</v>
       </c>
@@ -12940,7 +12938,7 @@
         <v>3380</v>
       </c>
     </row>
-    <row r="111" spans="1:36" ht="15" customHeight="1">
+    <row r="111" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="24">
         <v>174</v>
       </c>
@@ -13050,7 +13048,7 @@
         <v>3319</v>
       </c>
     </row>
-    <row r="112" spans="1:36" ht="15" customHeight="1">
+    <row r="112" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="24">
         <v>175</v>
       </c>
@@ -13160,7 +13158,7 @@
         <v>3727</v>
       </c>
     </row>
-    <row r="113" spans="1:36" ht="15" customHeight="1">
+    <row r="113" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="24">
         <v>178</v>
       </c>
@@ -13270,7 +13268,7 @@
         <v>3286</v>
       </c>
     </row>
-    <row r="114" spans="1:36" ht="15" customHeight="1">
+    <row r="114" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="24">
         <v>179</v>
       </c>
@@ -13380,7 +13378,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="115" spans="1:36" ht="15" customHeight="1">
+    <row r="115" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="24">
         <v>181</v>
       </c>
@@ -13490,7 +13488,7 @@
         <v>3581</v>
       </c>
     </row>
-    <row r="116" spans="1:36" ht="15" customHeight="1">
+    <row r="116" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="24">
         <v>182</v>
       </c>
@@ -13600,7 +13598,7 @@
         <v>3895</v>
       </c>
     </row>
-    <row r="117" spans="1:36" ht="15" customHeight="1">
+    <row r="117" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="24">
         <v>183</v>
       </c>
@@ -13710,7 +13708,7 @@
         <v>3751</v>
       </c>
     </row>
-    <row r="118" spans="1:36" ht="15" customHeight="1">
+    <row r="118" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="24">
         <v>185</v>
       </c>
@@ -13820,7 +13818,7 @@
         <v>3105</v>
       </c>
     </row>
-    <row r="119" spans="1:36" ht="15" customHeight="1">
+    <row r="119" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="24">
         <v>186</v>
       </c>
@@ -13930,7 +13928,7 @@
         <v>3779</v>
       </c>
     </row>
-    <row r="120" spans="1:36" ht="15" customHeight="1">
+    <row r="120" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="24">
         <v>187</v>
       </c>
@@ -14040,7 +14038,7 @@
         <v>3611</v>
       </c>
     </row>
-    <row r="121" spans="1:36" ht="15" customHeight="1">
+    <row r="121" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="24">
         <v>188</v>
       </c>
@@ -14150,7 +14148,7 @@
         <v>3023</v>
       </c>
     </row>
-    <row r="122" spans="1:36" ht="15" customHeight="1">
+    <row r="122" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="24">
         <v>189</v>
       </c>
@@ -14278,46 +14276,46 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCF8FC5-328B-42D6-97E6-FD36E465C669}">
   <dimension ref="A1:AJ83"/>
-  <sheetFormatPr defaultColWidth="57" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="57" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="6.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="1.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="10.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="57" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -14357,7 +14355,7 @@
       <c r="AI1" s="36"/>
       <c r="AJ1" s="37"/>
     </row>
-    <row r="2" spans="1:36" ht="15.75" customHeight="1">
+    <row r="2" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -14411,7 +14409,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="15.75">
+    <row r="3" spans="1:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
         <v>1</v>
       </c>
@@ -14495,7 +14493,7 @@
       <c r="AI3" s="47"/>
       <c r="AJ3" s="48"/>
     </row>
-    <row r="4" spans="1:36" ht="45.75">
+    <row r="4" spans="1:36" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>8</v>
       </c>
@@ -14599,7 +14597,7 @@
       </c>
       <c r="AJ4" s="49"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A5" s="24">
         <v>1</v>
       </c>
@@ -14709,7 +14707,7 @@
         <v>3433</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A6" s="24">
         <v>2</v>
       </c>
@@ -14819,7 +14817,7 @@
         <v>3551</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A7" s="24">
         <v>5</v>
       </c>
@@ -14929,7 +14927,7 @@
         <v>3776</v>
       </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A8" s="24">
         <v>6</v>
       </c>
@@ -15039,7 +15037,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="24">
         <v>10</v>
       </c>
@@ -15149,7 +15147,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A10" s="24">
         <v>11</v>
       </c>
@@ -15259,7 +15257,7 @@
         <v>3237</v>
       </c>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="24">
         <v>12</v>
       </c>
@@ -15369,7 +15367,7 @@
         <v>3293</v>
       </c>
     </row>
-    <row r="12" spans="1:36">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="24">
         <v>13</v>
       </c>
@@ -15479,7 +15477,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="24">
         <v>14</v>
       </c>
@@ -15589,7 +15587,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A14" s="24">
         <v>15</v>
       </c>
@@ -15699,7 +15697,7 @@
         <v>3219</v>
       </c>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15" s="24">
         <v>16</v>
       </c>
@@ -15809,7 +15807,7 @@
         <v>3290</v>
       </c>
     </row>
-    <row r="16" spans="1:36">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16" s="24">
         <v>17</v>
       </c>
@@ -15919,7 +15917,7 @@
         <v>3303</v>
       </c>
     </row>
-    <row r="17" spans="1:36">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A17" s="24">
         <v>18</v>
       </c>
@@ -16029,7 +16027,7 @@
         <v>3433</v>
       </c>
     </row>
-    <row r="18" spans="1:36">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A18" s="24">
         <v>20</v>
       </c>
@@ -16139,7 +16137,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="19" spans="1:36">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A19" s="24">
         <v>21</v>
       </c>
@@ -16249,7 +16247,7 @@
         <v>4101</v>
       </c>
     </row>
-    <row r="20" spans="1:36">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A20" s="24">
         <v>22</v>
       </c>
@@ -16359,7 +16357,7 @@
         <v>3089</v>
       </c>
     </row>
-    <row r="21" spans="1:36">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A21" s="24">
         <v>24</v>
       </c>
@@ -16469,7 +16467,7 @@
         <v>3409</v>
       </c>
     </row>
-    <row r="22" spans="1:36">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A22" s="24">
         <v>25</v>
       </c>
@@ -16579,7 +16577,7 @@
         <v>3307</v>
       </c>
     </row>
-    <row r="23" spans="1:36">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A23" s="24">
         <v>26</v>
       </c>
@@ -16689,7 +16687,7 @@
         <v>3235</v>
       </c>
     </row>
-    <row r="24" spans="1:36">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A24" s="24">
         <v>27</v>
       </c>
@@ -16799,7 +16797,7 @@
         <v>3325</v>
       </c>
     </row>
-    <row r="25" spans="1:36">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A25" s="24">
         <v>28</v>
       </c>
@@ -16909,7 +16907,7 @@
         <v>3684</v>
       </c>
     </row>
-    <row r="26" spans="1:36">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A26" s="24">
         <v>29</v>
       </c>
@@ -17019,7 +17017,7 @@
         <v>3346</v>
       </c>
     </row>
-    <row r="27" spans="1:36">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A27" s="24">
         <v>30</v>
       </c>
@@ -17129,7 +17127,7 @@
         <v>3349</v>
       </c>
     </row>
-    <row r="28" spans="1:36">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A28" s="24">
         <v>31</v>
       </c>
@@ -17239,7 +17237,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="29" spans="1:36">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A29" s="24">
         <v>32</v>
       </c>
@@ -17349,7 +17347,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="30" spans="1:36">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A30" s="24">
         <v>35</v>
       </c>
@@ -17459,7 +17457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:36">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A31" s="24">
         <v>36</v>
       </c>
@@ -17569,7 +17567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:36">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A32" s="24">
         <v>38</v>
       </c>
@@ -17679,7 +17677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:36">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A33" s="24">
         <v>39</v>
       </c>
@@ -17789,7 +17787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:36">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A34" s="24">
         <v>40</v>
       </c>
@@ -17899,7 +17897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:36">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A35" s="24">
         <v>41</v>
       </c>
@@ -18009,7 +18007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:36">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A36" s="24">
         <v>42</v>
       </c>
@@ -18119,7 +18117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:36">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A37" s="24">
         <v>43</v>
       </c>
@@ -18229,7 +18227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:36">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A38" s="24">
         <v>44</v>
       </c>
@@ -18339,7 +18337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:36">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A39" s="24">
         <v>45</v>
       </c>
@@ -18449,7 +18447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:36">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A40" s="24">
         <v>46</v>
       </c>
@@ -18457,7 +18455,7 @@
         <v>16526</v>
       </c>
       <c r="C40" s="25">
-        <v>46607</v>
+        <v>46242</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>1</v>
@@ -18559,7 +18557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:36">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A41" s="24">
         <v>47</v>
       </c>
@@ -18567,7 +18565,7 @@
         <v>16527</v>
       </c>
       <c r="C41" s="25">
-        <v>46973</v>
+        <v>46242</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>1</v>
@@ -18669,7 +18667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:36">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A42" s="24">
         <v>48</v>
       </c>
@@ -18677,7 +18675,7 @@
         <v>16528</v>
       </c>
       <c r="C42" s="25">
-        <v>46973</v>
+        <v>46242</v>
       </c>
       <c r="D42" s="20" t="s">
         <v>1</v>
@@ -18779,7 +18777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:36">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A43" s="24">
         <v>49</v>
       </c>
@@ -18787,7 +18785,7 @@
         <v>16529</v>
       </c>
       <c r="C43" s="25">
-        <v>46973</v>
+        <v>46242</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>1</v>
@@ -18889,7 +18887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:36">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A44" s="24">
         <v>50</v>
       </c>
@@ -18897,7 +18895,7 @@
         <v>16530</v>
       </c>
       <c r="C44" s="25">
-        <v>46973</v>
+        <v>46242</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>1</v>
@@ -18999,7 +18997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:36">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A45" s="24">
         <v>52</v>
       </c>
@@ -19109,7 +19107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:36">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A46" s="24">
         <v>53</v>
       </c>
@@ -19219,7 +19217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:36">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A47" s="24">
         <v>54</v>
       </c>
@@ -19329,7 +19327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:36">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A48" s="24">
         <v>55</v>
       </c>
@@ -19439,7 +19437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:36">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A49" s="24">
         <v>57</v>
       </c>
@@ -19549,7 +19547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:36">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A50" s="24">
         <v>59</v>
       </c>
@@ -19659,7 +19657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:36">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A51" s="24">
         <v>60</v>
       </c>
@@ -19769,7 +19767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:36">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A52" s="24">
         <v>61</v>
       </c>
@@ -19879,7 +19877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:36">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A53" s="24">
         <v>63</v>
       </c>
@@ -19989,7 +19987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:36">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A54" s="24">
         <v>65</v>
       </c>
@@ -20099,7 +20097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:36">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A55" s="24">
         <v>67</v>
       </c>
@@ -20209,7 +20207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:36">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A56" s="24">
         <v>68</v>
       </c>
@@ -20319,7 +20317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:36">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A57" s="24">
         <v>70</v>
       </c>
@@ -20429,7 +20427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:36">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A58" s="24">
         <v>71</v>
       </c>
@@ -20539,7 +20537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:36">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A59" s="24">
         <v>72</v>
       </c>
@@ -20649,7 +20647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:36">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A60" s="24">
         <v>74</v>
       </c>
@@ -20759,7 +20757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:36">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A61" s="24">
         <v>75</v>
       </c>
@@ -20869,7 +20867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:36">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A62" s="24">
         <v>76</v>
       </c>
@@ -20979,7 +20977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:36">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A63" s="24">
         <v>77</v>
       </c>
@@ -21089,7 +21087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:36">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A64" s="24">
         <v>80</v>
       </c>
@@ -21199,7 +21197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:36">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A65" s="24">
         <v>81</v>
       </c>
@@ -21309,7 +21307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:36">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A66" s="24">
         <v>83</v>
       </c>
@@ -21419,7 +21417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:36">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A67" s="24">
         <v>84</v>
       </c>
@@ -21529,7 +21527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:36">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A68" s="24">
         <v>86</v>
       </c>
@@ -21639,7 +21637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:36">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A69" s="24">
         <v>88</v>
       </c>
@@ -21749,7 +21747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A70" s="24">
         <v>89</v>
       </c>
@@ -21859,7 +21857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:36">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A71" s="24">
         <v>90</v>
       </c>
@@ -21969,7 +21967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A72" s="24">
         <v>92</v>
       </c>
@@ -22079,7 +22077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:36">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A73" s="24">
         <v>93</v>
       </c>
@@ -22189,7 +22187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:36">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A74" s="24">
         <v>96</v>
       </c>
@@ -22299,7 +22297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:36">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A75" s="24">
         <v>97</v>
       </c>
@@ -22409,7 +22407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:36">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A76" s="24">
         <v>98</v>
       </c>
@@ -22519,7 +22517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:36">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A77" s="24">
         <v>100</v>
       </c>
@@ -22629,7 +22627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:36">
+    <row r="78" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A78" s="24">
         <v>101</v>
       </c>
@@ -22739,7 +22737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:36">
+    <row r="79" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A79" s="24">
         <v>102</v>
       </c>
@@ -22849,7 +22847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:36">
+    <row r="80" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A80" s="24">
         <v>103</v>
       </c>
@@ -22959,7 +22957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:36">
+    <row r="81" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A81" s="24">
         <v>105</v>
       </c>
@@ -23069,7 +23067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:36">
+    <row r="82" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A82" s="24">
         <v>106</v>
       </c>
@@ -23179,7 +23177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:36">
+    <row r="83" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A83" s="24">
         <v>109</v>
       </c>

--- a/Quality.xlsx
+++ b/Quality.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rake Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rudranil.dutta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23FBAB3-3095-40F0-8F5E-24714C004086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF48809-750C-45CF-9FCE-7C6F7CF9417D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2369" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="52">
   <si>
     <t>IGI Report</t>
   </si>
@@ -212,43 +212,13 @@
     <t>F NOTE NO.</t>
   </si>
   <si>
-    <t>30-07-2026</t>
-  </si>
-  <si>
-    <t>31-07-2026</t>
-  </si>
-  <si>
-    <t>13-08-2026</t>
-  </si>
-  <si>
-    <t>14-08-2026</t>
-  </si>
-  <si>
-    <t>15-08-2026</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>16-08-2026</t>
-  </si>
-  <si>
-    <t>17-08-2026</t>
-  </si>
-  <si>
-    <t>17-07-2026</t>
-  </si>
-  <si>
-    <t>18-08-2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-14009]dd\-mm\-yyyy;@"/>
-  </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -316,7 +286,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,6 +320,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -627,7 +603,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -14275,47 +14251,46 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCF8FC5-328B-42D6-97E6-FD36E465C669}">
-  <dimension ref="A1:AJ83"/>
-  <sheetFormatPr defaultColWidth="57" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AK86"/>
+  <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="1.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="10.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="57" style="1"/>
+    <col min="11" max="11" width="7.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="1.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="1.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="10.453125" style="1"/>
+    <col min="32" max="32" width="5.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="10.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -14339,10 +14314,10 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
-      <c r="X1" s="35" t="s">
+      <c r="X1" s="13"/>
+      <c r="Y1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="36"/>
       <c r="Z1" s="36"/>
       <c r="AA1" s="36"/>
       <c r="AB1" s="36"/>
@@ -14353,9 +14328,10 @@
       <c r="AG1" s="36"/>
       <c r="AH1" s="36"/>
       <c r="AI1" s="36"/>
-      <c r="AJ1" s="37"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="37"/>
     </row>
-    <row r="2" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -14369,47 +14345,50 @@
       <c r="K2" s="31"/>
       <c r="L2" s="16"/>
       <c r="M2" s="17"/>
-      <c r="N2" s="38" t="s">
+      <c r="N2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="38"/>
       <c r="P2" s="38"/>
       <c r="Q2" s="38"/>
       <c r="R2" s="38"/>
       <c r="S2" s="38"/>
       <c r="T2" s="38"/>
       <c r="U2" s="38"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="X2" s="40" t="s">
+      <c r="V2" s="38"/>
+      <c r="W2" s="39"/>
+      <c r="X2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="42" t="s">
+      <c r="Z2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="Z2" s="43"/>
       <c r="AA2" s="43"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="48" t="s">
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="48" t="s">
+      <c r="AE2" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="42" t="s">
+      <c r="AF2" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="AF2" s="43"/>
       <c r="AG2" s="43"/>
       <c r="AH2" s="43"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="48" t="s">
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="44"/>
+      <c r="AK2" s="48" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
         <v>1</v>
       </c>
@@ -14449,7 +14428,7 @@
       <c r="M3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="22" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="10" t="s">
@@ -14476,24 +14455,27 @@
       <c r="V3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="46"/>
+      <c r="W3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="45"/>
       <c r="AA3" s="46"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="48"/>
+      <c r="AB3" s="46"/>
+      <c r="AC3" s="47"/>
       <c r="AD3" s="48"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="46"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="45"/>
       <c r="AG3" s="46"/>
       <c r="AH3" s="46"/>
-      <c r="AI3" s="47"/>
-      <c r="AJ3" s="48"/>
+      <c r="AI3" s="46"/>
+      <c r="AJ3" s="47"/>
+      <c r="AK3" s="48"/>
     </row>
-    <row r="4" spans="1:36" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>8</v>
       </c>
@@ -14533,78 +14515,81 @@
       <c r="M4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="20" t="s">
+      <c r="Q4" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="Q4" s="23" t="s">
+      <c r="R4" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="S4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="V4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AB4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AB4" s="6" t="s">
+      <c r="AC4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="49"/>
       <c r="AD4" s="49"/>
-      <c r="AE4" s="6" t="s">
+      <c r="AE4" s="49"/>
+      <c r="AF4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AG4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AG4" s="6" t="s">
+      <c r="AH4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AH4" s="6" t="s">
+      <c r="AI4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AI4" s="2" t="s">
+      <c r="AJ4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ4" s="49"/>
+      <c r="AK4" s="49"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" s="24">
         <v>1</v>
       </c>
       <c r="B5" s="20">
         <v>16481</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="25">
         <v>46235</v>
       </c>
       <c r="D5" s="20" t="s">
@@ -14625,8 +14610,8 @@
       <c r="I5" s="20">
         <v>162004361</v>
       </c>
-      <c r="J5" s="20" t="s">
-        <v>51</v>
+      <c r="J5" s="25">
+        <v>46233</v>
       </c>
       <c r="K5" s="20" t="s">
         <v>1</v>
@@ -14637,77 +14622,80 @@
       <c r="M5" s="20">
         <v>3787</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="20">
         <v>7.33</v>
       </c>
-      <c r="O5" s="20">
+      <c r="P5" s="20">
         <v>26.03</v>
       </c>
-      <c r="P5" s="20">
+      <c r="Q5" s="20">
         <v>37.93</v>
       </c>
-      <c r="Q5" s="20">
+      <c r="R5" s="20">
         <v>3960</v>
       </c>
-      <c r="R5" s="7">
+      <c r="S5" s="7">
         <v>18.46</v>
       </c>
-      <c r="S5" s="7">
+      <c r="T5" s="7">
         <v>22.9</v>
       </c>
-      <c r="T5" s="7">
+      <c r="U5" s="7">
         <v>33.369999999999997</v>
       </c>
-      <c r="U5" s="7">
+      <c r="V5" s="7">
         <v>25.27</v>
       </c>
-      <c r="V5" s="26">
+      <c r="W5" s="26">
         <v>3484</v>
       </c>
-      <c r="W5" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X5" s="33">
+      <c r="X5" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="33">
         <v>18.46</v>
       </c>
-      <c r="Y5" s="27">
+      <c r="Z5" s="27">
         <v>5.98</v>
       </c>
-      <c r="Z5" s="27">
+      <c r="AA5" s="27">
         <v>24.93</v>
       </c>
-      <c r="AA5" s="27">
+      <c r="AB5" s="27">
         <v>38.020000000000003</v>
       </c>
-      <c r="AB5" s="27">
+      <c r="AC5" s="27">
         <v>31.07</v>
       </c>
-      <c r="AC5" s="27">
+      <c r="AD5" s="27">
         <v>3959</v>
       </c>
-      <c r="AD5" s="28">
+      <c r="AE5" s="28">
         <v>3433</v>
       </c>
-      <c r="AE5" s="27">
+      <c r="AF5" s="27">
         <v>6.43</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AG5" s="29">
         <v>24.81</v>
       </c>
-      <c r="AG5" s="29">
+      <c r="AH5" s="29">
         <v>37.840000000000003</v>
       </c>
-      <c r="AH5" s="29">
+      <c r="AI5" s="29">
         <v>30.92</v>
       </c>
-      <c r="AI5" s="29">
+      <c r="AJ5" s="29">
         <v>3940</v>
       </c>
-      <c r="AJ5" s="20">
+      <c r="AK5" s="20">
         <v>3433</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" s="24">
         <v>2</v>
       </c>
@@ -14735,8 +14723,8 @@
       <c r="I6" s="20">
         <v>162004363</v>
       </c>
-      <c r="J6" s="20" t="s">
-        <v>51</v>
+      <c r="J6" s="25">
+        <v>46233</v>
       </c>
       <c r="K6" s="20" t="s">
         <v>1</v>
@@ -14747,77 +14735,80 @@
       <c r="M6" s="20">
         <v>3844</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="20">
         <v>7.89</v>
       </c>
-      <c r="O6" s="20">
+      <c r="P6" s="20">
         <v>27.01</v>
       </c>
-      <c r="P6" s="20">
+      <c r="Q6" s="20">
         <v>33.869999999999997</v>
       </c>
-      <c r="Q6" s="20">
+      <c r="R6" s="20">
         <v>4194</v>
       </c>
-      <c r="R6" s="7">
+      <c r="S6" s="7">
         <v>21.17</v>
       </c>
-      <c r="S6" s="7">
+      <c r="T6" s="7">
         <v>23.12</v>
       </c>
-      <c r="T6" s="7">
+      <c r="U6" s="7">
         <v>28.99</v>
       </c>
-      <c r="U6" s="7">
+      <c r="V6" s="7">
         <v>26.72</v>
       </c>
-      <c r="V6" s="26">
+      <c r="W6" s="26">
         <v>3589</v>
       </c>
-      <c r="W6" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X6" s="27">
+      <c r="X6" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="27">
         <v>21.17</v>
       </c>
-      <c r="Y6" s="27">
+      <c r="Z6" s="27">
         <v>6.85</v>
       </c>
-      <c r="Z6" s="27">
+      <c r="AA6" s="27">
         <v>26.23</v>
       </c>
-      <c r="AA6" s="27">
+      <c r="AB6" s="27">
         <v>33.61</v>
       </c>
-      <c r="AB6" s="27">
+      <c r="AC6" s="27">
         <v>33.31</v>
       </c>
-      <c r="AC6" s="27">
+      <c r="AD6" s="27">
         <v>4196</v>
       </c>
-      <c r="AD6" s="28">
+      <c r="AE6" s="28">
         <v>3551</v>
       </c>
-      <c r="AE6" s="27">
+      <c r="AF6" s="27">
         <v>7.15</v>
       </c>
-      <c r="AF6" s="29">
+      <c r="AG6" s="29">
         <v>26.15</v>
       </c>
-      <c r="AG6" s="29">
+      <c r="AH6" s="29">
         <v>33.5</v>
       </c>
-      <c r="AH6" s="29">
+      <c r="AI6" s="29">
         <v>33.200000000000003</v>
       </c>
-      <c r="AI6" s="29">
+      <c r="AJ6" s="29">
         <v>4182</v>
       </c>
-      <c r="AJ6" s="20">
+      <c r="AK6" s="20">
         <v>3551</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" s="24">
         <v>5</v>
       </c>
@@ -14845,8 +14836,8 @@
       <c r="I7" s="20">
         <v>162011682</v>
       </c>
-      <c r="J7" s="20" t="s">
-        <v>52</v>
+      <c r="J7" s="25">
+        <v>46234</v>
       </c>
       <c r="K7" s="20" t="s">
         <v>1</v>
@@ -14857,77 +14848,80 @@
       <c r="M7" s="20">
         <v>4026.2</v>
       </c>
-      <c r="N7" s="20">
+      <c r="N7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="20">
         <v>7.23</v>
       </c>
-      <c r="O7" s="20">
+      <c r="P7" s="20">
         <v>27.07</v>
       </c>
-      <c r="P7" s="20">
+      <c r="Q7" s="20">
         <v>31.5</v>
       </c>
-      <c r="Q7" s="20">
+      <c r="R7" s="20">
         <v>4432</v>
       </c>
-      <c r="R7" s="7">
+      <c r="S7" s="7">
         <v>20.85</v>
       </c>
-      <c r="S7" s="7">
+      <c r="T7" s="7">
         <v>23.1</v>
       </c>
-      <c r="T7" s="7">
+      <c r="U7" s="7">
         <v>26.88</v>
       </c>
-      <c r="U7" s="7">
+      <c r="V7" s="7">
         <v>29.17</v>
       </c>
-      <c r="V7" s="26">
+      <c r="W7" s="26">
         <v>3781</v>
       </c>
-      <c r="W7" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X7" s="27">
+      <c r="X7" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="27">
         <v>20.85</v>
       </c>
-      <c r="Y7" s="27">
+      <c r="Z7" s="27">
         <v>7.35</v>
       </c>
-      <c r="Z7" s="27">
+      <c r="AA7" s="27">
         <v>25.17</v>
       </c>
-      <c r="AA7" s="27">
+      <c r="AB7" s="27">
         <v>31.12</v>
       </c>
-      <c r="AB7" s="27">
+      <c r="AC7" s="27">
         <v>36.36</v>
       </c>
-      <c r="AC7" s="27">
+      <c r="AD7" s="27">
         <v>4420</v>
       </c>
-      <c r="AD7" s="28">
+      <c r="AE7" s="28">
         <v>3776</v>
       </c>
-      <c r="AE7" s="27">
+      <c r="AF7" s="27">
         <v>7.76</v>
       </c>
-      <c r="AF7" s="29">
+      <c r="AG7" s="29">
         <v>25.06</v>
       </c>
-      <c r="AG7" s="29">
+      <c r="AH7" s="29">
         <v>30.98</v>
       </c>
-      <c r="AH7" s="29">
+      <c r="AI7" s="29">
         <v>36.200000000000003</v>
       </c>
-      <c r="AI7" s="29">
+      <c r="AJ7" s="29">
         <v>4400</v>
       </c>
-      <c r="AJ7" s="20">
+      <c r="AK7" s="20">
         <v>3776</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" s="24">
         <v>6</v>
       </c>
@@ -14955,8 +14949,8 @@
       <c r="I8" s="20">
         <v>162006369</v>
       </c>
-      <c r="J8" s="20" t="s">
-        <v>51</v>
+      <c r="J8" s="25">
+        <v>46233</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>1</v>
@@ -14967,77 +14961,80 @@
       <c r="M8" s="20">
         <v>3476.8</v>
       </c>
-      <c r="N8" s="20">
+      <c r="N8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" s="20">
         <v>7.29</v>
       </c>
-      <c r="O8" s="20">
+      <c r="P8" s="20">
         <v>25.82</v>
       </c>
-      <c r="P8" s="20">
+      <c r="Q8" s="20">
         <v>37.78</v>
       </c>
-      <c r="Q8" s="20">
+      <c r="R8" s="20">
         <v>3837</v>
       </c>
-      <c r="R8" s="7">
+      <c r="S8" s="7">
         <v>17.48</v>
       </c>
-      <c r="S8" s="7">
+      <c r="T8" s="7">
         <v>22.98</v>
       </c>
-      <c r="T8" s="7">
+      <c r="U8" s="7">
         <v>33.630000000000003</v>
       </c>
-      <c r="U8" s="7">
+      <c r="V8" s="7">
         <v>25.91</v>
       </c>
-      <c r="V8" s="26">
+      <c r="W8" s="26">
         <v>3415</v>
       </c>
-      <c r="W8" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X8" s="27">
+      <c r="X8" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="27">
         <v>17.48</v>
       </c>
-      <c r="Y8" s="27">
+      <c r="Z8" s="27">
         <v>7.15</v>
       </c>
-      <c r="Z8" s="27">
+      <c r="AA8" s="27">
         <v>24.16</v>
       </c>
-      <c r="AA8" s="27">
+      <c r="AB8" s="27">
         <v>37.33</v>
       </c>
-      <c r="AB8" s="27">
+      <c r="AC8" s="27">
         <v>31.36</v>
       </c>
-      <c r="AC8" s="27">
+      <c r="AD8" s="27">
         <v>3888</v>
       </c>
-      <c r="AD8" s="28">
+      <c r="AE8" s="28">
         <v>3455</v>
       </c>
-      <c r="AE8" s="27">
+      <c r="AF8" s="27">
         <v>7.54</v>
       </c>
-      <c r="AF8" s="29">
+      <c r="AG8" s="29">
         <v>24.06</v>
       </c>
-      <c r="AG8" s="29">
+      <c r="AH8" s="29">
         <v>37.17</v>
       </c>
-      <c r="AH8" s="29">
+      <c r="AI8" s="29">
         <v>31.23</v>
       </c>
-      <c r="AI8" s="29">
+      <c r="AJ8" s="29">
         <v>3872</v>
       </c>
-      <c r="AJ8" s="20">
+      <c r="AK8" s="20">
         <v>3455</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" s="24">
         <v>10</v>
       </c>
@@ -15065,8 +15062,8 @@
       <c r="I9" s="20">
         <v>162011681</v>
       </c>
-      <c r="J9" s="20" t="s">
-        <v>52</v>
+      <c r="J9" s="25">
+        <v>46234</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>1</v>
@@ -15077,77 +15074,80 @@
       <c r="M9" s="20">
         <v>4148.2</v>
       </c>
-      <c r="N9" s="20">
+      <c r="N9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="20">
         <v>7.67</v>
       </c>
-      <c r="O9" s="20">
+      <c r="P9" s="20">
         <v>24.19</v>
       </c>
-      <c r="P9" s="20">
+      <c r="Q9" s="20">
         <v>38.22</v>
       </c>
-      <c r="Q9" s="20">
+      <c r="R9" s="20">
         <v>3739</v>
       </c>
-      <c r="R9" s="7">
+      <c r="S9" s="7">
         <v>18.87</v>
       </c>
-      <c r="S9" s="7">
+      <c r="T9" s="7">
         <v>21.26</v>
       </c>
-      <c r="T9" s="7">
+      <c r="U9" s="7">
         <v>33.58</v>
       </c>
-      <c r="U9" s="7">
+      <c r="V9" s="7">
         <v>26.29</v>
       </c>
-      <c r="V9" s="26">
+      <c r="W9" s="26">
         <v>3285</v>
       </c>
-      <c r="W9" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X9" s="27">
+      <c r="X9" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="27">
         <v>18.87</v>
       </c>
-      <c r="Y9" s="27">
+      <c r="Z9" s="27">
         <v>6.71</v>
       </c>
-      <c r="Z9" s="27">
+      <c r="AA9" s="27">
         <v>23.28</v>
       </c>
-      <c r="AA9" s="27">
+      <c r="AB9" s="27">
         <v>38.26</v>
       </c>
-      <c r="AB9" s="27">
+      <c r="AC9" s="27">
         <v>31.75</v>
       </c>
-      <c r="AC9" s="27">
+      <c r="AD9" s="27">
         <v>3697</v>
       </c>
-      <c r="AD9" s="28">
+      <c r="AE9" s="28">
         <v>3215</v>
       </c>
-      <c r="AE9" s="27">
+      <c r="AF9" s="27">
         <v>7.03</v>
       </c>
-      <c r="AF9" s="29">
+      <c r="AG9" s="29">
         <v>23.2</v>
       </c>
-      <c r="AG9" s="29">
+      <c r="AH9" s="29">
         <v>38.130000000000003</v>
       </c>
-      <c r="AH9" s="29">
+      <c r="AI9" s="29">
         <v>31.64</v>
       </c>
-      <c r="AI9" s="29">
+      <c r="AJ9" s="29">
         <v>3684</v>
       </c>
-      <c r="AJ9" s="20">
+      <c r="AK9" s="20">
         <v>3215</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" s="24">
         <v>11</v>
       </c>
@@ -15175,8 +15175,8 @@
       <c r="I10" s="20">
         <v>162004364</v>
       </c>
-      <c r="J10" s="20" t="s">
-        <v>52</v>
+      <c r="J10" s="25">
+        <v>46234</v>
       </c>
       <c r="K10" s="20" t="s">
         <v>1</v>
@@ -15187,77 +15187,80 @@
       <c r="M10" s="20">
         <v>3723.4</v>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O10" s="20">
         <v>7.2</v>
       </c>
-      <c r="O10" s="20">
+      <c r="P10" s="20">
         <v>25.42</v>
       </c>
-      <c r="P10" s="20">
+      <c r="Q10" s="20">
         <v>38.770000000000003</v>
       </c>
-      <c r="Q10" s="20">
+      <c r="R10" s="20">
         <v>3735</v>
       </c>
-      <c r="R10" s="7">
+      <c r="S10" s="7">
         <v>19.48</v>
       </c>
-      <c r="S10" s="7">
+      <c r="T10" s="7">
         <v>22.06</v>
       </c>
-      <c r="T10" s="7">
+      <c r="U10" s="7">
         <v>33.64</v>
       </c>
-      <c r="U10" s="7">
+      <c r="V10" s="7">
         <v>24.82</v>
       </c>
-      <c r="V10" s="26">
+      <c r="W10" s="26">
         <v>3241</v>
       </c>
-      <c r="W10" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X10" s="27">
+      <c r="X10" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="27">
         <v>19.48</v>
       </c>
-      <c r="Y10" s="27">
+      <c r="Z10" s="27">
         <v>6.85</v>
       </c>
-      <c r="Z10" s="27">
+      <c r="AA10" s="27">
         <v>23.93</v>
       </c>
-      <c r="AA10" s="27">
+      <c r="AB10" s="27">
         <v>37.68</v>
       </c>
-      <c r="AB10" s="27">
+      <c r="AC10" s="27">
         <v>31.54</v>
       </c>
-      <c r="AC10" s="27">
+      <c r="AD10" s="27">
         <v>3745</v>
       </c>
-      <c r="AD10" s="28">
+      <c r="AE10" s="28">
         <v>3237</v>
       </c>
-      <c r="AE10" s="27">
+      <c r="AF10" s="27">
         <v>7.26</v>
       </c>
-      <c r="AF10" s="29">
+      <c r="AG10" s="29">
         <v>23.82</v>
       </c>
-      <c r="AG10" s="29">
+      <c r="AH10" s="29">
         <v>37.51</v>
       </c>
-      <c r="AH10" s="29">
+      <c r="AI10" s="29">
         <v>31.4</v>
       </c>
-      <c r="AI10" s="29">
+      <c r="AJ10" s="29">
         <v>3729</v>
       </c>
-      <c r="AJ10" s="20">
+      <c r="AK10" s="20">
         <v>3237</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" s="24">
         <v>12</v>
       </c>
@@ -15285,8 +15288,8 @@
       <c r="I11" s="20">
         <v>162006376</v>
       </c>
-      <c r="J11" s="20" t="s">
-        <v>52</v>
+      <c r="J11" s="25">
+        <v>46234</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>1</v>
@@ -15297,77 +15300,80 @@
       <c r="M11" s="20">
         <v>3368.8</v>
       </c>
-      <c r="N11" s="20">
+      <c r="N11" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="20">
         <v>7.34</v>
       </c>
-      <c r="O11" s="20">
+      <c r="P11" s="20">
         <v>26.01</v>
       </c>
-      <c r="P11" s="20">
+      <c r="Q11" s="20">
         <v>38.909999999999997</v>
       </c>
-      <c r="Q11" s="20">
+      <c r="R11" s="20">
         <v>3688</v>
       </c>
-      <c r="R11" s="7">
+      <c r="S11" s="7">
         <v>18.39</v>
       </c>
-      <c r="S11" s="7">
+      <c r="T11" s="7">
         <v>22.91</v>
       </c>
-      <c r="T11" s="7">
+      <c r="U11" s="7">
         <v>34.270000000000003</v>
       </c>
-      <c r="U11" s="7">
+      <c r="V11" s="7">
         <v>24.43</v>
       </c>
-      <c r="V11" s="26">
+      <c r="W11" s="26">
         <v>3248</v>
       </c>
-      <c r="W11" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X11" s="27">
+      <c r="X11" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="27">
         <v>18.39</v>
       </c>
-      <c r="Y11" s="27">
+      <c r="Z11" s="27">
         <v>7.41</v>
       </c>
-      <c r="Z11" s="27">
+      <c r="AA11" s="27">
         <v>24.3</v>
       </c>
-      <c r="AA11" s="27">
+      <c r="AB11" s="27">
         <v>37.67</v>
       </c>
-      <c r="AB11" s="27">
+      <c r="AC11" s="27">
         <v>30.62</v>
       </c>
-      <c r="AC11" s="27">
+      <c r="AD11" s="27">
         <v>3736</v>
       </c>
-      <c r="AD11" s="28">
+      <c r="AE11" s="28">
         <v>3293</v>
       </c>
-      <c r="AE11" s="27">
+      <c r="AF11" s="27">
         <v>7.76</v>
       </c>
-      <c r="AF11" s="29">
+      <c r="AG11" s="29">
         <v>24.21</v>
       </c>
-      <c r="AG11" s="29">
+      <c r="AH11" s="29">
         <v>37.53</v>
       </c>
-      <c r="AH11" s="29">
+      <c r="AI11" s="29">
         <v>30.5</v>
       </c>
-      <c r="AI11" s="29">
+      <c r="AJ11" s="29">
         <v>3722</v>
       </c>
-      <c r="AJ11" s="20">
+      <c r="AK11" s="20">
         <v>3293</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" s="24">
         <v>13</v>
       </c>
@@ -15395,8 +15401,8 @@
       <c r="I12" s="20">
         <v>162004365</v>
       </c>
-      <c r="J12" s="20" t="s">
-        <v>52</v>
+      <c r="J12" s="25">
+        <v>46234</v>
       </c>
       <c r="K12" s="20" t="s">
         <v>1</v>
@@ -15407,77 +15413,80 @@
       <c r="M12" s="20">
         <v>3823.2</v>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12" s="20">
         <v>7.41</v>
       </c>
-      <c r="O12" s="20">
+      <c r="P12" s="20">
         <v>26.19</v>
       </c>
-      <c r="P12" s="20">
+      <c r="Q12" s="20">
         <v>36.99</v>
       </c>
-      <c r="Q12" s="20">
+      <c r="R12" s="20">
         <v>3938</v>
       </c>
-      <c r="R12" s="7">
+      <c r="S12" s="7">
         <v>20.69</v>
       </c>
-      <c r="S12" s="7">
+      <c r="T12" s="7">
         <v>22.43</v>
       </c>
-      <c r="T12" s="7">
+      <c r="U12" s="7">
         <v>31.68</v>
       </c>
-      <c r="U12" s="7">
+      <c r="V12" s="7">
         <v>25.2</v>
       </c>
-      <c r="V12" s="26">
+      <c r="W12" s="26">
         <v>3373</v>
       </c>
-      <c r="W12" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X12" s="27">
+      <c r="X12" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="27">
         <v>20.69</v>
       </c>
-      <c r="Y12" s="27">
+      <c r="Z12" s="27">
         <v>7.53</v>
       </c>
-      <c r="Z12" s="27">
+      <c r="AA12" s="27">
         <v>24.05</v>
       </c>
-      <c r="AA12" s="27">
+      <c r="AB12" s="27">
         <v>38.14</v>
       </c>
-      <c r="AB12" s="27">
+      <c r="AC12" s="27">
         <v>30.28</v>
       </c>
-      <c r="AC12" s="27">
+      <c r="AD12" s="27">
         <v>3887</v>
       </c>
-      <c r="AD12" s="28">
+      <c r="AE12" s="28">
         <v>3334</v>
       </c>
-      <c r="AE12" s="27">
+      <c r="AF12" s="27">
         <v>7.84</v>
       </c>
-      <c r="AF12" s="29">
+      <c r="AG12" s="29">
         <v>23.97</v>
       </c>
-      <c r="AG12" s="29">
+      <c r="AH12" s="29">
         <v>38.01</v>
       </c>
-      <c r="AH12" s="29">
+      <c r="AI12" s="29">
         <v>30.18</v>
       </c>
-      <c r="AI12" s="29">
+      <c r="AJ12" s="29">
         <v>3874</v>
       </c>
-      <c r="AJ12" s="20">
+      <c r="AK12" s="20">
         <v>3334</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" s="24">
         <v>14</v>
       </c>
@@ -15506,7 +15515,7 @@
         <v>162011684</v>
       </c>
       <c r="J13" s="25">
-        <v>46030</v>
+        <v>46235</v>
       </c>
       <c r="K13" s="20" t="s">
         <v>1</v>
@@ -15517,77 +15526,80 @@
       <c r="M13" s="20">
         <v>3802.8</v>
       </c>
-      <c r="N13" s="20">
+      <c r="N13" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O13" s="20">
         <v>7.55</v>
       </c>
-      <c r="O13" s="20">
+      <c r="P13" s="20">
         <v>23.36</v>
       </c>
-      <c r="P13" s="20">
+      <c r="Q13" s="20">
         <v>41</v>
       </c>
-      <c r="Q13" s="20">
+      <c r="R13" s="20">
         <v>3678</v>
       </c>
-      <c r="R13" s="7">
+      <c r="S13" s="7">
         <v>19.97</v>
       </c>
-      <c r="S13" s="7">
+      <c r="T13" s="7">
         <v>20.22</v>
       </c>
-      <c r="T13" s="7">
+      <c r="U13" s="7">
         <v>35.49</v>
       </c>
-      <c r="U13" s="7">
+      <c r="V13" s="7">
         <v>24.32</v>
       </c>
-      <c r="V13" s="26">
+      <c r="W13" s="26">
         <v>3184</v>
       </c>
-      <c r="W13" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X13" s="27">
+      <c r="X13" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="27">
         <v>19.97</v>
       </c>
-      <c r="Y13" s="27">
+      <c r="Z13" s="27">
         <v>6.39</v>
       </c>
-      <c r="Z13" s="27">
+      <c r="AA13" s="27">
         <v>21.78</v>
       </c>
-      <c r="AA13" s="27">
+      <c r="AB13" s="27">
         <v>40.630000000000003</v>
       </c>
-      <c r="AB13" s="27">
+      <c r="AC13" s="27">
         <v>31.2</v>
       </c>
-      <c r="AC13" s="27">
+      <c r="AD13" s="27">
         <v>3730</v>
       </c>
-      <c r="AD13" s="28">
+      <c r="AE13" s="28">
         <v>3189</v>
       </c>
-      <c r="AE13" s="27">
+      <c r="AF13" s="27">
         <v>7.81</v>
       </c>
-      <c r="AF13" s="29">
+      <c r="AG13" s="29">
         <v>21.45</v>
       </c>
-      <c r="AG13" s="29">
+      <c r="AH13" s="29">
         <v>40.01</v>
       </c>
-      <c r="AH13" s="29">
+      <c r="AI13" s="29">
         <v>30.73</v>
       </c>
-      <c r="AI13" s="29">
+      <c r="AJ13" s="29">
         <v>3673</v>
       </c>
-      <c r="AJ13" s="20">
+      <c r="AK13" s="20">
         <v>3189</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" s="24">
         <v>15</v>
       </c>
@@ -15616,7 +15628,7 @@
         <v>162004366</v>
       </c>
       <c r="J14" s="25">
-        <v>46030</v>
+        <v>46235</v>
       </c>
       <c r="K14" s="20" t="s">
         <v>1</v>
@@ -15627,77 +15639,80 @@
       <c r="M14" s="20">
         <v>3709.2</v>
       </c>
-      <c r="N14" s="20">
+      <c r="N14" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="20">
         <v>7.73</v>
       </c>
-      <c r="O14" s="20">
+      <c r="P14" s="20">
         <v>24.95</v>
       </c>
-      <c r="P14" s="20">
+      <c r="Q14" s="20">
         <v>38.74</v>
       </c>
-      <c r="Q14" s="20">
+      <c r="R14" s="20">
         <v>3638</v>
       </c>
-      <c r="R14" s="7">
+      <c r="S14" s="7">
         <v>18.920000000000002</v>
       </c>
-      <c r="S14" s="7">
+      <c r="T14" s="7">
         <v>21.92</v>
       </c>
-      <c r="T14" s="7">
+      <c r="U14" s="7">
         <v>34.04</v>
       </c>
-      <c r="U14" s="7">
+      <c r="V14" s="7">
         <v>25.12</v>
       </c>
-      <c r="V14" s="26">
+      <c r="W14" s="26">
         <v>3197</v>
       </c>
-      <c r="W14" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X14" s="27">
+      <c r="X14" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="27">
         <v>18.920000000000002</v>
       </c>
-      <c r="Y14" s="27">
+      <c r="Z14" s="27">
         <v>6.46</v>
       </c>
-      <c r="Z14" s="27">
+      <c r="AA14" s="27">
         <v>23.88</v>
       </c>
-      <c r="AA14" s="27">
+      <c r="AB14" s="27">
         <v>37.9</v>
       </c>
-      <c r="AB14" s="27">
+      <c r="AC14" s="27">
         <v>31.76</v>
       </c>
-      <c r="AC14" s="27">
+      <c r="AD14" s="27">
         <v>3714</v>
       </c>
-      <c r="AD14" s="28">
+      <c r="AE14" s="28">
         <v>3219</v>
       </c>
-      <c r="AE14" s="27">
+      <c r="AF14" s="27">
         <v>6.74</v>
       </c>
-      <c r="AF14" s="29">
+      <c r="AG14" s="29">
         <v>23.81</v>
       </c>
-      <c r="AG14" s="29">
+      <c r="AH14" s="29">
         <v>37.79</v>
       </c>
-      <c r="AH14" s="29">
+      <c r="AI14" s="29">
         <v>31.66</v>
       </c>
-      <c r="AI14" s="29">
+      <c r="AJ14" s="29">
         <v>3703</v>
       </c>
-      <c r="AJ14" s="20">
+      <c r="AK14" s="20">
         <v>3219</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" s="24">
         <v>16</v>
       </c>
@@ -15726,7 +15741,7 @@
         <v>162006378</v>
       </c>
       <c r="J15" s="25">
-        <v>46030</v>
+        <v>46235</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>1</v>
@@ -15737,77 +15752,80 @@
       <c r="M15" s="20">
         <v>3799.8</v>
       </c>
-      <c r="N15" s="20">
+      <c r="N15" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O15" s="20">
         <v>7.29</v>
       </c>
-      <c r="O15" s="20">
+      <c r="P15" s="20">
         <v>26.29</v>
       </c>
-      <c r="P15" s="20">
+      <c r="Q15" s="20">
         <v>37.880000000000003</v>
       </c>
-      <c r="Q15" s="20">
+      <c r="R15" s="20">
         <v>3902</v>
       </c>
-      <c r="R15" s="7">
+      <c r="S15" s="7">
         <v>20.63</v>
       </c>
-      <c r="S15" s="7">
+      <c r="T15" s="7">
         <v>22.51</v>
       </c>
-      <c r="T15" s="7">
+      <c r="U15" s="7">
         <v>32.43</v>
       </c>
-      <c r="U15" s="7">
+      <c r="V15" s="7">
         <v>24.43</v>
       </c>
-      <c r="V15" s="26">
+      <c r="W15" s="26">
         <v>3341</v>
       </c>
-      <c r="W15" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X15" s="27">
+      <c r="X15" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="27">
         <v>20.63</v>
       </c>
-      <c r="Y15" s="27">
+      <c r="Z15" s="27">
         <v>6.37</v>
       </c>
-      <c r="Z15" s="27">
+      <c r="AA15" s="27">
         <v>24.53</v>
       </c>
-      <c r="AA15" s="27">
+      <c r="AB15" s="27">
         <v>38.35</v>
       </c>
-      <c r="AB15" s="27">
+      <c r="AC15" s="27">
         <v>30.75</v>
       </c>
-      <c r="AC15" s="27">
+      <c r="AD15" s="27">
         <v>3881</v>
       </c>
-      <c r="AD15" s="28">
+      <c r="AE15" s="28">
         <v>3290</v>
       </c>
-      <c r="AE15" s="27">
+      <c r="AF15" s="27">
         <v>6.87</v>
       </c>
-      <c r="AF15" s="29">
+      <c r="AG15" s="29">
         <v>24.4</v>
       </c>
-      <c r="AG15" s="29">
+      <c r="AH15" s="29">
         <v>38.15</v>
       </c>
-      <c r="AH15" s="29">
+      <c r="AI15" s="29">
         <v>30.59</v>
       </c>
-      <c r="AI15" s="29">
+      <c r="AJ15" s="29">
         <v>3860</v>
       </c>
-      <c r="AJ15" s="20">
+      <c r="AK15" s="20">
         <v>3290</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" s="24">
         <v>17</v>
       </c>
@@ -15836,7 +15854,7 @@
         <v>162006382</v>
       </c>
       <c r="J16" s="25">
-        <v>46030</v>
+        <v>46235</v>
       </c>
       <c r="K16" s="20" t="s">
         <v>1</v>
@@ -15847,77 +15865,80 @@
       <c r="M16" s="20">
         <v>3869.6</v>
       </c>
-      <c r="N16" s="20">
+      <c r="N16" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" s="20">
         <v>7.17</v>
       </c>
-      <c r="O16" s="20">
+      <c r="P16" s="20">
         <v>26.02</v>
       </c>
-      <c r="P16" s="20">
+      <c r="Q16" s="20">
         <v>37.83</v>
       </c>
-      <c r="Q16" s="20">
+      <c r="R16" s="20">
         <v>3862</v>
       </c>
-      <c r="R16" s="7">
+      <c r="S16" s="7">
         <v>20.29</v>
       </c>
-      <c r="S16" s="7">
+      <c r="T16" s="7">
         <v>22.34</v>
       </c>
-      <c r="T16" s="7">
+      <c r="U16" s="7">
         <v>32.479999999999997</v>
       </c>
-      <c r="U16" s="7">
+      <c r="V16" s="7">
         <v>24.89</v>
       </c>
-      <c r="V16" s="26">
+      <c r="W16" s="26">
         <v>3316</v>
       </c>
-      <c r="W16" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X16" s="27">
+      <c r="X16" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="27">
         <v>20.29</v>
       </c>
-      <c r="Y16" s="27">
+      <c r="Z16" s="27">
         <v>6.33</v>
       </c>
-      <c r="Z16" s="27">
+      <c r="AA16" s="27">
         <v>24.32</v>
       </c>
-      <c r="AA16" s="27">
+      <c r="AB16" s="27">
         <v>38.299999999999997</v>
       </c>
-      <c r="AB16" s="27">
+      <c r="AC16" s="27">
         <v>31.05</v>
       </c>
-      <c r="AC16" s="27">
+      <c r="AD16" s="27">
         <v>3881</v>
       </c>
-      <c r="AD16" s="28">
+      <c r="AE16" s="28">
         <v>3303</v>
       </c>
-      <c r="AE16" s="27">
+      <c r="AF16" s="27">
         <v>6.72</v>
       </c>
-      <c r="AF16" s="29">
+      <c r="AG16" s="29">
         <v>24.22</v>
       </c>
-      <c r="AG16" s="29">
+      <c r="AH16" s="29">
         <v>38.14</v>
       </c>
-      <c r="AH16" s="29">
+      <c r="AI16" s="29">
         <v>30.92</v>
       </c>
-      <c r="AI16" s="29">
+      <c r="AJ16" s="29">
         <v>3865</v>
       </c>
-      <c r="AJ16" s="20">
+      <c r="AK16" s="20">
         <v>3303</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" s="24">
         <v>18</v>
       </c>
@@ -15946,7 +15967,7 @@
         <v>162004367</v>
       </c>
       <c r="J17" s="25">
-        <v>46030</v>
+        <v>46235</v>
       </c>
       <c r="K17" s="20" t="s">
         <v>1</v>
@@ -15957,77 +15978,80 @@
       <c r="M17" s="20">
         <v>3682.6</v>
       </c>
-      <c r="N17" s="20">
+      <c r="N17" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O17" s="20">
         <v>7.51</v>
       </c>
-      <c r="O17" s="20">
+      <c r="P17" s="20">
         <v>25.9</v>
       </c>
-      <c r="P17" s="20">
+      <c r="Q17" s="20">
         <v>36.6</v>
       </c>
-      <c r="Q17" s="20">
+      <c r="R17" s="20">
         <v>3989</v>
       </c>
-      <c r="R17" s="7">
+      <c r="S17" s="7">
         <v>20.27</v>
       </c>
-      <c r="S17" s="7">
+      <c r="T17" s="7">
         <v>22.33</v>
       </c>
-      <c r="T17" s="7">
+      <c r="U17" s="7">
         <v>31.55</v>
       </c>
-      <c r="U17" s="7">
+      <c r="V17" s="7">
         <v>25.85</v>
       </c>
-      <c r="V17" s="26">
+      <c r="W17" s="26">
         <v>3439</v>
       </c>
-      <c r="W17" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X17" s="27">
+      <c r="X17" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="27">
         <v>20.27</v>
       </c>
-      <c r="Y17" s="27">
+      <c r="Z17" s="27">
         <v>6.27</v>
       </c>
-      <c r="Z17" s="27">
+      <c r="AA17" s="27">
         <v>24.29</v>
       </c>
-      <c r="AA17" s="27">
+      <c r="AB17" s="27">
         <v>35.93</v>
       </c>
-      <c r="AB17" s="27">
+      <c r="AC17" s="27">
         <v>33.51</v>
       </c>
-      <c r="AC17" s="27">
+      <c r="AD17" s="27">
         <v>4036</v>
       </c>
-      <c r="AD17" s="28">
+      <c r="AE17" s="28">
         <v>3433</v>
       </c>
-      <c r="AE17" s="27">
+      <c r="AF17" s="27">
         <v>7.61</v>
       </c>
-      <c r="AF17" s="29">
+      <c r="AG17" s="29">
         <v>23.94</v>
       </c>
-      <c r="AG17" s="29">
+      <c r="AH17" s="29">
         <v>35.42</v>
       </c>
-      <c r="AH17" s="29">
+      <c r="AI17" s="29">
         <v>33.03</v>
       </c>
-      <c r="AI17" s="29">
+      <c r="AJ17" s="29">
         <v>3978</v>
       </c>
-      <c r="AJ17" s="20">
+      <c r="AK17" s="20">
         <v>3433</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" s="24">
         <v>20</v>
       </c>
@@ -16056,7 +16080,7 @@
         <v>162006383</v>
       </c>
       <c r="J18" s="25">
-        <v>46030</v>
+        <v>46235</v>
       </c>
       <c r="K18" s="20" t="s">
         <v>1</v>
@@ -16067,77 +16091,80 @@
       <c r="M18" s="20">
         <v>3997.8</v>
       </c>
-      <c r="N18" s="20">
+      <c r="N18" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="20">
         <v>8.16</v>
       </c>
-      <c r="O18" s="20">
+      <c r="P18" s="20">
         <v>26.38</v>
       </c>
-      <c r="P18" s="20">
+      <c r="Q18" s="20">
         <v>34.89</v>
       </c>
-      <c r="Q18" s="20">
+      <c r="R18" s="20">
         <v>4121</v>
       </c>
-      <c r="R18" s="7">
+      <c r="S18" s="7">
         <v>23.11</v>
       </c>
-      <c r="S18" s="7">
+      <c r="T18" s="7">
         <v>22.09</v>
       </c>
-      <c r="T18" s="7">
+      <c r="U18" s="7">
         <v>29.21</v>
       </c>
-      <c r="U18" s="7">
+      <c r="V18" s="7">
         <v>25.59</v>
       </c>
-      <c r="V18" s="26">
+      <c r="W18" s="26">
         <v>3450</v>
       </c>
-      <c r="W18" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X18" s="27">
+      <c r="X18" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="27">
         <v>23.11</v>
       </c>
-      <c r="Y18" s="27">
+      <c r="Z18" s="27">
         <v>6.85</v>
       </c>
-      <c r="Z18" s="27">
+      <c r="AA18" s="27">
         <v>25.85</v>
       </c>
-      <c r="AA18" s="27">
+      <c r="AB18" s="27">
         <v>34.22</v>
       </c>
-      <c r="AB18" s="27">
+      <c r="AC18" s="27">
         <v>33.08</v>
       </c>
-      <c r="AC18" s="27">
+      <c r="AD18" s="27">
         <v>4139</v>
       </c>
-      <c r="AD18" s="28">
+      <c r="AE18" s="28">
         <v>3417</v>
       </c>
-      <c r="AE18" s="27">
+      <c r="AF18" s="27">
         <v>7.21</v>
       </c>
-      <c r="AF18" s="29">
+      <c r="AG18" s="29">
         <v>25.75</v>
       </c>
-      <c r="AG18" s="29">
+      <c r="AH18" s="29">
         <v>34.090000000000003</v>
       </c>
-      <c r="AH18" s="29">
+      <c r="AI18" s="29">
         <v>32.950000000000003</v>
       </c>
-      <c r="AI18" s="29">
+      <c r="AJ18" s="29">
         <v>4123</v>
       </c>
-      <c r="AJ18" s="20">
+      <c r="AK18" s="20">
         <v>3417</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" s="24">
         <v>21</v>
       </c>
@@ -16166,7 +16193,7 @@
         <v>162011687</v>
       </c>
       <c r="J19" s="25">
-        <v>46061</v>
+        <v>46236</v>
       </c>
       <c r="K19" s="20" t="s">
         <v>1</v>
@@ -16177,77 +16204,80 @@
       <c r="M19" s="20">
         <v>3729.4</v>
       </c>
-      <c r="N19" s="20">
+      <c r="N19" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O19" s="20">
         <v>8.26</v>
       </c>
-      <c r="O19" s="20">
+      <c r="P19" s="20">
         <v>28.2</v>
       </c>
-      <c r="P19" s="20">
+      <c r="Q19" s="20">
         <v>25.74</v>
       </c>
-      <c r="Q19" s="20">
+      <c r="R19" s="20">
         <v>4952</v>
       </c>
-      <c r="R19" s="7">
+      <c r="S19" s="7">
         <v>22.85</v>
       </c>
-      <c r="S19" s="7">
+      <c r="T19" s="7">
         <v>23.72</v>
       </c>
-      <c r="T19" s="7">
+      <c r="U19" s="7">
         <v>21.65</v>
       </c>
-      <c r="U19" s="7">
+      <c r="V19" s="7">
         <v>31.78</v>
       </c>
-      <c r="V19" s="26">
+      <c r="W19" s="26">
         <v>4164</v>
       </c>
-      <c r="W19" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X19" s="27">
+      <c r="X19" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="27">
         <v>22.85</v>
       </c>
-      <c r="Y19" s="27">
+      <c r="Z19" s="27">
         <v>6.87</v>
       </c>
-      <c r="Z19" s="27">
+      <c r="AA19" s="27">
         <v>27.44</v>
       </c>
-      <c r="AA19" s="27">
+      <c r="AB19" s="27">
         <v>26.95</v>
       </c>
-      <c r="AB19" s="27">
+      <c r="AC19" s="27">
         <v>38.74</v>
       </c>
-      <c r="AC19" s="27">
+      <c r="AD19" s="27">
         <v>4951</v>
       </c>
-      <c r="AD19" s="28">
+      <c r="AE19" s="28">
         <v>4101</v>
       </c>
-      <c r="AE19" s="27">
+      <c r="AF19" s="27">
         <v>7.29</v>
       </c>
-      <c r="AF19" s="29">
+      <c r="AG19" s="29">
         <v>27.32</v>
       </c>
-      <c r="AG19" s="29">
+      <c r="AH19" s="29">
         <v>26.83</v>
       </c>
-      <c r="AH19" s="29">
+      <c r="AI19" s="29">
         <v>38.57</v>
       </c>
-      <c r="AI19" s="29">
+      <c r="AJ19" s="29">
         <v>4929</v>
       </c>
-      <c r="AJ19" s="20">
+      <c r="AK19" s="20">
         <v>4101</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" s="24">
         <v>22</v>
       </c>
@@ -16276,7 +16306,7 @@
         <v>162011686</v>
       </c>
       <c r="J20" s="25">
-        <v>46030</v>
+        <v>46235</v>
       </c>
       <c r="K20" s="20" t="s">
         <v>1</v>
@@ -16287,77 +16317,80 @@
       <c r="M20" s="20">
         <v>3936.8</v>
       </c>
-      <c r="N20" s="20">
+      <c r="N20" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O20" s="20">
         <v>6.48</v>
       </c>
-      <c r="O20" s="20">
+      <c r="P20" s="20">
         <v>23.5</v>
       </c>
-      <c r="P20" s="20">
+      <c r="Q20" s="20">
         <v>42.16</v>
       </c>
-      <c r="Q20" s="20">
+      <c r="R20" s="20">
         <v>3599</v>
       </c>
-      <c r="R20" s="7">
+      <c r="S20" s="7">
         <v>20.62</v>
       </c>
-      <c r="S20" s="7">
+      <c r="T20" s="7">
         <v>19.95</v>
       </c>
-      <c r="T20" s="7">
+      <c r="U20" s="7">
         <v>35.79</v>
       </c>
-      <c r="U20" s="7">
+      <c r="V20" s="7">
         <v>23.64</v>
       </c>
-      <c r="V20" s="26">
+      <c r="W20" s="26">
         <v>3055</v>
       </c>
-      <c r="W20" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X20" s="27">
+      <c r="X20" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="27">
         <v>20.62</v>
       </c>
-      <c r="Y20" s="27">
+      <c r="Z20" s="27">
         <v>6.09</v>
       </c>
-      <c r="Z20" s="27">
+      <c r="AA20" s="27">
         <v>22.12</v>
       </c>
-      <c r="AA20" s="27">
+      <c r="AB20" s="27">
         <v>41.23</v>
       </c>
-      <c r="AB20" s="27">
+      <c r="AC20" s="27">
         <v>30.56</v>
       </c>
-      <c r="AC20" s="27">
+      <c r="AD20" s="27">
         <v>3654</v>
       </c>
-      <c r="AD20" s="28">
+      <c r="AE20" s="28">
         <v>3089</v>
       </c>
-      <c r="AE20" s="27">
+      <c r="AF20" s="27">
         <v>6.56</v>
       </c>
-      <c r="AF20" s="29">
+      <c r="AG20" s="29">
         <v>22.01</v>
       </c>
-      <c r="AG20" s="29">
+      <c r="AH20" s="29">
         <v>41.02</v>
       </c>
-      <c r="AH20" s="29">
+      <c r="AI20" s="29">
         <v>30.41</v>
       </c>
-      <c r="AI20" s="29">
+      <c r="AJ20" s="29">
         <v>3636</v>
       </c>
-      <c r="AJ20" s="20">
+      <c r="AK20" s="20">
         <v>3089</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" s="24">
         <v>24</v>
       </c>
@@ -16386,7 +16419,7 @@
         <v>162004369</v>
       </c>
       <c r="J21" s="25">
-        <v>46061</v>
+        <v>46236</v>
       </c>
       <c r="K21" s="20" t="s">
         <v>1</v>
@@ -16397,77 +16430,80 @@
       <c r="M21" s="20">
         <v>3931.6</v>
       </c>
-      <c r="N21" s="20">
+      <c r="N21" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O21" s="20">
         <v>7.34</v>
       </c>
-      <c r="O21" s="20">
+      <c r="P21" s="20">
         <v>26.23</v>
       </c>
-      <c r="P21" s="20">
+      <c r="Q21" s="20">
         <v>36.159999999999997</v>
       </c>
-      <c r="Q21" s="20">
+      <c r="R21" s="20">
         <v>4067</v>
       </c>
-      <c r="R21" s="7">
+      <c r="S21" s="7">
         <v>21.43</v>
       </c>
-      <c r="S21" s="7">
+      <c r="T21" s="7">
         <v>22.24</v>
       </c>
-      <c r="T21" s="7">
+      <c r="U21" s="7">
         <v>30.66</v>
       </c>
-      <c r="U21" s="7">
+      <c r="V21" s="7">
         <v>25.67</v>
       </c>
-      <c r="V21" s="26">
+      <c r="W21" s="26">
         <v>3449</v>
       </c>
-      <c r="W21" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X21" s="27">
+      <c r="X21" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="27">
         <v>21.43</v>
       </c>
-      <c r="Y21" s="27">
+      <c r="Z21" s="27">
         <v>7.1</v>
       </c>
-      <c r="Z21" s="27">
+      <c r="AA21" s="27">
         <v>24.64</v>
       </c>
-      <c r="AA21" s="27">
+      <c r="AB21" s="27">
         <v>35.479999999999997</v>
       </c>
-      <c r="AB21" s="27">
+      <c r="AC21" s="27">
         <v>32.78</v>
       </c>
-      <c r="AC21" s="27">
+      <c r="AD21" s="27">
         <v>4031</v>
       </c>
-      <c r="AD21" s="28">
+      <c r="AE21" s="28">
         <v>3409</v>
       </c>
-      <c r="AE21" s="27">
+      <c r="AF21" s="27">
         <v>7.54</v>
       </c>
-      <c r="AF21" s="29">
+      <c r="AG21" s="29">
         <v>24.52</v>
       </c>
-      <c r="AG21" s="29">
+      <c r="AH21" s="29">
         <v>35.31</v>
       </c>
-      <c r="AH21" s="29">
+      <c r="AI21" s="29">
         <v>32.619999999999997</v>
       </c>
-      <c r="AI21" s="29">
+      <c r="AJ21" s="29">
         <v>4012</v>
       </c>
-      <c r="AJ21" s="20">
+      <c r="AK21" s="20">
         <v>3409</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" s="24">
         <v>25</v>
       </c>
@@ -16496,7 +16532,7 @@
         <v>162004370</v>
       </c>
       <c r="J22" s="25">
-        <v>46061</v>
+        <v>46236</v>
       </c>
       <c r="K22" s="20" t="s">
         <v>1</v>
@@ -16507,77 +16543,80 @@
       <c r="M22" s="20">
         <v>4171.8</v>
       </c>
-      <c r="N22" s="20">
+      <c r="N22" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O22" s="20">
         <v>7.42</v>
       </c>
-      <c r="O22" s="20">
+      <c r="P22" s="20">
         <v>26.6</v>
       </c>
-      <c r="P22" s="20">
+      <c r="Q22" s="20">
         <v>36.94</v>
       </c>
-      <c r="Q22" s="20">
+      <c r="R22" s="20">
         <v>4018</v>
       </c>
-      <c r="R22" s="7">
+      <c r="S22" s="7">
         <v>22.54</v>
       </c>
-      <c r="S22" s="7">
+      <c r="T22" s="7">
         <v>22.26</v>
       </c>
-      <c r="T22" s="7">
+      <c r="U22" s="7">
         <v>30.91</v>
       </c>
-      <c r="U22" s="7">
+      <c r="V22" s="7">
         <v>24.29</v>
       </c>
-      <c r="V22" s="26">
+      <c r="W22" s="26">
         <v>3362</v>
       </c>
-      <c r="W22" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X22" s="27">
+      <c r="X22" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="27">
         <v>22.54</v>
       </c>
-      <c r="Y22" s="27">
+      <c r="Z22" s="27">
         <v>6.61</v>
       </c>
-      <c r="Z22" s="27">
+      <c r="AA22" s="27">
         <v>24.69</v>
       </c>
-      <c r="AA22" s="27">
+      <c r="AB22" s="27">
         <v>37.82</v>
       </c>
-      <c r="AB22" s="27">
+      <c r="AC22" s="27">
         <v>30.88</v>
       </c>
-      <c r="AC22" s="27">
+      <c r="AD22" s="27">
         <v>3987</v>
       </c>
-      <c r="AD22" s="28">
+      <c r="AE22" s="28">
         <v>3307</v>
       </c>
-      <c r="AE22" s="27">
+      <c r="AF22" s="27">
         <v>6.88</v>
       </c>
-      <c r="AF22" s="29">
+      <c r="AG22" s="29">
         <v>24.62</v>
       </c>
-      <c r="AG22" s="29">
+      <c r="AH22" s="29">
         <v>37.71</v>
       </c>
-      <c r="AH22" s="29">
+      <c r="AI22" s="29">
         <v>30.79</v>
       </c>
-      <c r="AI22" s="29">
+      <c r="AJ22" s="29">
         <v>3975</v>
       </c>
-      <c r="AJ22" s="20">
+      <c r="AK22" s="20">
         <v>3307</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" s="24">
         <v>26</v>
       </c>
@@ -16606,7 +16645,7 @@
         <v>162006388</v>
       </c>
       <c r="J23" s="25">
-        <v>46061</v>
+        <v>46236</v>
       </c>
       <c r="K23" s="20" t="s">
         <v>1</v>
@@ -16617,77 +16656,80 @@
       <c r="M23" s="20">
         <v>3789.4</v>
       </c>
-      <c r="N23" s="20">
+      <c r="N23" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O23" s="20">
         <v>6.82</v>
       </c>
-      <c r="O23" s="20">
+      <c r="P23" s="20">
         <v>26.01</v>
       </c>
-      <c r="P23" s="20">
+      <c r="Q23" s="20">
         <v>39.380000000000003</v>
       </c>
-      <c r="Q23" s="20">
+      <c r="R23" s="20">
         <v>3893</v>
       </c>
-      <c r="R23" s="7">
+      <c r="S23" s="7">
         <v>21.4</v>
       </c>
-      <c r="S23" s="7">
+      <c r="T23" s="7">
         <v>21.94</v>
       </c>
-      <c r="T23" s="7">
+      <c r="U23" s="7">
         <v>33.22</v>
       </c>
-      <c r="U23" s="7">
+      <c r="V23" s="7">
         <v>23.44</v>
       </c>
-      <c r="V23" s="26">
+      <c r="W23" s="26">
         <v>3284</v>
       </c>
-      <c r="W23" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X23" s="27">
+      <c r="X23" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="27">
         <v>21.4</v>
       </c>
-      <c r="Y23" s="27">
+      <c r="Z23" s="27">
         <v>6.35</v>
       </c>
-      <c r="Z23" s="27">
+      <c r="AA23" s="27">
         <v>23.57</v>
       </c>
-      <c r="AA23" s="27">
+      <c r="AB23" s="27">
         <v>38.880000000000003</v>
       </c>
-      <c r="AB23" s="27">
+      <c r="AC23" s="27">
         <v>31.2</v>
       </c>
-      <c r="AC23" s="27">
+      <c r="AD23" s="27">
         <v>3854</v>
       </c>
-      <c r="AD23" s="28">
+      <c r="AE23" s="28">
         <v>3235</v>
       </c>
-      <c r="AE23" s="27">
+      <c r="AF23" s="27">
         <v>6.72</v>
       </c>
-      <c r="AF23" s="29">
+      <c r="AG23" s="29">
         <v>23.48</v>
       </c>
-      <c r="AG23" s="29">
+      <c r="AH23" s="29">
         <v>38.729999999999997</v>
       </c>
-      <c r="AH23" s="29">
+      <c r="AI23" s="29">
         <v>31.08</v>
       </c>
-      <c r="AI23" s="29">
+      <c r="AJ23" s="29">
         <v>3839</v>
       </c>
-      <c r="AJ23" s="20">
+      <c r="AK23" s="20">
         <v>3235</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" s="24">
         <v>27</v>
       </c>
@@ -16716,7 +16758,7 @@
         <v>162004371</v>
       </c>
       <c r="J24" s="25">
-        <v>46061</v>
+        <v>46236</v>
       </c>
       <c r="K24" s="20" t="s">
         <v>1</v>
@@ -16727,77 +16769,80 @@
       <c r="M24" s="20">
         <v>3665.8</v>
       </c>
-      <c r="N24" s="20">
+      <c r="N24" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O24" s="20">
         <v>7.11</v>
       </c>
-      <c r="O24" s="20">
+      <c r="P24" s="20">
         <v>26.58</v>
       </c>
-      <c r="P24" s="20">
+      <c r="Q24" s="20">
         <v>36.69</v>
       </c>
-      <c r="Q24" s="20">
+      <c r="R24" s="20">
         <v>4042</v>
       </c>
-      <c r="R24" s="7">
+      <c r="S24" s="7">
         <v>22.49</v>
       </c>
-      <c r="S24" s="7">
+      <c r="T24" s="7">
         <v>22.18</v>
       </c>
-      <c r="T24" s="7">
+      <c r="U24" s="7">
         <v>30.62</v>
       </c>
-      <c r="U24" s="7">
+      <c r="V24" s="7">
         <v>24.71</v>
       </c>
-      <c r="V24" s="26">
+      <c r="W24" s="26">
         <v>3373</v>
       </c>
-      <c r="W24" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X24" s="27">
+      <c r="X24" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="27">
         <v>22.49</v>
       </c>
-      <c r="Y24" s="27">
+      <c r="Z24" s="27">
         <v>6.45</v>
       </c>
-      <c r="Z24" s="27">
+      <c r="AA24" s="27">
         <v>24.7</v>
       </c>
-      <c r="AA24" s="27">
+      <c r="AB24" s="27">
         <v>36.979999999999997</v>
       </c>
-      <c r="AB24" s="27">
+      <c r="AC24" s="27">
         <v>31.87</v>
       </c>
-      <c r="AC24" s="27">
+      <c r="AD24" s="27">
         <v>4013</v>
       </c>
-      <c r="AD24" s="28">
+      <c r="AE24" s="28">
         <v>3325</v>
       </c>
-      <c r="AE24" s="27">
+      <c r="AF24" s="27">
         <v>6.75</v>
       </c>
-      <c r="AF24" s="29">
+      <c r="AG24" s="29">
         <v>24.62</v>
       </c>
-      <c r="AG24" s="29">
+      <c r="AH24" s="29">
         <v>36.86</v>
       </c>
-      <c r="AH24" s="29">
+      <c r="AI24" s="29">
         <v>31.77</v>
       </c>
-      <c r="AI24" s="29">
+      <c r="AJ24" s="29">
         <v>4000</v>
       </c>
-      <c r="AJ24" s="20">
+      <c r="AK24" s="20">
         <v>3325</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" s="24">
         <v>28</v>
       </c>
@@ -16826,7 +16871,7 @@
         <v>162011689</v>
       </c>
       <c r="J25" s="25">
-        <v>46089</v>
+        <v>46237</v>
       </c>
       <c r="K25" s="20" t="s">
         <v>1</v>
@@ -16837,77 +16882,80 @@
       <c r="M25" s="20">
         <v>3785.2</v>
       </c>
-      <c r="N25" s="20">
+      <c r="N25" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O25" s="20">
         <v>7.83</v>
       </c>
-      <c r="O25" s="20">
+      <c r="P25" s="20">
         <v>27.2</v>
       </c>
-      <c r="P25" s="20">
+      <c r="Q25" s="20">
         <v>31.24</v>
       </c>
-      <c r="Q25" s="20">
+      <c r="R25" s="20">
         <v>4516</v>
       </c>
-      <c r="R25" s="7">
+      <c r="S25" s="7">
         <v>23.62</v>
       </c>
-      <c r="S25" s="7">
+      <c r="T25" s="7">
         <v>22.54</v>
       </c>
-      <c r="T25" s="7">
+      <c r="U25" s="7">
         <v>25.89</v>
       </c>
-      <c r="U25" s="7">
+      <c r="V25" s="7">
         <v>27.95</v>
       </c>
-      <c r="V25" s="26">
+      <c r="W25" s="26">
         <v>3742</v>
       </c>
-      <c r="W25" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X25" s="27">
+      <c r="X25" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="27">
         <v>23.62</v>
       </c>
-      <c r="Y25" s="27">
+      <c r="Z25" s="27">
         <v>6.28</v>
       </c>
-      <c r="Z25" s="27">
+      <c r="AA25" s="27">
         <v>26.28</v>
       </c>
-      <c r="AA25" s="27">
+      <c r="AB25" s="27">
         <v>32.200000000000003</v>
       </c>
-      <c r="AB25" s="27">
+      <c r="AC25" s="27">
         <v>35.24</v>
       </c>
-      <c r="AC25" s="27">
+      <c r="AD25" s="27">
         <v>4520</v>
       </c>
-      <c r="AD25" s="28">
+      <c r="AE25" s="28">
         <v>3684</v>
       </c>
-      <c r="AE25" s="27">
+      <c r="AF25" s="27">
         <v>7.61</v>
       </c>
-      <c r="AF25" s="29">
+      <c r="AG25" s="29">
         <v>25.91</v>
       </c>
-      <c r="AG25" s="29">
+      <c r="AH25" s="29">
         <v>31.74</v>
       </c>
-      <c r="AH25" s="29">
+      <c r="AI25" s="29">
         <v>34.74</v>
       </c>
-      <c r="AI25" s="29">
+      <c r="AJ25" s="29">
         <v>4456</v>
       </c>
-      <c r="AJ25" s="20">
+      <c r="AK25" s="20">
         <v>3684</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" s="24">
         <v>29</v>
       </c>
@@ -16936,7 +16984,7 @@
         <v>162004372</v>
       </c>
       <c r="J26" s="25">
-        <v>46089</v>
+        <v>46237</v>
       </c>
       <c r="K26" s="20" t="s">
         <v>1</v>
@@ -16947,77 +16995,80 @@
       <c r="M26" s="20">
         <v>3923.8</v>
       </c>
-      <c r="N26" s="20">
+      <c r="N26" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O26" s="20">
         <v>7.6</v>
       </c>
-      <c r="O26" s="20">
+      <c r="P26" s="20">
         <v>25.48</v>
       </c>
-      <c r="P26" s="20">
+      <c r="Q26" s="20">
         <v>37.799999999999997</v>
       </c>
-      <c r="Q26" s="20">
+      <c r="R26" s="20">
         <v>3978</v>
       </c>
-      <c r="R26" s="7">
+      <c r="S26" s="7">
         <v>20.99</v>
       </c>
-      <c r="S26" s="7">
+      <c r="T26" s="7">
         <v>21.79</v>
       </c>
-      <c r="T26" s="7">
+      <c r="U26" s="7">
         <v>32.32</v>
       </c>
-      <c r="U26" s="7">
+      <c r="V26" s="7">
         <v>24.9</v>
       </c>
-      <c r="V26" s="26">
+      <c r="W26" s="26">
         <v>3402</v>
       </c>
-      <c r="W26" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X26" s="27">
+      <c r="X26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="27">
         <v>20.99</v>
       </c>
-      <c r="Y26" s="27">
+      <c r="Z26" s="27">
         <v>6.26</v>
       </c>
-      <c r="Z26" s="27">
+      <c r="AA26" s="27">
         <v>23.83</v>
       </c>
-      <c r="AA26" s="27">
+      <c r="AB26" s="27">
         <v>38.86</v>
       </c>
-      <c r="AB26" s="27">
+      <c r="AC26" s="27">
         <v>31.05</v>
       </c>
-      <c r="AC26" s="27">
+      <c r="AD26" s="27">
         <v>3970</v>
       </c>
-      <c r="AD26" s="28">
+      <c r="AE26" s="28">
         <v>3346</v>
       </c>
-      <c r="AE26" s="27">
+      <c r="AF26" s="27">
         <v>7.63</v>
       </c>
-      <c r="AF26" s="29">
+      <c r="AG26" s="29">
         <v>23.48</v>
       </c>
-      <c r="AG26" s="29">
+      <c r="AH26" s="29">
         <v>38.29</v>
       </c>
-      <c r="AH26" s="29">
+      <c r="AI26" s="29">
         <v>30.6</v>
       </c>
-      <c r="AI26" s="29">
+      <c r="AJ26" s="29">
         <v>3912</v>
       </c>
-      <c r="AJ26" s="20">
+      <c r="AK26" s="20">
         <v>3346</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" s="24">
         <v>30</v>
       </c>
@@ -17046,7 +17097,7 @@
         <v>162006389</v>
       </c>
       <c r="J27" s="25">
-        <v>46089</v>
+        <v>46237</v>
       </c>
       <c r="K27" s="20" t="s">
         <v>1</v>
@@ -17057,77 +17108,80 @@
       <c r="M27" s="20">
         <v>3988.4</v>
       </c>
-      <c r="N27" s="20">
+      <c r="N27" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O27" s="20">
         <v>7.23</v>
       </c>
-      <c r="O27" s="20">
+      <c r="P27" s="20">
         <v>27.1</v>
       </c>
-      <c r="P27" s="20">
+      <c r="Q27" s="20">
         <v>35.83</v>
       </c>
-      <c r="Q27" s="20">
+      <c r="R27" s="20">
         <v>4138</v>
       </c>
-      <c r="R27" s="7">
+      <c r="S27" s="7">
         <v>24.4</v>
       </c>
-      <c r="S27" s="7">
+      <c r="T27" s="7">
         <v>22.08</v>
       </c>
-      <c r="T27" s="7">
+      <c r="U27" s="7">
         <v>29.2</v>
       </c>
-      <c r="U27" s="7">
+      <c r="V27" s="7">
         <v>24.32</v>
       </c>
-      <c r="V27" s="26">
+      <c r="W27" s="26">
         <v>3372</v>
       </c>
-      <c r="W27" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X27" s="27">
+      <c r="X27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="27">
         <v>24.4</v>
       </c>
-      <c r="Y27" s="27">
+      <c r="Z27" s="27">
         <v>6.09</v>
       </c>
-      <c r="Z27" s="27">
+      <c r="AA27" s="27">
         <v>25.29</v>
       </c>
-      <c r="AA27" s="27">
+      <c r="AB27" s="27">
         <v>35.270000000000003</v>
       </c>
-      <c r="AB27" s="27">
+      <c r="AC27" s="27">
         <v>33.35</v>
       </c>
-      <c r="AC27" s="27">
+      <c r="AD27" s="27">
         <v>4160</v>
       </c>
-      <c r="AD27" s="28">
+      <c r="AE27" s="28">
         <v>3349</v>
       </c>
-      <c r="AE27" s="27">
+      <c r="AF27" s="27">
         <v>6.49</v>
       </c>
-      <c r="AF27" s="29">
+      <c r="AG27" s="29">
         <v>25.18</v>
       </c>
-      <c r="AG27" s="29">
+      <c r="AH27" s="29">
         <v>35.119999999999997</v>
       </c>
-      <c r="AH27" s="29">
+      <c r="AI27" s="29">
         <v>33.21</v>
       </c>
-      <c r="AI27" s="29">
+      <c r="AJ27" s="29">
         <v>4142</v>
       </c>
-      <c r="AJ27" s="20">
+      <c r="AK27" s="20">
         <v>3349</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" s="24">
         <v>31</v>
       </c>
@@ -17156,7 +17210,7 @@
         <v>162004373</v>
       </c>
       <c r="J28" s="25">
-        <v>46089</v>
+        <v>46237</v>
       </c>
       <c r="K28" s="20" t="s">
         <v>1</v>
@@ -17167,77 +17221,80 @@
       <c r="M28" s="20">
         <v>3362</v>
       </c>
-      <c r="N28" s="20">
+      <c r="N28" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O28" s="20">
         <v>7.05</v>
       </c>
-      <c r="O28" s="20">
+      <c r="P28" s="20">
         <v>25.8</v>
       </c>
-      <c r="P28" s="20">
+      <c r="Q28" s="20">
         <v>38.71</v>
       </c>
-      <c r="Q28" s="20">
+      <c r="R28" s="20">
         <v>3937</v>
       </c>
-      <c r="R28" s="7">
+      <c r="S28" s="7">
         <v>22.5</v>
       </c>
-      <c r="S28" s="7">
+      <c r="T28" s="7">
         <v>21.51</v>
       </c>
-      <c r="T28" s="7">
+      <c r="U28" s="7">
         <v>32.28</v>
       </c>
-      <c r="U28" s="7">
+      <c r="V28" s="7">
         <v>23.71</v>
       </c>
-      <c r="V28" s="26">
+      <c r="W28" s="26">
         <v>3283</v>
       </c>
-      <c r="W28" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X28" s="27">
+      <c r="X28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="27">
         <v>22.5</v>
       </c>
-      <c r="Y28" s="27">
+      <c r="Z28" s="27">
         <v>5.35</v>
       </c>
-      <c r="Z28" s="27">
+      <c r="AA28" s="27">
         <v>24.51</v>
       </c>
-      <c r="AA28" s="27">
+      <c r="AB28" s="27">
         <v>38.909999999999997</v>
       </c>
-      <c r="AB28" s="27">
+      <c r="AC28" s="27">
         <v>31.23</v>
       </c>
-      <c r="AC28" s="27">
+      <c r="AD28" s="27">
         <v>3927</v>
       </c>
-      <c r="AD28" s="28">
+      <c r="AE28" s="28">
         <v>3215</v>
       </c>
-      <c r="AE28" s="27">
+      <c r="AF28" s="27">
         <v>6.73</v>
       </c>
-      <c r="AF28" s="29">
+      <c r="AG28" s="29">
         <v>24.15</v>
       </c>
-      <c r="AG28" s="29">
+      <c r="AH28" s="29">
         <v>38.340000000000003</v>
       </c>
-      <c r="AH28" s="29">
+      <c r="AI28" s="29">
         <v>30.77</v>
       </c>
-      <c r="AI28" s="29">
+      <c r="AJ28" s="29">
         <v>3870</v>
       </c>
-      <c r="AJ28" s="20">
+      <c r="AK28" s="20">
         <v>3215</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" s="24">
         <v>32</v>
       </c>
@@ -17266,7 +17323,7 @@
         <v>162006393</v>
       </c>
       <c r="J29" s="25">
-        <v>46089</v>
+        <v>46237</v>
       </c>
       <c r="K29" s="20" t="s">
         <v>1</v>
@@ -17277,77 +17334,80 @@
       <c r="M29" s="20">
         <v>4099.8</v>
       </c>
-      <c r="N29" s="20">
+      <c r="N29" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O29" s="20">
         <v>6.16</v>
       </c>
-      <c r="O29" s="20">
+      <c r="P29" s="20">
         <v>23.87</v>
       </c>
-      <c r="P29" s="20">
+      <c r="Q29" s="20">
         <v>47.54</v>
       </c>
-      <c r="Q29" s="20">
+      <c r="R29" s="20">
         <v>3243</v>
       </c>
-      <c r="R29" s="7">
+      <c r="S29" s="7">
         <v>19.55</v>
       </c>
-      <c r="S29" s="7">
+      <c r="T29" s="7">
         <v>20.46</v>
       </c>
-      <c r="T29" s="7">
+      <c r="U29" s="7">
         <v>40.76</v>
       </c>
-      <c r="U29" s="7">
+      <c r="V29" s="7">
         <v>19.23</v>
       </c>
-      <c r="V29" s="26">
+      <c r="W29" s="26">
         <v>2780</v>
       </c>
-      <c r="W29" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X29" s="27">
+      <c r="X29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="27">
         <v>19.55</v>
       </c>
-      <c r="Y29" s="27">
+      <c r="Z29" s="27">
         <v>5.21</v>
       </c>
-      <c r="Z29" s="27">
+      <c r="AA29" s="27">
         <v>28.05</v>
       </c>
-      <c r="AA29" s="27">
+      <c r="AB29" s="27">
         <v>47.52</v>
       </c>
-      <c r="AB29" s="27">
+      <c r="AC29" s="27">
         <v>19.22</v>
       </c>
-      <c r="AC29" s="27">
+      <c r="AD29" s="27">
         <v>3298</v>
       </c>
-      <c r="AD29" s="28">
+      <c r="AE29" s="28">
         <v>2799</v>
       </c>
-      <c r="AE29" s="27">
+      <c r="AF29" s="27">
         <v>5.72</v>
       </c>
-      <c r="AF29" s="29">
+      <c r="AG29" s="29">
         <v>27.9</v>
       </c>
-      <c r="AG29" s="29">
+      <c r="AH29" s="29">
         <v>47.26</v>
       </c>
-      <c r="AH29" s="29">
+      <c r="AI29" s="29">
         <v>19.12</v>
       </c>
-      <c r="AI29" s="29">
+      <c r="AJ29" s="29">
         <v>3280</v>
       </c>
-      <c r="AJ29" s="20">
+      <c r="AK29" s="20">
         <v>2799</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" s="24">
         <v>35</v>
       </c>
@@ -17376,7 +17436,7 @@
         <v>162006396</v>
       </c>
       <c r="J30" s="25">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="K30" s="20" t="s">
         <v>1</v>
@@ -17387,37 +17447,37 @@
       <c r="M30" s="20">
         <v>3944.4</v>
       </c>
-      <c r="N30" s="20">
+      <c r="N30" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O30" s="20">
         <v>7.25</v>
       </c>
-      <c r="O30" s="20">
+      <c r="P30" s="20">
         <v>26.21</v>
       </c>
-      <c r="P30" s="20">
+      <c r="Q30" s="20">
         <v>37.97</v>
       </c>
-      <c r="Q30" s="20">
+      <c r="R30" s="20">
         <v>3926</v>
       </c>
-      <c r="R30" s="7">
+      <c r="S30" s="7">
         <v>24.31</v>
       </c>
-      <c r="S30" s="7">
+      <c r="T30" s="7">
         <v>21.39</v>
       </c>
-      <c r="T30" s="7">
+      <c r="U30" s="7">
         <v>30.99</v>
       </c>
-      <c r="U30" s="7">
+      <c r="V30" s="7">
         <v>23.31</v>
       </c>
-      <c r="V30" s="26">
+      <c r="W30" s="26">
         <v>3204</v>
       </c>
-      <c r="W30" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X30" s="27" t="s">
+      <c r="X30" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y30" s="27" t="s">
@@ -17435,13 +17495,13 @@
       <c r="AC30" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD30" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE30" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF30" s="29" t="s">
+      <c r="AD30" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE30" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG30" s="29" t="s">
@@ -17453,11 +17513,14 @@
       <c r="AI30" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ30" s="20" t="s">
+      <c r="AJ30" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK30" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" s="24">
         <v>36</v>
       </c>
@@ -17486,7 +17549,7 @@
         <v>162004374</v>
       </c>
       <c r="J31" s="25">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="K31" s="20" t="s">
         <v>1</v>
@@ -17497,37 +17560,37 @@
       <c r="M31" s="20">
         <v>3884.2</v>
       </c>
-      <c r="N31" s="20">
+      <c r="N31" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O31" s="20">
         <v>6.81</v>
       </c>
-      <c r="O31" s="20">
+      <c r="P31" s="20">
         <v>24.85</v>
       </c>
-      <c r="P31" s="20">
+      <c r="Q31" s="20">
         <v>41.69</v>
       </c>
-      <c r="Q31" s="20">
+      <c r="R31" s="20">
         <v>3664</v>
       </c>
-      <c r="R31" s="7">
+      <c r="S31" s="7">
         <v>23.18</v>
       </c>
-      <c r="S31" s="7">
+      <c r="T31" s="7">
         <v>20.48</v>
       </c>
-      <c r="T31" s="7">
+      <c r="U31" s="7">
         <v>34.369999999999997</v>
       </c>
-      <c r="U31" s="7">
+      <c r="V31" s="7">
         <v>21.97</v>
       </c>
-      <c r="V31" s="26">
+      <c r="W31" s="26">
         <v>3020</v>
       </c>
-      <c r="W31" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X31" s="27" t="s">
+      <c r="X31" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y31" s="27" t="s">
@@ -17545,13 +17608,13 @@
       <c r="AC31" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD31" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE31" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF31" s="29" t="s">
+      <c r="AD31" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE31" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG31" s="29" t="s">
@@ -17563,11 +17626,14 @@
       <c r="AI31" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ31" s="20" t="s">
+      <c r="AJ31" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK31" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" s="24">
         <v>38</v>
       </c>
@@ -17596,7 +17662,7 @@
         <v>162006397</v>
       </c>
       <c r="J32" s="25">
-        <v>46120</v>
+        <v>46238</v>
       </c>
       <c r="K32" s="20" t="s">
         <v>1</v>
@@ -17607,37 +17673,37 @@
       <c r="M32" s="20">
         <v>4022.2</v>
       </c>
-      <c r="N32" s="20">
+      <c r="N32" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O32" s="20">
         <v>6.78</v>
       </c>
-      <c r="O32" s="20">
+      <c r="P32" s="20">
         <v>24.05</v>
       </c>
-      <c r="P32" s="20">
+      <c r="Q32" s="20">
         <v>41.7</v>
       </c>
-      <c r="Q32" s="20">
+      <c r="R32" s="20">
         <v>3709</v>
       </c>
-      <c r="R32" s="7">
+      <c r="S32" s="7">
         <v>24.7</v>
       </c>
-      <c r="S32" s="7">
+      <c r="T32" s="7">
         <v>19.43</v>
       </c>
-      <c r="T32" s="7">
+      <c r="U32" s="7">
         <v>33.68</v>
       </c>
-      <c r="U32" s="7">
+      <c r="V32" s="7">
         <v>22.19</v>
       </c>
-      <c r="V32" s="26">
+      <c r="W32" s="26">
         <v>2996</v>
       </c>
-      <c r="W32" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X32" s="27" t="s">
+      <c r="X32" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y32" s="27" t="s">
@@ -17655,13 +17721,13 @@
       <c r="AC32" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD32" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE32" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF32" s="29" t="s">
+      <c r="AD32" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG32" s="29" t="s">
@@ -17673,11 +17739,14 @@
       <c r="AI32" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ32" s="20" t="s">
+      <c r="AJ32" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK32" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" s="24">
         <v>39</v>
       </c>
@@ -17706,7 +17775,7 @@
         <v>162006398</v>
       </c>
       <c r="J33" s="25">
-        <v>46150</v>
+        <v>46239</v>
       </c>
       <c r="K33" s="20" t="s">
         <v>1</v>
@@ -17717,37 +17786,37 @@
       <c r="M33" s="20">
         <v>3969</v>
       </c>
-      <c r="N33" s="20">
+      <c r="N33" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O33" s="20">
         <v>6.95</v>
       </c>
-      <c r="O33" s="20">
+      <c r="P33" s="20">
         <v>25.68</v>
       </c>
-      <c r="P33" s="20">
+      <c r="Q33" s="20">
         <v>38.46</v>
       </c>
-      <c r="Q33" s="20">
+      <c r="R33" s="20">
         <v>3958</v>
       </c>
-      <c r="R33" s="7">
+      <c r="S33" s="7">
         <v>25.26</v>
       </c>
-      <c r="S33" s="7">
+      <c r="T33" s="7">
         <v>20.63</v>
       </c>
-      <c r="T33" s="7">
+      <c r="U33" s="7">
         <v>30.89</v>
       </c>
-      <c r="U33" s="7">
+      <c r="V33" s="7">
         <v>23.22</v>
       </c>
-      <c r="V33" s="26">
+      <c r="W33" s="26">
         <v>3179</v>
       </c>
-      <c r="W33" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X33" s="27" t="s">
+      <c r="X33" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y33" s="27" t="s">
@@ -17765,13 +17834,13 @@
       <c r="AC33" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD33" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE33" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="29" t="s">
+      <c r="AD33" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG33" s="29" t="s">
@@ -17783,11 +17852,14 @@
       <c r="AI33" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ33" s="20" t="s">
+      <c r="AJ33" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK33" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" s="24">
         <v>40</v>
       </c>
@@ -17816,7 +17888,7 @@
         <v>162006399</v>
       </c>
       <c r="J34" s="25">
-        <v>46150</v>
+        <v>46239</v>
       </c>
       <c r="K34" s="20" t="s">
         <v>1</v>
@@ -17827,37 +17899,37 @@
       <c r="M34" s="20">
         <v>3800.4</v>
       </c>
-      <c r="N34" s="20">
+      <c r="N34" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O34" s="20">
         <v>7.29</v>
       </c>
-      <c r="O34" s="20">
+      <c r="P34" s="20">
         <v>25.32</v>
       </c>
-      <c r="P34" s="20">
+      <c r="Q34" s="20">
         <v>36.32</v>
       </c>
-      <c r="Q34" s="20">
+      <c r="R34" s="20">
         <v>4192</v>
       </c>
-      <c r="R34" s="7">
+      <c r="S34" s="7">
         <v>24.58</v>
       </c>
-      <c r="S34" s="7">
+      <c r="T34" s="7">
         <v>20.6</v>
       </c>
-      <c r="T34" s="7">
+      <c r="U34" s="7">
         <v>29.55</v>
       </c>
-      <c r="U34" s="7">
+      <c r="V34" s="7">
         <v>25.27</v>
       </c>
-      <c r="V34" s="26">
+      <c r="W34" s="26">
         <v>3410</v>
       </c>
-      <c r="W34" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X34" s="27" t="s">
+      <c r="X34" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y34" s="27" t="s">
@@ -17875,13 +17947,13 @@
       <c r="AC34" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD34" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE34" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="29" t="s">
+      <c r="AD34" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG34" s="29" t="s">
@@ -17893,11 +17965,14 @@
       <c r="AI34" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ34" s="20" t="s">
+      <c r="AJ34" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK34" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" s="24">
         <v>41</v>
       </c>
@@ -17926,7 +18001,7 @@
         <v>162004375</v>
       </c>
       <c r="J35" s="25">
-        <v>46150</v>
+        <v>46239</v>
       </c>
       <c r="K35" s="20" t="s">
         <v>1</v>
@@ -17937,37 +18012,37 @@
       <c r="M35" s="20">
         <v>3585.4</v>
       </c>
-      <c r="N35" s="20">
+      <c r="N35" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O35" s="20">
         <v>7.72</v>
       </c>
-      <c r="O35" s="20">
+      <c r="P35" s="20">
         <v>26</v>
       </c>
-      <c r="P35" s="20">
+      <c r="Q35" s="20">
         <v>36.57</v>
       </c>
-      <c r="Q35" s="20">
+      <c r="R35" s="20">
         <v>4048</v>
       </c>
-      <c r="R35" s="7">
+      <c r="S35" s="7">
         <v>24.36</v>
       </c>
-      <c r="S35" s="7">
+      <c r="T35" s="7">
         <v>21.31</v>
       </c>
-      <c r="T35" s="7">
+      <c r="U35" s="7">
         <v>29.98</v>
       </c>
-      <c r="U35" s="7">
+      <c r="V35" s="7">
         <v>24.35</v>
       </c>
-      <c r="V35" s="26">
+      <c r="W35" s="26">
         <v>3318</v>
       </c>
-      <c r="W35" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X35" s="27" t="s">
+      <c r="X35" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y35" s="27" t="s">
@@ -17985,13 +18060,13 @@
       <c r="AC35" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD35" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE35" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF35" s="29" t="s">
+      <c r="AD35" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG35" s="29" t="s">
@@ -18003,11 +18078,14 @@
       <c r="AI35" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ35" s="20" t="s">
+      <c r="AJ35" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK35" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" s="24">
         <v>42</v>
       </c>
@@ -18036,7 +18114,7 @@
         <v>142000356</v>
       </c>
       <c r="J36" s="25">
-        <v>46181</v>
+        <v>46240</v>
       </c>
       <c r="K36" s="20" t="s">
         <v>1</v>
@@ -18047,37 +18125,37 @@
       <c r="M36" s="20">
         <v>3788.6</v>
       </c>
-      <c r="N36" s="20">
+      <c r="N36" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O36" s="20">
         <v>7.11</v>
       </c>
-      <c r="O36" s="20">
+      <c r="P36" s="20">
         <v>23.89</v>
       </c>
-      <c r="P36" s="20">
+      <c r="Q36" s="20">
         <v>41.71</v>
       </c>
-      <c r="Q36" s="20">
+      <c r="R36" s="20">
         <v>3782</v>
       </c>
-      <c r="R36" s="7">
+      <c r="S36" s="7">
         <v>23.01</v>
       </c>
-      <c r="S36" s="7">
+      <c r="T36" s="7">
         <v>19.8</v>
       </c>
-      <c r="T36" s="7">
+      <c r="U36" s="7">
         <v>34.57</v>
       </c>
-      <c r="U36" s="7">
+      <c r="V36" s="7">
         <v>22.62</v>
       </c>
-      <c r="V36" s="26">
+      <c r="W36" s="26">
         <v>3135</v>
       </c>
-      <c r="W36" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X36" s="27" t="s">
+      <c r="X36" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y36" s="27" t="s">
@@ -18095,13 +18173,13 @@
       <c r="AC36" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD36" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE36" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF36" s="29" t="s">
+      <c r="AD36" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE36" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG36" s="29" t="s">
@@ -18113,11 +18191,14 @@
       <c r="AI36" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ36" s="20" t="s">
+      <c r="AJ36" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK36" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A37" s="24">
         <v>43</v>
       </c>
@@ -18146,7 +18227,7 @@
         <v>162011692</v>
       </c>
       <c r="J37" s="25">
-        <v>46150</v>
+        <v>46239</v>
       </c>
       <c r="K37" s="20" t="s">
         <v>1</v>
@@ -18157,37 +18238,37 @@
       <c r="M37" s="20">
         <v>4142</v>
       </c>
-      <c r="N37" s="20">
+      <c r="N37" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O37" s="20">
         <v>8.06</v>
       </c>
-      <c r="O37" s="20">
+      <c r="P37" s="20">
         <v>26.13</v>
       </c>
-      <c r="P37" s="20">
+      <c r="Q37" s="20">
         <v>31.66</v>
       </c>
-      <c r="Q37" s="20">
+      <c r="R37" s="20">
         <v>4461</v>
       </c>
-      <c r="R37" s="7">
+      <c r="S37" s="7">
         <v>23.85</v>
       </c>
-      <c r="S37" s="7">
+      <c r="T37" s="7">
         <v>21.64</v>
       </c>
-      <c r="T37" s="7">
+      <c r="U37" s="7">
         <v>26.22</v>
       </c>
-      <c r="U37" s="7">
+      <c r="V37" s="7">
         <v>28.29</v>
       </c>
-      <c r="V37" s="26">
+      <c r="W37" s="26">
         <v>3695</v>
       </c>
-      <c r="W37" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X37" s="27" t="s">
+      <c r="X37" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y37" s="27" t="s">
@@ -18205,13 +18286,13 @@
       <c r="AC37" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD37" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE37" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF37" s="29" t="s">
+      <c r="AD37" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE37" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG37" s="29" t="s">
@@ -18223,11 +18304,14 @@
       <c r="AI37" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ37" s="20" t="s">
+      <c r="AJ37" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK37" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A38" s="24">
         <v>44</v>
       </c>
@@ -18256,7 +18340,7 @@
         <v>162004376</v>
       </c>
       <c r="J38" s="25">
-        <v>46181</v>
+        <v>46240</v>
       </c>
       <c r="K38" s="20" t="s">
         <v>1</v>
@@ -18267,37 +18351,37 @@
       <c r="M38" s="20">
         <v>3862.8</v>
       </c>
-      <c r="N38" s="20">
+      <c r="N38" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O38" s="20">
         <v>8.16</v>
       </c>
-      <c r="O38" s="20">
+      <c r="P38" s="20">
         <v>28.07</v>
       </c>
-      <c r="P38" s="20">
+      <c r="Q38" s="20">
         <v>30.9</v>
       </c>
-      <c r="Q38" s="20">
+      <c r="R38" s="20">
         <v>4542</v>
       </c>
-      <c r="R38" s="7">
+      <c r="S38" s="7">
         <v>23.89</v>
       </c>
-      <c r="S38" s="7">
+      <c r="T38" s="7">
         <v>23.26</v>
       </c>
-      <c r="T38" s="7">
+      <c r="U38" s="7">
         <v>25.61</v>
       </c>
-      <c r="U38" s="7">
+      <c r="V38" s="7">
         <v>27.24</v>
       </c>
-      <c r="V38" s="26">
+      <c r="W38" s="26">
         <v>3764</v>
       </c>
-      <c r="W38" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X38" s="27" t="s">
+      <c r="X38" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y38" s="27" t="s">
@@ -18315,13 +18399,13 @@
       <c r="AC38" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD38" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE38" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF38" s="29" t="s">
+      <c r="AD38" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG38" s="29" t="s">
@@ -18333,11 +18417,14 @@
       <c r="AI38" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ38" s="20" t="s">
+      <c r="AJ38" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK38" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A39" s="24">
         <v>45</v>
       </c>
@@ -18366,7 +18453,7 @@
         <v>162011693</v>
       </c>
       <c r="J39" s="25">
-        <v>46181</v>
+        <v>46240</v>
       </c>
       <c r="K39" s="20" t="s">
         <v>1</v>
@@ -18377,37 +18464,37 @@
       <c r="M39" s="20">
         <v>3936</v>
       </c>
-      <c r="N39" s="20">
+      <c r="N39" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O39" s="20">
         <v>7.52</v>
       </c>
-      <c r="O39" s="20">
+      <c r="P39" s="20">
         <v>24.73</v>
       </c>
-      <c r="P39" s="20">
+      <c r="Q39" s="20">
         <v>37.11</v>
       </c>
-      <c r="Q39" s="20">
+      <c r="R39" s="20">
         <v>4060</v>
       </c>
-      <c r="R39" s="7">
+      <c r="S39" s="7">
         <v>22.25</v>
       </c>
-      <c r="S39" s="7">
+      <c r="T39" s="7">
         <v>20.79</v>
       </c>
-      <c r="T39" s="7">
+      <c r="U39" s="7">
         <v>31.2</v>
       </c>
-      <c r="U39" s="7">
+      <c r="V39" s="7">
         <v>25.76</v>
       </c>
-      <c r="V39" s="26">
+      <c r="W39" s="26">
         <v>3413</v>
       </c>
-      <c r="W39" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X39" s="27" t="s">
+      <c r="X39" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y39" s="27" t="s">
@@ -18425,13 +18512,13 @@
       <c r="AC39" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD39" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE39" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF39" s="29" t="s">
+      <c r="AD39" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE39" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG39" s="29" t="s">
@@ -18443,11 +18530,14 @@
       <c r="AI39" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ39" s="20" t="s">
+      <c r="AJ39" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK39" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A40" s="24">
         <v>46</v>
       </c>
@@ -18476,7 +18566,7 @@
         <v>162006402</v>
       </c>
       <c r="J40" s="25">
-        <v>46181</v>
+        <v>46240</v>
       </c>
       <c r="K40" s="20" t="s">
         <v>1</v>
@@ -18487,37 +18577,37 @@
       <c r="M40" s="20">
         <v>3668.8</v>
       </c>
-      <c r="N40" s="20">
+      <c r="N40" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O40" s="20">
         <v>6.77</v>
       </c>
-      <c r="O40" s="20">
+      <c r="P40" s="20">
         <v>26.24</v>
       </c>
-      <c r="P40" s="20">
+      <c r="Q40" s="20">
         <v>37.58</v>
       </c>
-      <c r="Q40" s="20">
+      <c r="R40" s="20">
         <v>4001</v>
       </c>
-      <c r="R40" s="7">
+      <c r="S40" s="7">
         <v>20.81</v>
       </c>
-      <c r="S40" s="7">
+      <c r="T40" s="7">
         <v>22.29</v>
       </c>
-      <c r="T40" s="7">
+      <c r="U40" s="7">
         <v>31.92</v>
       </c>
-      <c r="U40" s="7">
+      <c r="V40" s="7">
         <v>24.98</v>
       </c>
-      <c r="V40" s="26">
+      <c r="W40" s="26">
         <v>3398</v>
       </c>
-      <c r="W40" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X40" s="27" t="s">
+      <c r="X40" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y40" s="27" t="s">
@@ -18535,13 +18625,13 @@
       <c r="AC40" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD40" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE40" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF40" s="29" t="s">
+      <c r="AD40" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE40" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF40" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG40" s="29" t="s">
@@ -18553,11 +18643,14 @@
       <c r="AI40" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ40" s="20" t="s">
+      <c r="AJ40" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK40" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A41" s="24">
         <v>47</v>
       </c>
@@ -18586,7 +18679,7 @@
         <v>162004377</v>
       </c>
       <c r="J41" s="25">
-        <v>46211</v>
+        <v>46241</v>
       </c>
       <c r="K41" s="20" t="s">
         <v>1</v>
@@ -18597,37 +18690,37 @@
       <c r="M41" s="20">
         <v>3548.4</v>
       </c>
-      <c r="N41" s="20">
+      <c r="N41" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O41" s="20">
         <v>7.28</v>
       </c>
-      <c r="O41" s="20">
+      <c r="P41" s="20">
         <v>24.71</v>
       </c>
-      <c r="P41" s="20">
+      <c r="Q41" s="20">
         <v>38.630000000000003</v>
       </c>
-      <c r="Q41" s="20">
+      <c r="R41" s="20">
         <v>3950</v>
       </c>
-      <c r="R41" s="7">
+      <c r="S41" s="7">
         <v>19.989999999999998</v>
       </c>
-      <c r="S41" s="7">
+      <c r="T41" s="7">
         <v>21.32</v>
       </c>
-      <c r="T41" s="7">
+      <c r="U41" s="7">
         <v>33.33</v>
       </c>
-      <c r="U41" s="7">
+      <c r="V41" s="7">
         <v>25.36</v>
       </c>
-      <c r="V41" s="26">
+      <c r="W41" s="26">
         <v>3409</v>
       </c>
-      <c r="W41" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X41" s="27" t="s">
+      <c r="X41" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y41" s="27" t="s">
@@ -18645,13 +18738,13 @@
       <c r="AC41" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD41" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE41" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF41" s="29" t="s">
+      <c r="AD41" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE41" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG41" s="29" t="s">
@@ -18663,11 +18756,14 @@
       <c r="AI41" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ41" s="20" t="s">
+      <c r="AJ41" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK41" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A42" s="24">
         <v>48</v>
       </c>
@@ -18696,7 +18792,7 @@
         <v>162011695</v>
       </c>
       <c r="J42" s="25">
-        <v>46211</v>
+        <v>46241</v>
       </c>
       <c r="K42" s="20" t="s">
         <v>1</v>
@@ -18707,37 +18803,37 @@
       <c r="M42" s="20">
         <v>3763</v>
       </c>
-      <c r="N42" s="20">
+      <c r="N42" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O42" s="20">
         <v>7.98</v>
       </c>
-      <c r="O42" s="20">
+      <c r="P42" s="20">
         <v>28.13</v>
       </c>
-      <c r="P42" s="20">
+      <c r="Q42" s="20">
         <v>30.19</v>
       </c>
-      <c r="Q42" s="20">
+      <c r="R42" s="20">
         <v>4607</v>
       </c>
-      <c r="R42" s="7">
+      <c r="S42" s="7">
         <v>22.61</v>
       </c>
-      <c r="S42" s="7">
+      <c r="T42" s="7">
         <v>23.66</v>
       </c>
-      <c r="T42" s="7">
+      <c r="U42" s="7">
         <v>25.39</v>
       </c>
-      <c r="U42" s="7">
+      <c r="V42" s="7">
         <v>28.34</v>
       </c>
-      <c r="V42" s="26">
+      <c r="W42" s="26">
         <v>3875</v>
       </c>
-      <c r="W42" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X42" s="27" t="s">
+      <c r="X42" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y42" s="27" t="s">
@@ -18755,13 +18851,13 @@
       <c r="AC42" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD42" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE42" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF42" s="29" t="s">
+      <c r="AD42" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG42" s="29" t="s">
@@ -18773,11 +18869,14 @@
       <c r="AI42" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ42" s="20" t="s">
+      <c r="AJ42" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK42" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A43" s="24">
         <v>49</v>
       </c>
@@ -18806,7 +18905,7 @@
         <v>162004378</v>
       </c>
       <c r="J43" s="25">
-        <v>46211</v>
+        <v>46241</v>
       </c>
       <c r="K43" s="20" t="s">
         <v>1</v>
@@ -18817,37 +18916,37 @@
       <c r="M43" s="20">
         <v>3772</v>
       </c>
-      <c r="N43" s="20">
+      <c r="N43" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O43" s="20">
         <v>7.56</v>
       </c>
-      <c r="O43" s="20">
+      <c r="P43" s="20">
         <v>26.11</v>
       </c>
-      <c r="P43" s="20">
+      <c r="Q43" s="20">
         <v>37.56</v>
       </c>
-      <c r="Q43" s="20">
+      <c r="R43" s="20">
         <v>3963</v>
       </c>
-      <c r="R43" s="7">
+      <c r="S43" s="7">
         <v>21.03</v>
       </c>
-      <c r="S43" s="7">
+      <c r="T43" s="7">
         <v>22.31</v>
       </c>
-      <c r="T43" s="7">
+      <c r="U43" s="7">
         <v>32.090000000000003</v>
       </c>
-      <c r="U43" s="7">
+      <c r="V43" s="7">
         <v>24.57</v>
       </c>
-      <c r="V43" s="26">
+      <c r="W43" s="26">
         <v>3386</v>
       </c>
-      <c r="W43" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X43" s="27" t="s">
+      <c r="X43" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y43" s="27" t="s">
@@ -18865,13 +18964,13 @@
       <c r="AC43" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD43" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE43" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF43" s="29" t="s">
+      <c r="AD43" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE43" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF43" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG43" s="29" t="s">
@@ -18883,11 +18982,14 @@
       <c r="AI43" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ43" s="20" t="s">
+      <c r="AJ43" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK43" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A44" s="24">
         <v>50</v>
       </c>
@@ -18916,7 +19018,7 @@
         <v>162006406</v>
       </c>
       <c r="J44" s="25">
-        <v>46211</v>
+        <v>46241</v>
       </c>
       <c r="K44" s="20" t="s">
         <v>1</v>
@@ -18927,37 +19029,37 @@
       <c r="M44" s="20">
         <v>3857.6</v>
       </c>
-      <c r="N44" s="20">
+      <c r="N44" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O44" s="20">
         <v>6.63</v>
       </c>
-      <c r="O44" s="20">
+      <c r="P44" s="20">
         <v>23.54</v>
       </c>
-      <c r="P44" s="20">
+      <c r="Q44" s="20">
         <v>43.69</v>
       </c>
-      <c r="Q44" s="20">
+      <c r="R44" s="20">
         <v>3549</v>
       </c>
-      <c r="R44" s="7">
+      <c r="S44" s="7">
         <v>19.22</v>
       </c>
-      <c r="S44" s="7">
+      <c r="T44" s="7">
         <v>20.37</v>
       </c>
-      <c r="T44" s="7">
+      <c r="U44" s="7">
         <v>37.799999999999997</v>
       </c>
-      <c r="U44" s="7">
+      <c r="V44" s="7">
         <v>22.61</v>
       </c>
-      <c r="V44" s="26">
+      <c r="W44" s="26">
         <v>3070</v>
       </c>
-      <c r="W44" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X44" s="27" t="s">
+      <c r="X44" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y44" s="27" t="s">
@@ -18975,13 +19077,13 @@
       <c r="AC44" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD44" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE44" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF44" s="29" t="s">
+      <c r="AD44" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE44" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF44" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG44" s="29" t="s">
@@ -18993,11 +19095,14 @@
       <c r="AI44" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ44" s="20" t="s">
+      <c r="AJ44" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK44" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A45" s="24">
         <v>52</v>
       </c>
@@ -19037,37 +19142,37 @@
       <c r="M45" s="20">
         <v>3907.2</v>
       </c>
-      <c r="N45" s="20">
+      <c r="N45" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O45" s="20">
         <v>6.13</v>
       </c>
-      <c r="O45" s="20">
+      <c r="P45" s="20">
         <v>22.72</v>
       </c>
-      <c r="P45" s="20">
+      <c r="Q45" s="20">
         <v>48.57</v>
       </c>
-      <c r="Q45" s="20">
+      <c r="R45" s="20">
         <v>3173</v>
       </c>
-      <c r="R45" s="7">
+      <c r="S45" s="7">
         <v>18.809999999999999</v>
       </c>
-      <c r="S45" s="7">
+      <c r="T45" s="7">
         <v>19.649999999999999</v>
       </c>
-      <c r="T45" s="7">
+      <c r="U45" s="7">
         <v>42.01</v>
       </c>
-      <c r="U45" s="7">
+      <c r="V45" s="7">
         <v>19.53</v>
       </c>
-      <c r="V45" s="26">
+      <c r="W45" s="26">
         <v>2744</v>
       </c>
-      <c r="W45" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X45" s="27" t="s">
+      <c r="X45" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y45" s="27" t="s">
@@ -19085,13 +19190,13 @@
       <c r="AC45" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD45" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE45" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF45" s="29" t="s">
+      <c r="AD45" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE45" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF45" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG45" s="29" t="s">
@@ -19103,11 +19208,14 @@
       <c r="AI45" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ45" s="20" t="s">
+      <c r="AJ45" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK45" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A46" s="24">
         <v>53</v>
       </c>
@@ -19147,37 +19255,37 @@
       <c r="M46" s="20">
         <v>3735.4</v>
       </c>
-      <c r="N46" s="20">
+      <c r="N46" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O46" s="20">
         <v>7.13</v>
       </c>
-      <c r="O46" s="20">
+      <c r="P46" s="20">
         <v>24.94</v>
       </c>
-      <c r="P46" s="20">
+      <c r="Q46" s="20">
         <v>39.51</v>
       </c>
-      <c r="Q46" s="20">
+      <c r="R46" s="20">
         <v>3818</v>
       </c>
-      <c r="R46" s="7">
+      <c r="S46" s="7">
         <v>19.420000000000002</v>
       </c>
-      <c r="S46" s="7">
+      <c r="T46" s="7">
         <v>21.64</v>
       </c>
-      <c r="T46" s="7">
+      <c r="U46" s="7">
         <v>34.28</v>
       </c>
-      <c r="U46" s="7">
+      <c r="V46" s="7">
         <v>24.66</v>
       </c>
-      <c r="V46" s="26">
+      <c r="W46" s="26">
         <v>3313</v>
       </c>
-      <c r="W46" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X46" s="27" t="s">
+      <c r="X46" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y46" s="27" t="s">
@@ -19195,13 +19303,13 @@
       <c r="AC46" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD46" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE46" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF46" s="29" t="s">
+      <c r="AD46" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE46" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF46" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG46" s="29" t="s">
@@ -19213,11 +19321,14 @@
       <c r="AI46" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ46" s="20" t="s">
+      <c r="AJ46" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK46" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A47" s="24">
         <v>54</v>
       </c>
@@ -19257,37 +19368,37 @@
       <c r="M47" s="20">
         <v>3734.4</v>
       </c>
-      <c r="N47" s="20">
+      <c r="N47" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O47" s="20">
         <v>7.24</v>
       </c>
-      <c r="O47" s="20">
+      <c r="P47" s="20">
         <v>23.34</v>
       </c>
-      <c r="P47" s="20">
+      <c r="Q47" s="20">
         <v>44.4</v>
       </c>
-      <c r="Q47" s="20">
+      <c r="R47" s="20">
         <v>3431</v>
       </c>
-      <c r="R47" s="7">
+      <c r="S47" s="7">
         <v>18.579999999999998</v>
       </c>
-      <c r="S47" s="7">
+      <c r="T47" s="7">
         <v>20.49</v>
       </c>
-      <c r="T47" s="7">
+      <c r="U47" s="7">
         <v>38.97</v>
       </c>
-      <c r="U47" s="7">
+      <c r="V47" s="7">
         <v>21.96</v>
       </c>
-      <c r="V47" s="26">
+      <c r="W47" s="26">
         <v>3012</v>
       </c>
-      <c r="W47" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X47" s="27" t="s">
+      <c r="X47" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y47" s="27" t="s">
@@ -19305,13 +19416,13 @@
       <c r="AC47" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD47" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE47" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF47" s="29" t="s">
+      <c r="AD47" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF47" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG47" s="29" t="s">
@@ -19323,11 +19434,14 @@
       <c r="AI47" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ47" s="20" t="s">
+      <c r="AJ47" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK47" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A48" s="24">
         <v>55</v>
       </c>
@@ -19367,37 +19481,37 @@
       <c r="M48" s="20">
         <v>3892</v>
       </c>
-      <c r="N48" s="20">
+      <c r="N48" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O48" s="20">
         <v>7.28</v>
       </c>
-      <c r="O48" s="20">
+      <c r="P48" s="20">
         <v>24.37</v>
       </c>
-      <c r="P48" s="20">
+      <c r="Q48" s="20">
         <v>40.380000000000003</v>
       </c>
-      <c r="Q48" s="20">
+      <c r="R48" s="20">
         <v>3776</v>
       </c>
-      <c r="R48" s="7">
+      <c r="S48" s="7">
         <v>20.99</v>
       </c>
-      <c r="S48" s="7">
+      <c r="T48" s="7">
         <v>20.77</v>
       </c>
-      <c r="T48" s="7">
+      <c r="U48" s="7">
         <v>34.409999999999997</v>
       </c>
-      <c r="U48" s="7">
+      <c r="V48" s="7">
         <v>23.83</v>
       </c>
-      <c r="V48" s="26">
+      <c r="W48" s="26">
         <v>3218</v>
       </c>
-      <c r="W48" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X48" s="27" t="s">
+      <c r="X48" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y48" s="27" t="s">
@@ -19415,13 +19529,13 @@
       <c r="AC48" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD48" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE48" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF48" s="29" t="s">
+      <c r="AD48" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF48" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG48" s="29" t="s">
@@ -19433,11 +19547,14 @@
       <c r="AI48" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ48" s="20" t="s">
+      <c r="AJ48" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK48" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A49" s="24">
         <v>57</v>
       </c>
@@ -19477,37 +19594,37 @@
       <c r="M49" s="20">
         <v>3823.6</v>
       </c>
-      <c r="N49" s="20">
+      <c r="N49" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O49" s="20">
         <v>6.28</v>
       </c>
-      <c r="O49" s="20">
+      <c r="P49" s="20">
         <v>22.89</v>
       </c>
-      <c r="P49" s="20">
+      <c r="Q49" s="20">
         <v>46.02</v>
       </c>
-      <c r="Q49" s="20">
+      <c r="R49" s="20">
         <v>3447</v>
       </c>
-      <c r="R49" s="7">
+      <c r="S49" s="7">
         <v>19.62</v>
       </c>
-      <c r="S49" s="7">
+      <c r="T49" s="7">
         <v>19.63</v>
       </c>
-      <c r="T49" s="7">
+      <c r="U49" s="7">
         <v>39.47</v>
       </c>
-      <c r="U49" s="7">
+      <c r="V49" s="7">
         <v>21.28</v>
       </c>
-      <c r="V49" s="26">
+      <c r="W49" s="26">
         <v>2956</v>
       </c>
-      <c r="W49" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X49" s="27" t="s">
+      <c r="X49" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y49" s="27" t="s">
@@ -19525,13 +19642,13 @@
       <c r="AC49" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD49" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE49" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF49" s="29" t="s">
+      <c r="AD49" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE49" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF49" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG49" s="29" t="s">
@@ -19543,11 +19660,14 @@
       <c r="AI49" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ49" s="20" t="s">
+      <c r="AJ49" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK49" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A50" s="24">
         <v>59</v>
       </c>
@@ -19576,7 +19696,7 @@
         <v>162004383</v>
       </c>
       <c r="J50" s="25">
-        <v>46273</v>
+        <v>46243</v>
       </c>
       <c r="K50" s="20" t="s">
         <v>1</v>
@@ -19587,37 +19707,37 @@
       <c r="M50" s="20">
         <v>3769.4</v>
       </c>
-      <c r="N50" s="20">
+      <c r="N50" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O50" s="20">
         <v>7.08</v>
       </c>
-      <c r="O50" s="20">
+      <c r="P50" s="20">
         <v>24.69</v>
       </c>
-      <c r="P50" s="20">
+      <c r="Q50" s="20">
         <v>40.450000000000003</v>
       </c>
-      <c r="Q50" s="20">
+      <c r="R50" s="20">
         <v>3764</v>
       </c>
-      <c r="R50" s="7">
+      <c r="S50" s="7">
         <v>18.940000000000001</v>
       </c>
-      <c r="S50" s="7">
+      <c r="T50" s="7">
         <v>21.54</v>
       </c>
-      <c r="T50" s="7">
+      <c r="U50" s="7">
         <v>35.29</v>
       </c>
-      <c r="U50" s="7">
+      <c r="V50" s="7">
         <v>24.23</v>
       </c>
-      <c r="V50" s="26">
+      <c r="W50" s="26">
         <v>3284</v>
       </c>
-      <c r="W50" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X50" s="27" t="s">
+      <c r="X50" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y50" s="27" t="s">
@@ -19635,13 +19755,13 @@
       <c r="AC50" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD50" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE50" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF50" s="29" t="s">
+      <c r="AD50" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE50" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF50" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG50" s="29" t="s">
@@ -19653,11 +19773,14 @@
       <c r="AI50" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ50" s="20" t="s">
+      <c r="AJ50" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK50" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A51" s="24">
         <v>60</v>
       </c>
@@ -19697,37 +19820,37 @@
       <c r="M51" s="20">
         <v>3955.2</v>
       </c>
-      <c r="N51" s="20">
+      <c r="N51" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O51" s="20">
         <v>6.94</v>
       </c>
-      <c r="O51" s="20">
+      <c r="P51" s="20">
         <v>24.91</v>
       </c>
-      <c r="P51" s="20">
+      <c r="Q51" s="20">
         <v>39.61</v>
       </c>
-      <c r="Q51" s="20">
+      <c r="R51" s="20">
         <v>3895</v>
       </c>
-      <c r="R51" s="7">
+      <c r="S51" s="7">
         <v>21.27</v>
       </c>
-      <c r="S51" s="7">
+      <c r="T51" s="7">
         <v>21.07</v>
       </c>
-      <c r="T51" s="7">
+      <c r="U51" s="7">
         <v>33.51</v>
       </c>
-      <c r="U51" s="7">
+      <c r="V51" s="7">
         <v>24.15</v>
       </c>
-      <c r="V51" s="26">
+      <c r="W51" s="26">
         <v>3295</v>
       </c>
-      <c r="W51" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X51" s="27" t="s">
+      <c r="X51" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y51" s="27" t="s">
@@ -19745,13 +19868,13 @@
       <c r="AC51" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE51" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF51" s="29" t="s">
+      <c r="AD51" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE51" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF51" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG51" s="29" t="s">
@@ -19763,11 +19886,14 @@
       <c r="AI51" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ51" s="20" t="s">
+      <c r="AJ51" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK51" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A52" s="24">
         <v>61</v>
       </c>
@@ -19796,7 +19922,7 @@
         <v>162011699</v>
       </c>
       <c r="J52" s="25">
-        <v>46273</v>
+        <v>46243</v>
       </c>
       <c r="K52" s="20" t="s">
         <v>1</v>
@@ -19807,37 +19933,37 @@
       <c r="M52" s="20">
         <v>3541.8</v>
       </c>
-      <c r="N52" s="20">
+      <c r="N52" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O52" s="20">
         <v>7.6</v>
       </c>
-      <c r="O52" s="20">
+      <c r="P52" s="20">
         <v>24.52</v>
       </c>
-      <c r="P52" s="20">
+      <c r="Q52" s="20">
         <v>37.270000000000003</v>
       </c>
-      <c r="Q52" s="20">
+      <c r="R52" s="20">
         <v>4168</v>
       </c>
-      <c r="R52" s="7">
+      <c r="S52" s="7">
         <v>23.91</v>
       </c>
-      <c r="S52" s="7">
+      <c r="T52" s="7">
         <v>20.190000000000001</v>
       </c>
-      <c r="T52" s="7">
+      <c r="U52" s="7">
         <v>30.69</v>
       </c>
-      <c r="U52" s="7">
+      <c r="V52" s="7">
         <v>25.21</v>
       </c>
-      <c r="V52" s="26">
+      <c r="W52" s="26">
         <v>3432</v>
       </c>
-      <c r="W52" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X52" s="27" t="s">
+      <c r="X52" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y52" s="27" t="s">
@@ -19855,13 +19981,13 @@
       <c r="AC52" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD52" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE52" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF52" s="29" t="s">
+      <c r="AD52" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE52" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF52" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG52" s="29" t="s">
@@ -19873,11 +19999,14 @@
       <c r="AI52" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ52" s="20" t="s">
+      <c r="AJ52" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK52" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A53" s="24">
         <v>63</v>
       </c>
@@ -19906,7 +20035,7 @@
         <v>162004385</v>
       </c>
       <c r="J53" s="25">
-        <v>46273</v>
+        <v>46243</v>
       </c>
       <c r="K53" s="20" t="s">
         <v>1</v>
@@ -19917,37 +20046,37 @@
       <c r="M53" s="20">
         <v>3777.2</v>
       </c>
-      <c r="N53" s="20">
+      <c r="N53" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O53" s="20">
         <v>6.91</v>
       </c>
-      <c r="O53" s="20">
+      <c r="P53" s="20">
         <v>23.27</v>
       </c>
-      <c r="P53" s="20">
+      <c r="Q53" s="20">
         <v>43.39</v>
       </c>
-      <c r="Q53" s="20">
+      <c r="R53" s="20">
         <v>3590</v>
       </c>
-      <c r="R53" s="7">
+      <c r="S53" s="7">
         <v>19.670000000000002</v>
       </c>
-      <c r="S53" s="7">
+      <c r="T53" s="7">
         <v>20.079999999999998</v>
       </c>
-      <c r="T53" s="7">
+      <c r="U53" s="7">
         <v>37.44</v>
       </c>
-      <c r="U53" s="7">
+      <c r="V53" s="7">
         <v>22.81</v>
       </c>
-      <c r="V53" s="26">
+      <c r="W53" s="26">
         <v>3098</v>
       </c>
-      <c r="W53" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X53" s="27" t="s">
+      <c r="X53" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y53" s="27" t="s">
@@ -19965,13 +20094,13 @@
       <c r="AC53" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD53" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE53" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF53" s="29" t="s">
+      <c r="AD53" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE53" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF53" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG53" s="29" t="s">
@@ -19983,11 +20112,14 @@
       <c r="AI53" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ53" s="20" t="s">
+      <c r="AJ53" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK53" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A54" s="24">
         <v>65</v>
       </c>
@@ -20016,7 +20148,7 @@
         <v>162006415</v>
       </c>
       <c r="J54" s="25">
-        <v>46273</v>
+        <v>46243</v>
       </c>
       <c r="K54" s="20" t="s">
         <v>1</v>
@@ -20027,37 +20159,37 @@
       <c r="M54" s="20">
         <v>3840.6</v>
       </c>
-      <c r="N54" s="20">
+      <c r="N54" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O54" s="20">
         <v>6.45</v>
       </c>
-      <c r="O54" s="20">
+      <c r="P54" s="20">
         <v>22.11</v>
       </c>
-      <c r="P54" s="20">
+      <c r="Q54" s="20">
         <v>47.92</v>
       </c>
-      <c r="Q54" s="20">
+      <c r="R54" s="20">
         <v>3280</v>
       </c>
-      <c r="R54" s="7">
+      <c r="S54" s="7">
         <v>18.079999999999998</v>
       </c>
-      <c r="S54" s="7">
+      <c r="T54" s="7">
         <v>19.36</v>
       </c>
-      <c r="T54" s="7">
+      <c r="U54" s="7">
         <v>41.96</v>
       </c>
-      <c r="U54" s="7">
+      <c r="V54" s="7">
         <v>20.6</v>
       </c>
-      <c r="V54" s="26">
+      <c r="W54" s="26">
         <v>2872</v>
       </c>
-      <c r="W54" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X54" s="27" t="s">
+      <c r="X54" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y54" s="27" t="s">
@@ -20075,13 +20207,13 @@
       <c r="AC54" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD54" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE54" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF54" s="29" t="s">
+      <c r="AD54" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE54" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF54" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG54" s="29" t="s">
@@ -20093,11 +20225,14 @@
       <c r="AI54" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ54" s="20" t="s">
+      <c r="AJ54" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK54" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A55" s="24">
         <v>67</v>
       </c>
@@ -20126,7 +20261,7 @@
         <v>162004386</v>
       </c>
       <c r="J55" s="25">
-        <v>46303</v>
+        <v>46244</v>
       </c>
       <c r="K55" s="20" t="s">
         <v>1</v>
@@ -20137,37 +20272,37 @@
       <c r="M55" s="20">
         <v>3836.2</v>
       </c>
-      <c r="N55" s="20">
+      <c r="N55" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O55" s="20">
         <v>7.09</v>
       </c>
-      <c r="O55" s="20">
+      <c r="P55" s="20">
         <v>23.52</v>
       </c>
-      <c r="P55" s="20">
+      <c r="Q55" s="20">
         <v>43.99</v>
       </c>
-      <c r="Q55" s="20">
+      <c r="R55" s="20">
         <v>3537</v>
       </c>
-      <c r="R55" s="7">
+      <c r="S55" s="7">
         <v>19.77</v>
       </c>
-      <c r="S55" s="7">
+      <c r="T55" s="7">
         <v>20.309999999999999</v>
       </c>
-      <c r="T55" s="7">
+      <c r="U55" s="7">
         <v>37.99</v>
       </c>
-      <c r="U55" s="7">
+      <c r="V55" s="7">
         <v>21.93</v>
       </c>
-      <c r="V55" s="26">
+      <c r="W55" s="26">
         <v>3054</v>
       </c>
-      <c r="W55" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X55" s="27" t="s">
+      <c r="X55" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y55" s="27" t="s">
@@ -20185,13 +20320,13 @@
       <c r="AC55" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD55" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE55" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF55" s="29" t="s">
+      <c r="AD55" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE55" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG55" s="29" t="s">
@@ -20203,11 +20338,14 @@
       <c r="AI55" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ55" s="20" t="s">
+      <c r="AJ55" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK55" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A56" s="24">
         <v>68</v>
       </c>
@@ -20236,7 +20374,7 @@
         <v>162011702</v>
       </c>
       <c r="J56" s="25">
-        <v>46303</v>
+        <v>46244</v>
       </c>
       <c r="K56" s="20" t="s">
         <v>1</v>
@@ -20247,37 +20385,37 @@
       <c r="M56" s="20">
         <v>3991.6</v>
       </c>
-      <c r="N56" s="20">
+      <c r="N56" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O56" s="20">
         <v>6.65</v>
       </c>
-      <c r="O56" s="20">
+      <c r="P56" s="20">
         <v>22.12</v>
       </c>
-      <c r="P56" s="20">
+      <c r="Q56" s="20">
         <v>45.92</v>
       </c>
-      <c r="Q56" s="20">
+      <c r="R56" s="20">
         <v>3425</v>
       </c>
-      <c r="R56" s="7">
+      <c r="S56" s="7">
         <v>17.329999999999998</v>
       </c>
-      <c r="S56" s="7">
+      <c r="T56" s="7">
         <v>19.59</v>
       </c>
-      <c r="T56" s="7">
+      <c r="U56" s="7">
         <v>40.67</v>
       </c>
-      <c r="U56" s="7">
+      <c r="V56" s="7">
         <v>22.41</v>
       </c>
-      <c r="V56" s="26">
+      <c r="W56" s="26">
         <v>3033</v>
       </c>
-      <c r="W56" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X56" s="27" t="s">
+      <c r="X56" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y56" s="27" t="s">
@@ -20295,13 +20433,13 @@
       <c r="AC56" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD56" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE56" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF56" s="29" t="s">
+      <c r="AD56" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE56" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG56" s="29" t="s">
@@ -20313,11 +20451,14 @@
       <c r="AI56" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ56" s="20" t="s">
+      <c r="AJ56" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK56" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A57" s="24">
         <v>70</v>
       </c>
@@ -20346,7 +20487,7 @@
         <v>162006417</v>
       </c>
       <c r="J57" s="25">
-        <v>46303</v>
+        <v>46244</v>
       </c>
       <c r="K57" s="20" t="s">
         <v>1</v>
@@ -20357,37 +20498,37 @@
       <c r="M57" s="20">
         <v>4039.3</v>
       </c>
-      <c r="N57" s="20">
+      <c r="N57" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O57" s="20">
         <v>6.82</v>
       </c>
-      <c r="O57" s="20">
+      <c r="P57" s="20">
         <v>23.74</v>
       </c>
-      <c r="P57" s="20">
+      <c r="Q57" s="20">
         <v>44.3</v>
       </c>
-      <c r="Q57" s="20">
+      <c r="R57" s="20">
         <v>3411</v>
       </c>
-      <c r="R57" s="7">
+      <c r="S57" s="7">
         <v>19.190000000000001</v>
       </c>
-      <c r="S57" s="7">
+      <c r="T57" s="7">
         <v>20.59</v>
       </c>
-      <c r="T57" s="7">
+      <c r="U57" s="7">
         <v>38.42</v>
       </c>
-      <c r="U57" s="7">
+      <c r="V57" s="7">
         <v>21.8</v>
       </c>
-      <c r="V57" s="26">
+      <c r="W57" s="26">
         <v>2958</v>
       </c>
-      <c r="W57" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X57" s="27" t="s">
+      <c r="X57" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y57" s="27" t="s">
@@ -20405,13 +20546,13 @@
       <c r="AC57" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD57" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE57" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF57" s="29" t="s">
+      <c r="AD57" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE57" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF57" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG57" s="29" t="s">
@@ -20423,11 +20564,14 @@
       <c r="AI57" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ57" s="20" t="s">
+      <c r="AJ57" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK57" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A58" s="24">
         <v>71</v>
       </c>
@@ -20456,7 +20600,7 @@
         <v>162011703</v>
       </c>
       <c r="J58" s="25">
-        <v>46334</v>
+        <v>46245</v>
       </c>
       <c r="K58" s="20" t="s">
         <v>1</v>
@@ -20467,37 +20611,37 @@
       <c r="M58" s="20">
         <v>3673.6</v>
       </c>
-      <c r="N58" s="20">
+      <c r="N58" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O58" s="20">
         <v>7.66</v>
       </c>
-      <c r="O58" s="20">
+      <c r="P58" s="20">
         <v>27.2</v>
       </c>
-      <c r="P58" s="20">
+      <c r="Q58" s="20">
         <v>31.62</v>
       </c>
-      <c r="Q58" s="20">
+      <c r="R58" s="20">
         <v>4573</v>
       </c>
-      <c r="R58" s="7">
+      <c r="S58" s="7">
         <v>21.67</v>
       </c>
-      <c r="S58" s="7">
+      <c r="T58" s="7">
         <v>23.07</v>
       </c>
-      <c r="T58" s="7">
+      <c r="U58" s="7">
         <v>26.82</v>
       </c>
-      <c r="U58" s="7">
+      <c r="V58" s="7">
         <v>28.44</v>
       </c>
-      <c r="V58" s="26">
+      <c r="W58" s="26">
         <v>3879</v>
       </c>
-      <c r="W58" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X58" s="27" t="s">
+      <c r="X58" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y58" s="27" t="s">
@@ -20515,13 +20659,13 @@
       <c r="AC58" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD58" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE58" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF58" s="29" t="s">
+      <c r="AD58" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE58" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG58" s="29" t="s">
@@ -20533,11 +20677,14 @@
       <c r="AI58" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ58" s="20" t="s">
+      <c r="AJ58" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK58" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A59" s="24">
         <v>72</v>
       </c>
@@ -20566,7 +20713,7 @@
         <v>162006421</v>
       </c>
       <c r="J59" s="25">
-        <v>46303</v>
+        <v>46244</v>
       </c>
       <c r="K59" s="20" t="s">
         <v>1</v>
@@ -20577,37 +20724,37 @@
       <c r="M59" s="20">
         <v>4103.6000000000004</v>
       </c>
-      <c r="N59" s="20">
+      <c r="N59" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O59" s="20">
         <v>6.98</v>
       </c>
-      <c r="O59" s="20">
+      <c r="P59" s="20">
         <v>22.63</v>
       </c>
-      <c r="P59" s="20">
+      <c r="Q59" s="20">
         <v>44.75</v>
       </c>
-      <c r="Q59" s="20">
+      <c r="R59" s="20">
         <v>3477</v>
       </c>
-      <c r="R59" s="7">
+      <c r="S59" s="7">
         <v>19.45</v>
       </c>
-      <c r="S59" s="7">
+      <c r="T59" s="7">
         <v>19.600000000000001</v>
       </c>
-      <c r="T59" s="7">
+      <c r="U59" s="7">
         <v>38.75</v>
       </c>
-      <c r="U59" s="7">
+      <c r="V59" s="7">
         <v>22.2</v>
       </c>
-      <c r="V59" s="26">
+      <c r="W59" s="26">
         <v>3011</v>
       </c>
-      <c r="W59" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X59" s="27" t="s">
+      <c r="X59" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y59" s="27" t="s">
@@ -20625,13 +20772,13 @@
       <c r="AC59" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD59" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE59" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF59" s="29" t="s">
+      <c r="AD59" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE59" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF59" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG59" s="29" t="s">
@@ -20643,11 +20790,14 @@
       <c r="AI59" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ59" s="20" t="s">
+      <c r="AJ59" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK59" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A60" s="24">
         <v>74</v>
       </c>
@@ -20676,7 +20826,7 @@
         <v>162004389</v>
       </c>
       <c r="J60" s="25">
-        <v>46334</v>
+        <v>46245</v>
       </c>
       <c r="K60" s="20" t="s">
         <v>1</v>
@@ -20699,25 +20849,25 @@
       <c r="Q60" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R60" s="7">
+      <c r="R60" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S60" s="7">
         <v>20.399999999999999</v>
       </c>
-      <c r="S60" s="7">
+      <c r="T60" s="7">
         <v>22.12</v>
       </c>
-      <c r="T60" s="7">
+      <c r="U60" s="7">
         <v>33.090000000000003</v>
       </c>
-      <c r="U60" s="7">
+      <c r="V60" s="7">
         <v>24.39</v>
       </c>
-      <c r="V60" s="26">
+      <c r="W60" s="26">
         <v>3348</v>
       </c>
-      <c r="W60" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X60" s="27" t="s">
+      <c r="X60" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y60" s="27" t="s">
@@ -20735,13 +20885,13 @@
       <c r="AC60" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD60" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE60" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF60" s="29" t="s">
+      <c r="AD60" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE60" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF60" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG60" s="29" t="s">
@@ -20753,11 +20903,14 @@
       <c r="AI60" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ60" s="20" t="s">
+      <c r="AJ60" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK60" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A61" s="24">
         <v>75</v>
       </c>
@@ -20786,7 +20939,7 @@
         <v>162004390</v>
       </c>
       <c r="J61" s="25">
-        <v>46334</v>
+        <v>46245</v>
       </c>
       <c r="K61" s="20" t="s">
         <v>1</v>
@@ -20809,25 +20962,25 @@
       <c r="Q61" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R61" s="7">
+      <c r="R61" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S61" s="7">
         <v>21.71</v>
       </c>
-      <c r="S61" s="7">
+      <c r="T61" s="7">
         <v>21.31</v>
       </c>
-      <c r="T61" s="7">
+      <c r="U61" s="7">
         <v>33.11</v>
       </c>
-      <c r="U61" s="7">
+      <c r="V61" s="7">
         <v>23.87</v>
       </c>
-      <c r="V61" s="26">
+      <c r="W61" s="26">
         <v>3242</v>
       </c>
-      <c r="W61" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X61" s="27" t="s">
+      <c r="X61" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y61" s="27" t="s">
@@ -20845,13 +20998,13 @@
       <c r="AC61" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE61" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF61" s="29" t="s">
+      <c r="AD61" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE61" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF61" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG61" s="29" t="s">
@@ -20863,11 +21016,14 @@
       <c r="AI61" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ61" s="20" t="s">
+      <c r="AJ61" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK61" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A62" s="24">
         <v>76</v>
       </c>
@@ -20896,7 +21052,7 @@
         <v>162004387</v>
       </c>
       <c r="J62" s="25">
-        <v>46303</v>
+        <v>46244</v>
       </c>
       <c r="K62" s="20" t="s">
         <v>1</v>
@@ -20919,25 +21075,25 @@
       <c r="Q62" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R62" s="7">
+      <c r="R62" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S62" s="7">
         <v>20.67</v>
       </c>
-      <c r="S62" s="7">
+      <c r="T62" s="7">
         <v>22.6</v>
       </c>
-      <c r="T62" s="7">
+      <c r="U62" s="7">
         <v>31.11</v>
       </c>
-      <c r="U62" s="7">
+      <c r="V62" s="7">
         <v>25.63</v>
       </c>
-      <c r="V62" s="26">
+      <c r="W62" s="26">
         <v>3515</v>
       </c>
-      <c r="W62" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X62" s="27" t="s">
+      <c r="X62" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y62" s="27" t="s">
@@ -20955,13 +21111,13 @@
       <c r="AC62" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD62" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE62" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF62" s="29" t="s">
+      <c r="AD62" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE62" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF62" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG62" s="29" t="s">
@@ -20973,11 +21129,14 @@
       <c r="AI62" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ62" s="20" t="s">
+      <c r="AJ62" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK62" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A63" s="24">
         <v>77</v>
       </c>
@@ -21006,7 +21165,7 @@
         <v>162011706</v>
       </c>
       <c r="J63" s="25">
-        <v>46364</v>
+        <v>46246</v>
       </c>
       <c r="K63" s="20" t="s">
         <v>1</v>
@@ -21029,25 +21188,25 @@
       <c r="Q63" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R63" s="7">
+      <c r="R63" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S63" s="7">
         <v>21.36</v>
       </c>
-      <c r="S63" s="7">
+      <c r="T63" s="7">
         <v>21.31</v>
       </c>
-      <c r="T63" s="7">
+      <c r="U63" s="7">
         <v>33</v>
       </c>
-      <c r="U63" s="7">
+      <c r="V63" s="7">
         <v>24.33</v>
       </c>
-      <c r="V63" s="26">
+      <c r="W63" s="26">
         <v>3326</v>
       </c>
-      <c r="W63" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X63" s="27" t="s">
+      <c r="X63" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y63" s="27" t="s">
@@ -21065,13 +21224,13 @@
       <c r="AC63" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD63" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE63" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF63" s="29" t="s">
+      <c r="AD63" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE63" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF63" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG63" s="29" t="s">
@@ -21083,11 +21242,14 @@
       <c r="AI63" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ63" s="20" t="s">
+      <c r="AJ63" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK63" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A64" s="24">
         <v>80</v>
       </c>
@@ -21116,7 +21278,7 @@
         <v>162004392</v>
       </c>
       <c r="J64" s="25">
-        <v>46364</v>
+        <v>46246</v>
       </c>
       <c r="K64" s="20" t="s">
         <v>1</v>
@@ -21139,25 +21301,25 @@
       <c r="Q64" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R64" s="7">
+      <c r="R64" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S64" s="7">
         <v>20.03</v>
       </c>
-      <c r="S64" s="7">
+      <c r="T64" s="7">
         <v>22.11</v>
       </c>
-      <c r="T64" s="7">
+      <c r="U64" s="7">
         <v>34.24</v>
       </c>
-      <c r="U64" s="7">
+      <c r="V64" s="7">
         <v>23.63</v>
       </c>
-      <c r="V64" s="26">
+      <c r="W64" s="26">
         <v>3238</v>
       </c>
-      <c r="W64" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X64" s="27" t="s">
+      <c r="X64" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y64" s="27" t="s">
@@ -21175,13 +21337,13 @@
       <c r="AC64" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD64" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE64" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF64" s="29" t="s">
+      <c r="AD64" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE64" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF64" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG64" s="29" t="s">
@@ -21193,11 +21355,14 @@
       <c r="AI64" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ64" s="20" t="s">
+      <c r="AJ64" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK64" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A65" s="24">
         <v>81</v>
       </c>
@@ -21226,7 +21391,7 @@
         <v>162011705</v>
       </c>
       <c r="J65" s="25">
-        <v>46364</v>
+        <v>46246</v>
       </c>
       <c r="K65" s="20" t="s">
         <v>1</v>
@@ -21249,25 +21414,25 @@
       <c r="Q65" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R65" s="7">
+      <c r="R65" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S65" s="7">
         <v>23.33</v>
       </c>
-      <c r="S65" s="7">
+      <c r="T65" s="7">
         <v>23.35</v>
       </c>
-      <c r="T65" s="7">
+      <c r="U65" s="7">
         <v>21.86</v>
       </c>
-      <c r="U65" s="7">
+      <c r="V65" s="7">
         <v>31.46</v>
       </c>
-      <c r="V65" s="26">
+      <c r="W65" s="26">
         <v>4068</v>
       </c>
-      <c r="W65" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X65" s="27" t="s">
+      <c r="X65" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y65" s="27" t="s">
@@ -21285,13 +21450,13 @@
       <c r="AC65" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD65" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE65" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF65" s="29" t="s">
+      <c r="AD65" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE65" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF65" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG65" s="29" t="s">
@@ -21303,11 +21468,14 @@
       <c r="AI65" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ65" s="20" t="s">
+      <c r="AJ65" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK65" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A66" s="24">
         <v>83</v>
       </c>
@@ -21335,8 +21503,8 @@
       <c r="I66" s="20">
         <v>162011708</v>
       </c>
-      <c r="J66" s="20" t="s">
-        <v>53</v>
+      <c r="J66" s="25">
+        <v>46247</v>
       </c>
       <c r="K66" s="20" t="s">
         <v>1</v>
@@ -21359,25 +21527,25 @@
       <c r="Q66" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R66" s="7">
+      <c r="R66" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S66" s="7">
         <v>23.06</v>
       </c>
-      <c r="S66" s="7">
+      <c r="T66" s="7">
         <v>19.95</v>
       </c>
-      <c r="T66" s="7">
+      <c r="U66" s="7">
         <v>31.35</v>
       </c>
-      <c r="U66" s="7">
+      <c r="V66" s="7">
         <v>25.64</v>
       </c>
-      <c r="V66" s="26">
+      <c r="W66" s="26">
         <v>3265</v>
       </c>
-      <c r="W66" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X66" s="27" t="s">
+      <c r="X66" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y66" s="27" t="s">
@@ -21395,13 +21563,13 @@
       <c r="AC66" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD66" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE66" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF66" s="29" t="s">
+      <c r="AD66" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE66" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF66" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG66" s="29" t="s">
@@ -21413,11 +21581,14 @@
       <c r="AI66" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ66" s="20" t="s">
+      <c r="AJ66" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK66" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A67" s="24">
         <v>84</v>
       </c>
@@ -21446,7 +21617,7 @@
         <v>162006427</v>
       </c>
       <c r="J67" s="25">
-        <v>46364</v>
+        <v>46246</v>
       </c>
       <c r="K67" s="20" t="s">
         <v>1</v>
@@ -21469,25 +21640,25 @@
       <c r="Q67" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R67" s="7">
+      <c r="R67" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S67" s="7">
         <v>22.48</v>
       </c>
-      <c r="S67" s="7">
+      <c r="T67" s="7">
         <v>20.68</v>
       </c>
-      <c r="T67" s="7">
+      <c r="U67" s="7">
         <v>35.83</v>
       </c>
-      <c r="U67" s="7">
+      <c r="V67" s="7">
         <v>21</v>
       </c>
-      <c r="V67" s="26">
+      <c r="W67" s="26">
         <v>2925</v>
       </c>
-      <c r="W67" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X67" s="27" t="s">
+      <c r="X67" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y67" s="27" t="s">
@@ -21505,13 +21676,13 @@
       <c r="AC67" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD67" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE67" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF67" s="29" t="s">
+      <c r="AD67" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE67" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF67" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG67" s="29" t="s">
@@ -21523,11 +21694,14 @@
       <c r="AI67" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ67" s="20" t="s">
+      <c r="AJ67" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK67" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A68" s="24">
         <v>86</v>
       </c>
@@ -21555,8 +21729,8 @@
       <c r="I68" s="20">
         <v>162004394</v>
       </c>
-      <c r="J68" s="20" t="s">
-        <v>53</v>
+      <c r="J68" s="25">
+        <v>46247</v>
       </c>
       <c r="K68" s="20" t="s">
         <v>1</v>
@@ -21579,25 +21753,25 @@
       <c r="Q68" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R68" s="7">
+      <c r="R68" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S68" s="7">
         <v>22.82</v>
       </c>
-      <c r="S68" s="7">
+      <c r="T68" s="7">
         <v>20.440000000000001</v>
       </c>
-      <c r="T68" s="7">
+      <c r="U68" s="7">
         <v>34.119999999999997</v>
       </c>
-      <c r="U68" s="7">
+      <c r="V68" s="7">
         <v>22.62</v>
       </c>
-      <c r="V68" s="26">
+      <c r="W68" s="26">
         <v>3047</v>
       </c>
-      <c r="W68" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X68" s="27" t="s">
+      <c r="X68" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y68" s="27" t="s">
@@ -21615,13 +21789,13 @@
       <c r="AC68" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD68" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE68" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF68" s="29" t="s">
+      <c r="AD68" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF68" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG68" s="29" t="s">
@@ -21633,11 +21807,14 @@
       <c r="AI68" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ68" s="20" t="s">
+      <c r="AJ68" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK68" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A69" s="24">
         <v>88</v>
       </c>
@@ -21665,8 +21842,8 @@
       <c r="I69" s="20">
         <v>162011709</v>
       </c>
-      <c r="J69" s="20" t="s">
-        <v>53</v>
+      <c r="J69" s="25">
+        <v>46247</v>
       </c>
       <c r="K69" s="20" t="s">
         <v>1</v>
@@ -21689,25 +21866,25 @@
       <c r="Q69" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R69" s="7">
+      <c r="R69" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S69" s="7">
         <v>23.8</v>
       </c>
-      <c r="S69" s="7">
+      <c r="T69" s="7">
         <v>20.87</v>
       </c>
-      <c r="T69" s="7">
+      <c r="U69" s="7">
         <v>29.16</v>
       </c>
-      <c r="U69" s="7">
+      <c r="V69" s="7">
         <v>26.17</v>
       </c>
-      <c r="V69" s="26">
+      <c r="W69" s="26">
         <v>3485</v>
       </c>
-      <c r="W69" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X69" s="27" t="s">
+      <c r="X69" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y69" s="27" t="s">
@@ -21725,13 +21902,13 @@
       <c r="AC69" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD69" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE69" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF69" s="29" t="s">
+      <c r="AD69" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE69" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF69" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG69" s="29" t="s">
@@ -21743,11 +21920,14 @@
       <c r="AI69" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ69" s="20" t="s">
+      <c r="AJ69" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK69" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A70" s="24">
         <v>89</v>
       </c>
@@ -21775,8 +21955,8 @@
       <c r="I70" s="20">
         <v>162011711</v>
       </c>
-      <c r="J70" s="20" t="s">
-        <v>54</v>
+      <c r="J70" s="25">
+        <v>46248</v>
       </c>
       <c r="K70" s="20" t="s">
         <v>1</v>
@@ -21799,25 +21979,25 @@
       <c r="Q70" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R70" s="7">
+      <c r="R70" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S70" s="7">
         <v>23.1</v>
       </c>
-      <c r="S70" s="7">
+      <c r="T70" s="7">
         <v>21.45</v>
       </c>
-      <c r="T70" s="7">
+      <c r="U70" s="7">
         <v>29.06</v>
       </c>
-      <c r="U70" s="7">
+      <c r="V70" s="7">
         <v>26.39</v>
       </c>
-      <c r="V70" s="26">
+      <c r="W70" s="26">
         <v>3559</v>
       </c>
-      <c r="W70" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X70" s="27" t="s">
+      <c r="X70" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y70" s="27" t="s">
@@ -21835,13 +22015,13 @@
       <c r="AC70" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD70" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE70" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF70" s="29" t="s">
+      <c r="AD70" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE70" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF70" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG70" s="29" t="s">
@@ -21853,11 +22033,14 @@
       <c r="AI70" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ70" s="20" t="s">
+      <c r="AJ70" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK70" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A71" s="24">
         <v>90</v>
       </c>
@@ -21885,8 +22068,8 @@
       <c r="I71" s="20">
         <v>162004398</v>
       </c>
-      <c r="J71" s="20" t="s">
-        <v>54</v>
+      <c r="J71" s="25">
+        <v>46248</v>
       </c>
       <c r="K71" s="20" t="s">
         <v>1</v>
@@ -21909,25 +22092,25 @@
       <c r="Q71" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R71" s="7">
+      <c r="R71" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S71" s="7">
         <v>23.75</v>
       </c>
-      <c r="S71" s="7">
+      <c r="T71" s="7">
         <v>20.51</v>
       </c>
-      <c r="T71" s="7">
+      <c r="U71" s="7">
         <v>31.43</v>
       </c>
-      <c r="U71" s="7">
+      <c r="V71" s="7">
         <v>24.31</v>
       </c>
-      <c r="V71" s="26">
+      <c r="W71" s="26">
         <v>3333</v>
       </c>
-      <c r="W71" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X71" s="27" t="s">
+      <c r="X71" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y71" s="27" t="s">
@@ -21945,13 +22128,13 @@
       <c r="AC71" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD71" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE71" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF71" s="29" t="s">
+      <c r="AD71" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE71" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF71" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG71" s="29" t="s">
@@ -21963,11 +22146,14 @@
       <c r="AI71" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ71" s="20" t="s">
+      <c r="AJ71" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK71" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A72" s="24">
         <v>92</v>
       </c>
@@ -21995,8 +22181,8 @@
       <c r="I72" s="20">
         <v>162004397</v>
       </c>
-      <c r="J72" s="20" t="s">
-        <v>54</v>
+      <c r="J72" s="25">
+        <v>46248</v>
       </c>
       <c r="K72" s="20" t="s">
         <v>1</v>
@@ -22019,25 +22205,25 @@
       <c r="Q72" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R72" s="7">
+      <c r="R72" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S72" s="7">
         <v>22.5</v>
       </c>
-      <c r="S72" s="7">
+      <c r="T72" s="7">
         <v>22.63</v>
       </c>
-      <c r="T72" s="7">
+      <c r="U72" s="7">
         <v>28.32</v>
       </c>
-      <c r="U72" s="7">
+      <c r="V72" s="7">
         <v>26.55</v>
       </c>
-      <c r="V72" s="26">
+      <c r="W72" s="26">
         <v>3586</v>
       </c>
-      <c r="W72" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X72" s="27" t="s">
+      <c r="X72" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y72" s="27" t="s">
@@ -22055,13 +22241,13 @@
       <c r="AC72" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD72" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE72" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF72" s="29" t="s">
+      <c r="AD72" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE72" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF72" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG72" s="29" t="s">
@@ -22073,11 +22259,14 @@
       <c r="AI72" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ72" s="20" t="s">
+      <c r="AJ72" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK72" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A73" s="24">
         <v>93</v>
       </c>
@@ -22105,8 +22294,8 @@
       <c r="I73" s="20">
         <v>162004396</v>
       </c>
-      <c r="J73" s="20" t="s">
-        <v>53</v>
+      <c r="J73" s="25">
+        <v>46247</v>
       </c>
       <c r="K73" s="20" t="s">
         <v>1</v>
@@ -22129,25 +22318,25 @@
       <c r="Q73" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R73" s="7">
+      <c r="R73" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S73" s="7">
         <v>21.53</v>
       </c>
-      <c r="S73" s="7">
+      <c r="T73" s="7">
         <v>21.48</v>
       </c>
-      <c r="T73" s="7">
+      <c r="U73" s="7">
         <v>32.47</v>
       </c>
-      <c r="U73" s="7">
+      <c r="V73" s="7">
         <v>24.53</v>
       </c>
-      <c r="V73" s="26">
+      <c r="W73" s="26">
         <v>3307</v>
       </c>
-      <c r="W73" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X73" s="27" t="s">
+      <c r="X73" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y73" s="27" t="s">
@@ -22165,13 +22354,13 @@
       <c r="AC73" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD73" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE73" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF73" s="29" t="s">
+      <c r="AD73" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE73" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF73" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG73" s="29" t="s">
@@ -22183,11 +22372,14 @@
       <c r="AI73" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ73" s="20" t="s">
+      <c r="AJ73" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK73" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A74" s="24">
         <v>96</v>
       </c>
@@ -22215,8 +22407,8 @@
       <c r="I74" s="20">
         <v>162004401</v>
       </c>
-      <c r="J74" s="20" t="s">
-        <v>55</v>
+      <c r="J74" s="25">
+        <v>46249</v>
       </c>
       <c r="K74" s="20" t="s">
         <v>1</v>
@@ -22239,25 +22431,25 @@
       <c r="Q74" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R74" s="7">
+      <c r="R74" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S74" s="7">
         <v>22.91</v>
       </c>
-      <c r="S74" s="7">
+      <c r="T74" s="7">
         <v>22.09</v>
       </c>
-      <c r="T74" s="7">
+      <c r="U74" s="7">
         <v>30.2</v>
       </c>
-      <c r="U74" s="7">
+      <c r="V74" s="7">
         <v>24.8</v>
       </c>
-      <c r="V74" s="26">
+      <c r="W74" s="26">
         <v>3406</v>
       </c>
-      <c r="W74" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X74" s="27" t="s">
+      <c r="X74" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y74" s="27" t="s">
@@ -22275,13 +22467,13 @@
       <c r="AC74" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD74" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE74" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF74" s="29" t="s">
+      <c r="AD74" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE74" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF74" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG74" s="29" t="s">
@@ -22293,11 +22485,14 @@
       <c r="AI74" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ74" s="20" t="s">
+      <c r="AJ74" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK74" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A75" s="24">
         <v>97</v>
       </c>
@@ -22325,8 +22520,8 @@
       <c r="I75" s="20">
         <v>162006437</v>
       </c>
-      <c r="J75" s="20" t="s">
-        <v>54</v>
+      <c r="J75" s="25">
+        <v>46248</v>
       </c>
       <c r="K75" s="20" t="s">
         <v>1</v>
@@ -22349,25 +22544,25 @@
       <c r="Q75" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R75" s="7">
+      <c r="R75" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S75" s="7">
         <v>24.49</v>
       </c>
-      <c r="S75" s="7">
+      <c r="T75" s="7">
         <v>19.63</v>
       </c>
-      <c r="T75" s="7">
+      <c r="U75" s="7">
         <v>34.9</v>
       </c>
-      <c r="U75" s="7">
+      <c r="V75" s="7">
         <v>20.98</v>
       </c>
-      <c r="V75" s="26">
+      <c r="W75" s="26">
         <v>2979</v>
       </c>
-      <c r="W75" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X75" s="27" t="s">
+      <c r="X75" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y75" s="27" t="s">
@@ -22385,13 +22580,13 @@
       <c r="AC75" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD75" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE75" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF75" s="29" t="s">
+      <c r="AD75" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE75" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF75" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG75" s="29" t="s">
@@ -22403,11 +22598,14 @@
       <c r="AI75" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ75" s="20" t="s">
+      <c r="AJ75" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK75" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A76" s="24">
         <v>98</v>
       </c>
@@ -22435,8 +22633,8 @@
       <c r="I76" s="20">
         <v>162006441</v>
       </c>
-      <c r="J76" s="20" t="s">
-        <v>55</v>
+      <c r="J76" s="25">
+        <v>46249</v>
       </c>
       <c r="K76" s="20" t="s">
         <v>1</v>
@@ -22459,25 +22657,25 @@
       <c r="Q76" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R76" s="7">
+      <c r="R76" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S76" s="7">
         <v>24.64</v>
       </c>
-      <c r="S76" s="7">
+      <c r="T76" s="7">
         <v>21.9</v>
       </c>
-      <c r="T76" s="7">
+      <c r="U76" s="7">
         <v>29.6</v>
       </c>
-      <c r="U76" s="7">
+      <c r="V76" s="7">
         <v>23.86</v>
       </c>
-      <c r="V76" s="26">
+      <c r="W76" s="26">
         <v>3345</v>
       </c>
-      <c r="W76" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X76" s="27" t="s">
+      <c r="X76" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y76" s="27" t="s">
@@ -22495,29 +22693,32 @@
       <c r="AC76" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD76" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE76" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF76" s="29" t="s">
+      <c r="AD76" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE76" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF76" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG76" s="29" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="AH76" s="29" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AI76" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ76" s="20" t="s">
+      <c r="AJ76" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK76" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A77" s="24">
         <v>100</v>
       </c>
@@ -22545,8 +22746,8 @@
       <c r="I77" s="20">
         <v>162011715</v>
       </c>
-      <c r="J77" s="20" t="s">
-        <v>55</v>
+      <c r="J77" s="25">
+        <v>46249</v>
       </c>
       <c r="K77" s="20" t="s">
         <v>1</v>
@@ -22569,25 +22770,25 @@
       <c r="Q77" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R77" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S77" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T77" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U77" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V77" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="W77" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X77" s="27" t="s">
+      <c r="R77" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S77" s="7">
+        <v>24.22</v>
+      </c>
+      <c r="T77" s="7">
+        <v>21.8</v>
+      </c>
+      <c r="U77" s="7">
+        <v>25.23</v>
+      </c>
+      <c r="V77" s="7">
+        <v>28.75</v>
+      </c>
+      <c r="W77" s="26">
+        <v>3785</v>
+      </c>
+      <c r="X77" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y77" s="27" t="s">
@@ -22605,13 +22806,13 @@
       <c r="AC77" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD77" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE77" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF77" s="29" t="s">
+      <c r="AD77" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE77" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF77" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG77" s="29" t="s">
@@ -22623,11 +22824,14 @@
       <c r="AI77" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ77" s="20" t="s">
+      <c r="AJ77" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK77" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A78" s="24">
         <v>101</v>
       </c>
@@ -22655,8 +22859,8 @@
       <c r="I78" s="20">
         <v>162004402</v>
       </c>
-      <c r="J78" s="20" t="s">
-        <v>55</v>
+      <c r="J78" s="25">
+        <v>46249</v>
       </c>
       <c r="K78" s="20" t="s">
         <v>1</v>
@@ -22679,25 +22883,25 @@
       <c r="Q78" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R78" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S78" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T78" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U78" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V78" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="W78" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X78" s="27" t="s">
+      <c r="R78" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S78" s="7">
+        <v>24.29</v>
+      </c>
+      <c r="T78" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="U78" s="7">
+        <v>31.24</v>
+      </c>
+      <c r="V78" s="7">
+        <v>23.67</v>
+      </c>
+      <c r="W78" s="26">
+        <v>3256</v>
+      </c>
+      <c r="X78" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y78" s="27" t="s">
@@ -22715,13 +22919,13 @@
       <c r="AC78" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD78" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE78" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF78" s="29" t="s">
+      <c r="AD78" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE78" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF78" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG78" s="29" t="s">
@@ -22733,11 +22937,14 @@
       <c r="AI78" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ78" s="20" t="s">
+      <c r="AJ78" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK78" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A79" s="24">
         <v>102</v>
       </c>
@@ -22765,8 +22972,8 @@
       <c r="I79" s="20">
         <v>162011713</v>
       </c>
-      <c r="J79" s="20" t="s">
-        <v>55</v>
+      <c r="J79" s="25">
+        <v>46249</v>
       </c>
       <c r="K79" s="20" t="s">
         <v>1</v>
@@ -22789,25 +22996,25 @@
       <c r="Q79" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R79" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S79" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T79" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U79" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V79" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="W79" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X79" s="27" t="s">
+      <c r="R79" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S79" s="7">
+        <v>22.85</v>
+      </c>
+      <c r="T79" s="7">
+        <v>21.63</v>
+      </c>
+      <c r="U79" s="7">
+        <v>28.29</v>
+      </c>
+      <c r="V79" s="7">
+        <v>27.24</v>
+      </c>
+      <c r="W79" s="26">
+        <v>3632</v>
+      </c>
+      <c r="X79" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y79" s="27" t="s">
@@ -22825,13 +23032,13 @@
       <c r="AC79" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD79" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE79" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF79" s="29" t="s">
+      <c r="AD79" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE79" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF79" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG79" s="29" t="s">
@@ -22843,11 +23050,14 @@
       <c r="AI79" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ79" s="20" t="s">
+      <c r="AJ79" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK79" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A80" s="24">
         <v>103</v>
       </c>
@@ -22875,8 +23085,8 @@
       <c r="I80" s="20">
         <v>162004403</v>
       </c>
-      <c r="J80" s="20" t="s">
-        <v>57</v>
+      <c r="J80" s="25">
+        <v>46250</v>
       </c>
       <c r="K80" s="20" t="s">
         <v>1</v>
@@ -22899,25 +23109,25 @@
       <c r="Q80" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R80" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S80" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T80" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U80" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V80" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="W80" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X80" s="27" t="s">
+      <c r="R80" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S80" s="7">
+        <v>23.1</v>
+      </c>
+      <c r="T80" s="7">
+        <v>21.51</v>
+      </c>
+      <c r="U80" s="7">
+        <v>31.48</v>
+      </c>
+      <c r="V80" s="7">
+        <v>23.91</v>
+      </c>
+      <c r="W80" s="26">
+        <v>3296</v>
+      </c>
+      <c r="X80" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y80" s="27" t="s">
@@ -22935,13 +23145,13 @@
       <c r="AC80" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD80" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE80" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF80" s="29" t="s">
+      <c r="AD80" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE80" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF80" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG80" s="29" t="s">
@@ -22953,11 +23163,14 @@
       <c r="AI80" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ80" s="20" t="s">
+      <c r="AJ80" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK80" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A81" s="24">
         <v>105</v>
       </c>
@@ -22985,8 +23198,8 @@
       <c r="I81" s="20">
         <v>162011717</v>
       </c>
-      <c r="J81" s="20" t="s">
-        <v>58</v>
+      <c r="J81" s="25">
+        <v>46251</v>
       </c>
       <c r="K81" s="20" t="s">
         <v>1</v>
@@ -23009,25 +23222,25 @@
       <c r="Q81" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R81" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S81" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T81" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U81" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V81" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="W81" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X81" s="27" t="s">
+      <c r="R81" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S81" s="7">
+        <v>23.1</v>
+      </c>
+      <c r="T81" s="7">
+        <v>22.53</v>
+      </c>
+      <c r="U81" s="7">
+        <v>25.61</v>
+      </c>
+      <c r="V81" s="7">
+        <v>28.76</v>
+      </c>
+      <c r="W81" s="26">
+        <v>3821</v>
+      </c>
+      <c r="X81" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y81" s="27" t="s">
@@ -23045,13 +23258,13 @@
       <c r="AC81" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD81" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE81" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF81" s="29" t="s">
+      <c r="AD81" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE81" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF81" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG81" s="29" t="s">
@@ -23063,11 +23276,14 @@
       <c r="AI81" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ81" s="20" t="s">
+      <c r="AJ81" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK81" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A82" s="24">
         <v>106</v>
       </c>
@@ -23095,8 +23311,8 @@
       <c r="I82" s="20">
         <v>162004404</v>
       </c>
-      <c r="J82" s="20" t="s">
-        <v>59</v>
+      <c r="J82" s="25">
+        <v>46220</v>
       </c>
       <c r="K82" s="20" t="s">
         <v>1</v>
@@ -23119,25 +23335,25 @@
       <c r="Q82" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R82" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S82" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T82" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U82" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V82" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="W82" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X82" s="27" t="s">
+      <c r="R82" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S82" s="7">
+        <v>23.86</v>
+      </c>
+      <c r="T82" s="7">
+        <v>22.01</v>
+      </c>
+      <c r="U82" s="7">
+        <v>28.41</v>
+      </c>
+      <c r="V82" s="7">
+        <v>25.72</v>
+      </c>
+      <c r="W82" s="26">
+        <v>3514</v>
+      </c>
+      <c r="X82" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y82" s="27" t="s">
@@ -23155,13 +23371,13 @@
       <c r="AC82" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD82" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE82" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF82" s="29" t="s">
+      <c r="AD82" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE82" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF82" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG82" s="29" t="s">
@@ -23173,11 +23389,14 @@
       <c r="AI82" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ82" s="20" t="s">
+      <c r="AJ82" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK82" s="20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A83" s="24">
         <v>109</v>
       </c>
@@ -23205,8 +23424,8 @@
       <c r="I83" s="20">
         <v>162011719</v>
       </c>
-      <c r="J83" s="20" t="s">
-        <v>60</v>
+      <c r="J83" s="25">
+        <v>46252</v>
       </c>
       <c r="K83" s="20" t="s">
         <v>1</v>
@@ -23229,25 +23448,25 @@
       <c r="Q83" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="R83" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S83" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T83" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U83" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V83" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="W83" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="X83" s="27" t="s">
+      <c r="R83" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S83" s="7">
+        <v>24.7</v>
+      </c>
+      <c r="T83" s="7">
+        <v>23.36</v>
+      </c>
+      <c r="U83" s="7">
+        <v>22.16</v>
+      </c>
+      <c r="V83" s="7">
+        <v>29.78</v>
+      </c>
+      <c r="W83" s="26">
+        <v>3972</v>
+      </c>
+      <c r="X83" s="26" t="s">
         <v>1</v>
       </c>
       <c r="Y83" s="27" t="s">
@@ -23265,13 +23484,13 @@
       <c r="AC83" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="AD83" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE83" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF83" s="29" t="s">
+      <c r="AD83" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE83" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF83" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AG83" s="29" t="s">
@@ -23283,20 +23502,363 @@
       <c r="AI83" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AJ83" s="20" t="s">
+      <c r="AJ83" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK83" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A84" s="24">
+        <v>112</v>
+      </c>
+      <c r="B84" s="20">
+        <v>16592</v>
+      </c>
+      <c r="C84" s="25">
+        <v>46254</v>
+      </c>
+      <c r="D84" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E84" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G84" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H84" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I84" s="20">
+        <v>162004407</v>
+      </c>
+      <c r="J84" s="25">
+        <v>46253</v>
+      </c>
+      <c r="K84" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L84" s="20">
+        <v>3894.4</v>
+      </c>
+      <c r="M84" s="20">
+        <v>3755.4</v>
+      </c>
+      <c r="N84" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O84" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P84" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q84" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R84" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S84" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T84" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U84" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V84" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W84" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X84" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y84" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z84" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA84" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB84" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC84" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD84" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE84" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF84" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG84" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH84" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI84" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ84" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK84" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A85" s="24">
+        <v>113</v>
+      </c>
+      <c r="B85" s="20">
+        <v>16593</v>
+      </c>
+      <c r="C85" s="25">
+        <v>46254</v>
+      </c>
+      <c r="D85" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H85" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I85" s="20">
+        <v>162006452</v>
+      </c>
+      <c r="J85" s="25">
+        <v>46253</v>
+      </c>
+      <c r="K85" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L85" s="20">
+        <v>3701.6</v>
+      </c>
+      <c r="M85" s="34">
+        <f>L85</f>
+        <v>3701.6</v>
+      </c>
+      <c r="N85" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O85" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P85" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q85" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R85" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S85" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T85" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U85" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V85" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W85" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X85" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y85" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA85" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB85" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC85" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD85" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE85" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF85" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG85" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH85" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI85" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ85" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK85" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A86" s="24">
+        <v>114</v>
+      </c>
+      <c r="B86" s="20">
+        <v>16594</v>
+      </c>
+      <c r="C86" s="25">
+        <v>46255</v>
+      </c>
+      <c r="D86" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H86" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I86" s="20">
+        <v>162006453</v>
+      </c>
+      <c r="J86" s="25">
+        <v>46254</v>
+      </c>
+      <c r="K86" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L86" s="20">
+        <v>3910.8</v>
+      </c>
+      <c r="M86" s="20">
+        <v>3805.2</v>
+      </c>
+      <c r="N86" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O86" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P86" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q86" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R86" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S86" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T86" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U86" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V86" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W86" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X86" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z86" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA86" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB86" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC86" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD86" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE86" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF86" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG86" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH86" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI86" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ86" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK86" s="20" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="X1:AJ1"/>
-    <mergeCell ref="N2:V2"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:AB3"/>
-    <mergeCell ref="AC2:AC4"/>
+    <mergeCell ref="Y1:AK1"/>
+    <mergeCell ref="O2:W2"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AD2:AD4"/>
-    <mergeCell ref="AE2:AI3"/>
-    <mergeCell ref="AJ2:AJ4"/>
+    <mergeCell ref="AE2:AE4"/>
+    <mergeCell ref="AF2:AJ3"/>
+    <mergeCell ref="AK2:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Quality.xlsx
+++ b/Quality.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rudranil.dutta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF48809-750C-45CF-9FCE-7C6F7CF9417D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42354EA4-6514-4762-8AE2-CCC7AA605D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2365" uniqueCount="52">
   <si>
     <t>IGI Report</t>
   </si>
@@ -286,7 +286,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,12 +320,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -502,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -602,9 +596,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -994,21 +985,21 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
-      <c r="X1" s="35" t="s">
+      <c r="X1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="37"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AJ1" s="36"/>
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15"/>
@@ -1026,43 +1017,43 @@
       <c r="M2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="38" t="s">
+      <c r="N2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="39"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="38"/>
       <c r="W2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="40" t="s">
+      <c r="X2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="42" t="s">
+      <c r="Y2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="48" t="s">
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="42"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="48" t="s">
+      <c r="AD2" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="42" t="s">
+      <c r="AE2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="48" t="s">
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="47" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1136,19 +1127,19 @@
       <c r="W3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="46"/>
-      <c r="AG3" s="46"/>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="47"/>
-      <c r="AJ3" s="48"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="46"/>
+      <c r="AC3" s="47"/>
+      <c r="AD3" s="47"/>
+      <c r="AE3" s="44"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="46"/>
+      <c r="AJ3" s="47"/>
     </row>
     <row r="4" spans="1:36" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
@@ -1235,8 +1226,8 @@
       <c r="AB4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="49"/>
+      <c r="AC4" s="48"/>
+      <c r="AD4" s="48"/>
       <c r="AE4" s="6" t="s">
         <v>32</v>
       </c>
@@ -1252,7 +1243,7 @@
       <c r="AI4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ4" s="49"/>
+      <c r="AJ4" s="48"/>
     </row>
     <row r="5" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="24">
@@ -14251,7 +14242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCF8FC5-328B-42D6-97E6-FD36E465C669}">
-  <dimension ref="A1:AK86"/>
+  <dimension ref="A1:AK96"/>
   <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.453125" style="1" bestFit="1" customWidth="1"/>
@@ -14259,7 +14250,7 @@
     <col min="3" max="3" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -14315,21 +14306,21 @@
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
       <c r="X1" s="13"/>
-      <c r="Y1" s="35" t="s">
+      <c r="Y1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="36"/>
-      <c r="AK1" s="37"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AJ1" s="35"/>
+      <c r="AK1" s="36"/>
     </row>
     <row r="2" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15"/>
@@ -14348,86 +14339,60 @@
       <c r="N2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="38" t="s">
+      <c r="O2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="39"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="38"/>
       <c r="X2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="Y2" s="40" t="s">
+      <c r="Y2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="42" t="s">
+      <c r="Z2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="43"/>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="48" t="s">
+      <c r="AA2" s="42"/>
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AE2" s="48" t="s">
+      <c r="AE2" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="AF2" s="42" t="s">
+      <c r="AF2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="44"/>
-      <c r="AK2" s="48" t="s">
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="42"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>1</v>
-      </c>
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="21"/>
       <c r="N3" s="22" t="s">
         <v>1</v>
       </c>
@@ -14461,19 +14426,19 @@
       <c r="X3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="46"/>
-      <c r="AC3" s="47"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="48"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="46"/>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="46"/>
-      <c r="AJ3" s="47"/>
-      <c r="AK3" s="48"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="44"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="46"/>
+      <c r="AD3" s="47"/>
+      <c r="AE3" s="47"/>
+      <c r="AF3" s="44"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="46"/>
+      <c r="AK3" s="47"/>
     </row>
     <row r="4" spans="1:37" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
@@ -14563,8 +14528,8 @@
       <c r="AC4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AD4" s="49"/>
-      <c r="AE4" s="49"/>
+      <c r="AD4" s="48"/>
+      <c r="AE4" s="48"/>
       <c r="AF4" s="6" t="s">
         <v>32</v>
       </c>
@@ -14580,7 +14545,7 @@
       <c r="AJ4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AK4" s="49"/>
+      <c r="AK4" s="48"/>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" s="24">
@@ -14810,7 +14775,7 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" s="24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" s="20">
         <v>16485</v>
@@ -14923,7 +14888,7 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" s="24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" s="20">
         <v>16486</v>
@@ -15036,7 +15001,7 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" s="24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B9" s="20">
         <v>16490</v>
@@ -15149,7 +15114,7 @@
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" s="24">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B10" s="20">
         <v>16491</v>
@@ -15262,7 +15227,7 @@
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" s="24">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B11" s="20">
         <v>16492</v>
@@ -15375,7 +15340,7 @@
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" s="24">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B12" s="20">
         <v>16493</v>
@@ -15488,7 +15453,7 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" s="24">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B13" s="20">
         <v>16494</v>
@@ -15601,7 +15566,7 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" s="24">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B14" s="20">
         <v>16495</v>
@@ -15714,7 +15679,7 @@
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" s="24">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B15" s="20">
         <v>16496</v>
@@ -15827,7 +15792,7 @@
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" s="24">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B16" s="20">
         <v>16497</v>
@@ -15940,7 +15905,7 @@
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" s="24">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B17" s="20">
         <v>16498</v>
@@ -16053,7 +16018,7 @@
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" s="24">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B18" s="20">
         <v>16500</v>
@@ -16166,7 +16131,7 @@
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" s="24">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B19" s="20">
         <v>16501</v>
@@ -16279,7 +16244,7 @@
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" s="24">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B20" s="20">
         <v>16502</v>
@@ -16392,7 +16357,7 @@
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" s="24">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B21" s="20">
         <v>16504</v>
@@ -16505,7 +16470,7 @@
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" s="24">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B22" s="20">
         <v>16505</v>
@@ -16618,7 +16583,7 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" s="24">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B23" s="20">
         <v>16506</v>
@@ -16731,7 +16696,7 @@
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" s="24">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B24" s="20">
         <v>16507</v>
@@ -16844,7 +16809,7 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" s="24">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B25" s="20">
         <v>16508</v>
@@ -16957,7 +16922,7 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" s="24">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B26" s="20">
         <v>16509</v>
@@ -17070,7 +17035,7 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" s="24">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B27" s="20">
         <v>16510</v>
@@ -17183,7 +17148,7 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" s="24">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B28" s="20">
         <v>16511</v>
@@ -17296,7 +17261,7 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" s="24">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B29" s="20">
         <v>16512</v>
@@ -17409,7 +17374,7 @@
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" s="24">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B30" s="20">
         <v>16515</v>
@@ -17480,49 +17445,49 @@
       <c r="X30" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y30" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA30" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB30" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD30" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE30" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF30" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH30" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI30" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ30" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK30" s="20" t="s">
-        <v>1</v>
+      <c r="Y30" s="27">
+        <v>24.31</v>
+      </c>
+      <c r="Z30" s="27">
+        <v>6.63</v>
+      </c>
+      <c r="AA30" s="27">
+        <v>23.42</v>
+      </c>
+      <c r="AB30" s="27">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="AC30" s="27">
+        <v>32.75</v>
+      </c>
+      <c r="AD30" s="27">
+        <v>3924</v>
+      </c>
+      <c r="AE30" s="28">
+        <v>3181</v>
+      </c>
+      <c r="AF30" s="27">
+        <v>7.07</v>
+      </c>
+      <c r="AG30" s="29">
+        <v>23.31</v>
+      </c>
+      <c r="AH30" s="29">
+        <v>37.020000000000003</v>
+      </c>
+      <c r="AI30" s="29">
+        <v>32.6</v>
+      </c>
+      <c r="AJ30" s="29">
+        <v>3906</v>
+      </c>
+      <c r="AK30" s="20">
+        <v>3181</v>
       </c>
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" s="24">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B31" s="20">
         <v>16516</v>
@@ -17593,49 +17558,49 @@
       <c r="X31" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y31" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA31" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB31" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD31" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE31" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF31" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH31" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI31" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ31" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK31" s="20" t="s">
-        <v>1</v>
+      <c r="Y31" s="27">
+        <v>23.18</v>
+      </c>
+      <c r="Z31" s="27">
+        <v>6.29</v>
+      </c>
+      <c r="AA31" s="27">
+        <v>22.37</v>
+      </c>
+      <c r="AB31" s="27">
+        <v>41.4</v>
+      </c>
+      <c r="AC31" s="27">
+        <v>29.94</v>
+      </c>
+      <c r="AD31" s="27">
+        <v>3629</v>
+      </c>
+      <c r="AE31" s="28">
+        <v>2975</v>
+      </c>
+      <c r="AF31" s="27">
+        <v>6.67</v>
+      </c>
+      <c r="AG31" s="29">
+        <v>22.28</v>
+      </c>
+      <c r="AH31" s="29">
+        <v>41.23</v>
+      </c>
+      <c r="AI31" s="29">
+        <v>29.82</v>
+      </c>
+      <c r="AJ31" s="29">
+        <v>3614</v>
+      </c>
+      <c r="AK31" s="20">
+        <v>2975</v>
       </c>
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" s="24">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B32" s="20">
         <v>16518</v>
@@ -17706,49 +17671,49 @@
       <c r="X32" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y32" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD32" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE32" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF32" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG32" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH32" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI32" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ32" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK32" s="20" t="s">
-        <v>1</v>
+      <c r="Y32" s="27">
+        <v>24.7</v>
+      </c>
+      <c r="Z32" s="27">
+        <v>6.29</v>
+      </c>
+      <c r="AA32" s="27">
+        <v>22.39</v>
+      </c>
+      <c r="AB32" s="27">
+        <v>41.4</v>
+      </c>
+      <c r="AC32" s="27">
+        <v>29.92</v>
+      </c>
+      <c r="AD32" s="27">
+        <v>3677</v>
+      </c>
+      <c r="AE32" s="28">
+        <v>2955</v>
+      </c>
+      <c r="AF32" s="27">
+        <v>6.76</v>
+      </c>
+      <c r="AG32" s="29">
+        <v>22.28</v>
+      </c>
+      <c r="AH32" s="29">
+        <v>41.19</v>
+      </c>
+      <c r="AI32" s="29">
+        <v>29.77</v>
+      </c>
+      <c r="AJ32" s="29">
+        <v>3659</v>
+      </c>
+      <c r="AK32" s="20">
+        <v>2955</v>
       </c>
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" s="24">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B33" s="20">
         <v>16519</v>
@@ -17819,49 +17784,49 @@
       <c r="X33" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y33" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB33" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD33" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE33" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH33" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI33" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ33" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK33" s="20" t="s">
-        <v>1</v>
+      <c r="Y33" s="27">
+        <v>25.26</v>
+      </c>
+      <c r="Z33" s="27">
+        <v>6.22</v>
+      </c>
+      <c r="AA33" s="27">
+        <v>23.29</v>
+      </c>
+      <c r="AB33" s="27">
+        <v>38.08</v>
+      </c>
+      <c r="AC33" s="27">
+        <v>32.409999999999997</v>
+      </c>
+      <c r="AD33" s="27">
+        <v>3922</v>
+      </c>
+      <c r="AE33" s="28">
+        <v>3126</v>
+      </c>
+      <c r="AF33" s="27">
+        <v>6.6</v>
+      </c>
+      <c r="AG33" s="29">
+        <v>23.2</v>
+      </c>
+      <c r="AH33" s="29">
+        <v>37.93</v>
+      </c>
+      <c r="AI33" s="29">
+        <v>32.28</v>
+      </c>
+      <c r="AJ33" s="29">
+        <v>3906</v>
+      </c>
+      <c r="AK33" s="20">
+        <v>3126</v>
       </c>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" s="24">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B34" s="20">
         <v>16520</v>
@@ -17932,49 +17897,49 @@
       <c r="X34" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y34" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD34" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE34" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH34" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI34" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ34" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK34" s="20" t="s">
-        <v>1</v>
+      <c r="Y34" s="27">
+        <v>24.58</v>
+      </c>
+      <c r="Z34" s="27">
+        <v>6.11</v>
+      </c>
+      <c r="AA34" s="27">
+        <v>24.09</v>
+      </c>
+      <c r="AB34" s="27">
+        <v>36.909999999999997</v>
+      </c>
+      <c r="AC34" s="27">
+        <v>32.89</v>
+      </c>
+      <c r="AD34" s="27">
+        <v>4166</v>
+      </c>
+      <c r="AE34" s="28">
+        <v>3346</v>
+      </c>
+      <c r="AF34" s="27">
+        <v>6.4</v>
+      </c>
+      <c r="AG34" s="29">
+        <v>24.02</v>
+      </c>
+      <c r="AH34" s="29">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="AI34" s="29">
+        <v>32.79</v>
+      </c>
+      <c r="AJ34" s="29">
+        <v>4153</v>
+      </c>
+      <c r="AK34" s="20">
+        <v>3346</v>
       </c>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" s="24">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B35" s="20">
         <v>16521</v>
@@ -18045,49 +18010,49 @@
       <c r="X35" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y35" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA35" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC35" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD35" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE35" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF35" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG35" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH35" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI35" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ35" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK35" s="20" t="s">
-        <v>1</v>
+      <c r="Y35" s="27">
+        <v>24.36</v>
+      </c>
+      <c r="Z35" s="27">
+        <v>6.41</v>
+      </c>
+      <c r="AA35" s="27">
+        <v>25.02</v>
+      </c>
+      <c r="AB35" s="27">
+        <v>36.11</v>
+      </c>
+      <c r="AC35" s="27">
+        <v>32.46</v>
+      </c>
+      <c r="AD35" s="27">
+        <v>4041</v>
+      </c>
+      <c r="AE35" s="28">
+        <v>3266</v>
+      </c>
+      <c r="AF35" s="27">
+        <v>6.72</v>
+      </c>
+      <c r="AG35" s="29">
+        <v>24.94</v>
+      </c>
+      <c r="AH35" s="29">
+        <v>35.99</v>
+      </c>
+      <c r="AI35" s="29">
+        <v>32.35</v>
+      </c>
+      <c r="AJ35" s="29">
+        <v>4028</v>
+      </c>
+      <c r="AK35" s="20">
+        <v>3266</v>
       </c>
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" s="24">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B36" s="20">
         <v>16522</v>
@@ -18158,49 +18123,49 @@
       <c r="X36" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y36" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA36" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC36" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD36" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE36" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF36" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG36" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI36" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ36" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK36" s="20" t="s">
-        <v>1</v>
+      <c r="Y36" s="27">
+        <v>23.01</v>
+      </c>
+      <c r="Z36" s="27">
+        <v>5.81</v>
+      </c>
+      <c r="AA36" s="27">
+        <v>23.2</v>
+      </c>
+      <c r="AB36" s="27">
+        <v>41.55</v>
+      </c>
+      <c r="AC36" s="27">
+        <v>29.44</v>
+      </c>
+      <c r="AD36" s="27">
+        <v>3768</v>
+      </c>
+      <c r="AE36" s="28">
+        <v>3080</v>
+      </c>
+      <c r="AF36" s="27">
+        <v>6.25</v>
+      </c>
+      <c r="AG36" s="29">
+        <v>23.09</v>
+      </c>
+      <c r="AH36" s="29">
+        <v>41.36</v>
+      </c>
+      <c r="AI36" s="29">
+        <v>29.3</v>
+      </c>
+      <c r="AJ36" s="29">
+        <v>3750</v>
+      </c>
+      <c r="AK36" s="20">
+        <v>3080</v>
       </c>
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A37" s="24">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B37" s="20">
         <v>16523</v>
@@ -18271,49 +18236,49 @@
       <c r="X37" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y37" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA37" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD37" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE37" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF37" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG37" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH37" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI37" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ37" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK37" s="20" t="s">
-        <v>1</v>
+      <c r="Y37" s="27">
+        <v>23.85</v>
+      </c>
+      <c r="Z37" s="27">
+        <v>6.34</v>
+      </c>
+      <c r="AA37" s="27">
+        <v>23.41</v>
+      </c>
+      <c r="AB37" s="27">
+        <v>32.74</v>
+      </c>
+      <c r="AC37" s="27">
+        <v>37.51</v>
+      </c>
+      <c r="AD37" s="27">
+        <v>4478</v>
+      </c>
+      <c r="AE37" s="28">
+        <v>3641</v>
+      </c>
+      <c r="AF37" s="27">
+        <v>7.82</v>
+      </c>
+      <c r="AG37" s="29">
+        <v>23.04</v>
+      </c>
+      <c r="AH37" s="29">
+        <v>32.22</v>
+      </c>
+      <c r="AI37" s="29">
+        <v>36.92</v>
+      </c>
+      <c r="AJ37" s="29">
+        <v>4407</v>
+      </c>
+      <c r="AK37" s="20">
+        <v>3641</v>
       </c>
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A38" s="24">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B38" s="20">
         <v>16524</v>
@@ -18384,49 +18349,49 @@
       <c r="X38" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y38" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD38" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE38" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF38" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH38" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI38" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ38" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK38" s="20" t="s">
-        <v>1</v>
+      <c r="Y38" s="27">
+        <v>23.89</v>
+      </c>
+      <c r="Z38" s="27">
+        <v>7.26</v>
+      </c>
+      <c r="AA38" s="27">
+        <v>26.47</v>
+      </c>
+      <c r="AB38" s="27">
+        <v>31.39</v>
+      </c>
+      <c r="AC38" s="27">
+        <v>34.880000000000003</v>
+      </c>
+      <c r="AD38" s="27">
+        <v>4513</v>
+      </c>
+      <c r="AE38" s="28">
+        <v>3704</v>
+      </c>
+      <c r="AF38" s="27">
+        <v>7.75</v>
+      </c>
+      <c r="AG38" s="29">
+        <v>26.33</v>
+      </c>
+      <c r="AH38" s="29">
+        <v>31.22</v>
+      </c>
+      <c r="AI38" s="29">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="AJ38" s="29">
+        <v>4489</v>
+      </c>
+      <c r="AK38" s="20">
+        <v>3704</v>
       </c>
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A39" s="24">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B39" s="20">
         <v>16525</v>
@@ -18497,49 +18462,49 @@
       <c r="X39" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y39" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA39" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB39" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD39" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE39" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF39" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG39" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH39" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI39" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ39" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK39" s="20" t="s">
-        <v>1</v>
+      <c r="Y39" s="27">
+        <v>22.25</v>
+      </c>
+      <c r="Z39" s="27">
+        <v>6.96</v>
+      </c>
+      <c r="AA39" s="27">
+        <v>23.87</v>
+      </c>
+      <c r="AB39" s="27">
+        <v>35.97</v>
+      </c>
+      <c r="AC39" s="27">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="AD39" s="27">
+        <v>4102</v>
+      </c>
+      <c r="AE39" s="28">
+        <v>3428</v>
+      </c>
+      <c r="AF39" s="27">
+        <v>7.2</v>
+      </c>
+      <c r="AG39" s="29">
+        <v>23.81</v>
+      </c>
+      <c r="AH39" s="29">
+        <v>35.880000000000003</v>
+      </c>
+      <c r="AI39" s="29">
+        <v>33.11</v>
+      </c>
+      <c r="AJ39" s="29">
+        <v>4091</v>
+      </c>
+      <c r="AK39" s="20">
+        <v>3428</v>
       </c>
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A40" s="24">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B40" s="20">
         <v>16526</v>
@@ -18610,49 +18575,49 @@
       <c r="X40" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y40" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD40" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE40" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF40" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG40" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH40" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI40" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ40" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK40" s="20" t="s">
-        <v>1</v>
+      <c r="Y40" s="27">
+        <v>20.81</v>
+      </c>
+      <c r="Z40" s="27">
+        <v>6.49</v>
+      </c>
+      <c r="AA40" s="27">
+        <v>24.65</v>
+      </c>
+      <c r="AB40" s="27">
+        <v>37.78</v>
+      </c>
+      <c r="AC40" s="27">
+        <v>31.08</v>
+      </c>
+      <c r="AD40" s="27">
+        <v>3963</v>
+      </c>
+      <c r="AE40" s="28">
+        <v>3356</v>
+      </c>
+      <c r="AF40" s="27">
+        <v>6.88</v>
+      </c>
+      <c r="AG40" s="29">
+        <v>24.55</v>
+      </c>
+      <c r="AH40" s="29">
+        <v>37.619999999999997</v>
+      </c>
+      <c r="AI40" s="29">
+        <v>30.95</v>
+      </c>
+      <c r="AJ40" s="29">
+        <v>3946</v>
+      </c>
+      <c r="AK40" s="20">
+        <v>3356</v>
       </c>
     </row>
     <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A41" s="24">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B41" s="20">
         <v>16527</v>
@@ -18723,49 +18688,49 @@
       <c r="X41" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y41" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA41" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC41" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD41" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE41" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF41" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG41" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH41" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI41" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ41" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK41" s="20" t="s">
-        <v>1</v>
+      <c r="Y41" s="27">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="Z41" s="27">
+        <v>6.13</v>
+      </c>
+      <c r="AA41" s="27">
+        <v>23.29</v>
+      </c>
+      <c r="AB41" s="27">
+        <v>38.76</v>
+      </c>
+      <c r="AC41" s="27">
+        <v>31.82</v>
+      </c>
+      <c r="AD41" s="27">
+        <v>3934</v>
+      </c>
+      <c r="AE41" s="28">
+        <v>3353</v>
+      </c>
+      <c r="AF41" s="27">
+        <v>6.61</v>
+      </c>
+      <c r="AG41" s="29">
+        <v>23.17</v>
+      </c>
+      <c r="AH41" s="29">
+        <v>38.56</v>
+      </c>
+      <c r="AI41" s="29">
+        <v>31.66</v>
+      </c>
+      <c r="AJ41" s="29">
+        <v>3914</v>
+      </c>
+      <c r="AK41" s="20">
+        <v>3353</v>
       </c>
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A42" s="24">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B42" s="20">
         <v>16528</v>
@@ -18836,49 +18801,49 @@
       <c r="X42" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y42" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z42" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB42" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD42" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE42" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF42" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG42" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH42" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI42" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ42" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK42" s="20" t="s">
-        <v>1</v>
+      <c r="Y42" s="27">
+        <v>22.61</v>
+      </c>
+      <c r="Z42" s="27">
+        <v>6.2</v>
+      </c>
+      <c r="AA42" s="27">
+        <v>27.17</v>
+      </c>
+      <c r="AB42" s="27">
+        <v>30.96</v>
+      </c>
+      <c r="AC42" s="27">
+        <v>35.67</v>
+      </c>
+      <c r="AD42" s="27">
+        <v>4622</v>
+      </c>
+      <c r="AE42" s="28">
+        <v>3813</v>
+      </c>
+      <c r="AF42" s="27">
+        <v>7.53</v>
+      </c>
+      <c r="AG42" s="29">
+        <v>26.78</v>
+      </c>
+      <c r="AH42" s="29">
+        <v>30.52</v>
+      </c>
+      <c r="AI42" s="29">
+        <v>35.159999999999997</v>
+      </c>
+      <c r="AJ42" s="29">
+        <v>4556</v>
+      </c>
+      <c r="AK42" s="20">
+        <v>3813</v>
       </c>
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A43" s="24">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B43" s="20">
         <v>16529</v>
@@ -18949,49 +18914,49 @@
       <c r="X43" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y43" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA43" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB43" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC43" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD43" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE43" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF43" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG43" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH43" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI43" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ43" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK43" s="20" t="s">
-        <v>1</v>
+      <c r="Y43" s="27">
+        <v>21.03</v>
+      </c>
+      <c r="Z43" s="27">
+        <v>6.78</v>
+      </c>
+      <c r="AA43" s="27">
+        <v>24.65</v>
+      </c>
+      <c r="AB43" s="27">
+        <v>37</v>
+      </c>
+      <c r="AC43" s="27">
+        <v>31.57</v>
+      </c>
+      <c r="AD43" s="27">
+        <v>3930</v>
+      </c>
+      <c r="AE43" s="28">
+        <v>3329</v>
+      </c>
+      <c r="AF43" s="27">
+        <v>7.13</v>
+      </c>
+      <c r="AG43" s="29">
+        <v>24.56</v>
+      </c>
+      <c r="AH43" s="29">
+        <v>36.86</v>
+      </c>
+      <c r="AI43" s="29">
+        <v>31.45</v>
+      </c>
+      <c r="AJ43" s="29">
+        <v>3915</v>
+      </c>
+      <c r="AK43" s="20">
+        <v>3329</v>
       </c>
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A44" s="24">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B44" s="20">
         <v>16530</v>
@@ -19062,49 +19027,49 @@
       <c r="X44" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y44" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA44" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB44" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC44" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD44" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE44" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF44" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG44" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH44" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI44" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ44" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK44" s="20" t="s">
-        <v>1</v>
+      <c r="Y44" s="27">
+        <v>19.22</v>
+      </c>
+      <c r="Z44" s="27">
+        <v>5.62</v>
+      </c>
+      <c r="AA44" s="27">
+        <v>22.48</v>
+      </c>
+      <c r="AB44" s="27">
+        <v>43.49</v>
+      </c>
+      <c r="AC44" s="27">
+        <v>28.41</v>
+      </c>
+      <c r="AD44" s="27">
+        <v>3590</v>
+      </c>
+      <c r="AE44" s="28">
+        <v>3073</v>
+      </c>
+      <c r="AF44" s="27">
+        <v>6.12</v>
+      </c>
+      <c r="AG44" s="29">
+        <v>22.36</v>
+      </c>
+      <c r="AH44" s="29">
+        <v>43.26</v>
+      </c>
+      <c r="AI44" s="29">
+        <v>28.26</v>
+      </c>
+      <c r="AJ44" s="29">
+        <v>3571</v>
+      </c>
+      <c r="AK44" s="20">
+        <v>3073</v>
       </c>
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A45" s="24">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B45" s="20">
         <v>16532</v>
@@ -19175,49 +19140,49 @@
       <c r="X45" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y45" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA45" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB45" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC45" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD45" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE45" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF45" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG45" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH45" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI45" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ45" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK45" s="20" t="s">
-        <v>1</v>
+      <c r="Y45" s="27">
+        <v>18.809999999999999</v>
+      </c>
+      <c r="Z45" s="27">
+        <v>5.31</v>
+      </c>
+      <c r="AA45" s="27">
+        <v>20.83</v>
+      </c>
+      <c r="AB45" s="27">
+        <v>48.37</v>
+      </c>
+      <c r="AC45" s="27">
+        <v>25.49</v>
+      </c>
+      <c r="AD45" s="27">
+        <v>3152</v>
+      </c>
+      <c r="AE45" s="28">
+        <v>2703</v>
+      </c>
+      <c r="AF45" s="27">
+        <v>5.66</v>
+      </c>
+      <c r="AG45" s="29">
+        <v>20.75</v>
+      </c>
+      <c r="AH45" s="29">
+        <v>48.19</v>
+      </c>
+      <c r="AI45" s="29">
+        <v>25.4</v>
+      </c>
+      <c r="AJ45" s="29">
+        <v>3140</v>
+      </c>
+      <c r="AK45" s="20">
+        <v>2703</v>
       </c>
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A46" s="24">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B46" s="20">
         <v>16533</v>
@@ -19288,49 +19253,49 @@
       <c r="X46" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y46" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z46" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA46" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB46" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC46" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD46" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE46" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF46" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG46" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH46" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI46" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ46" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK46" s="20" t="s">
-        <v>1</v>
+      <c r="Y46" s="27">
+        <v>19.420000000000002</v>
+      </c>
+      <c r="Z46" s="27">
+        <v>6.02</v>
+      </c>
+      <c r="AA46" s="27">
+        <v>23.12</v>
+      </c>
+      <c r="AB46" s="27">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="AC46" s="27">
+        <v>31.56</v>
+      </c>
+      <c r="AD46" s="27">
+        <v>3807</v>
+      </c>
+      <c r="AE46" s="28">
+        <v>3264</v>
+      </c>
+      <c r="AF46" s="27">
+        <v>6.46</v>
+      </c>
+      <c r="AG46" s="29">
+        <v>23.01</v>
+      </c>
+      <c r="AH46" s="29">
+        <v>39.119999999999997</v>
+      </c>
+      <c r="AI46" s="29">
+        <v>31.41</v>
+      </c>
+      <c r="AJ46" s="29">
+        <v>3789</v>
+      </c>
+      <c r="AK46" s="20">
+        <v>3264</v>
       </c>
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A47" s="24">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B47" s="20">
         <v>16534</v>
@@ -19401,49 +19366,49 @@
       <c r="X47" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y47" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z47" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA47" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB47" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC47" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD47" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE47" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF47" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG47" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH47" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI47" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ47" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK47" s="20" t="s">
-        <v>1</v>
+      <c r="Y47" s="27">
+        <v>18.579999999999998</v>
+      </c>
+      <c r="Z47" s="27">
+        <v>6.35</v>
+      </c>
+      <c r="AA47" s="27">
+        <v>22.13</v>
+      </c>
+      <c r="AB47" s="27">
+        <v>45.14</v>
+      </c>
+      <c r="AC47" s="27">
+        <v>26.38</v>
+      </c>
+      <c r="AD47" s="27">
+        <v>3393</v>
+      </c>
+      <c r="AE47" s="28">
+        <v>2950</v>
+      </c>
+      <c r="AF47" s="27">
+        <v>6.73</v>
+      </c>
+      <c r="AG47" s="29">
+        <v>22.04</v>
+      </c>
+      <c r="AH47" s="29">
+        <v>44.96</v>
+      </c>
+      <c r="AI47" s="29">
+        <v>26.27</v>
+      </c>
+      <c r="AJ47" s="29">
+        <v>3379</v>
+      </c>
+      <c r="AK47" s="20">
+        <v>2950</v>
       </c>
     </row>
     <row r="48" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A48" s="24">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B48" s="20">
         <v>16535</v>
@@ -19514,49 +19479,49 @@
       <c r="X48" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y48" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z48" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA48" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB48" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC48" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD48" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE48" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF48" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG48" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH48" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI48" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ48" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK48" s="20" t="s">
-        <v>1</v>
+      <c r="Y48" s="27">
+        <v>20.99</v>
+      </c>
+      <c r="Z48" s="27">
+        <v>5.76</v>
+      </c>
+      <c r="AA48" s="27">
+        <v>23.26</v>
+      </c>
+      <c r="AB48" s="27">
+        <v>40.1</v>
+      </c>
+      <c r="AC48" s="27">
+        <v>30.88</v>
+      </c>
+      <c r="AD48" s="27">
+        <v>3759</v>
+      </c>
+      <c r="AE48" s="28">
+        <v>3152</v>
+      </c>
+      <c r="AF48" s="27">
+        <v>6.83</v>
+      </c>
+      <c r="AG48" s="29">
+        <v>23</v>
+      </c>
+      <c r="AH48" s="29">
+        <v>39.64</v>
+      </c>
+      <c r="AI48" s="29">
+        <v>30.53</v>
+      </c>
+      <c r="AJ48" s="29">
+        <v>3716</v>
+      </c>
+      <c r="AK48" s="20">
+        <v>3152</v>
       </c>
     </row>
     <row r="49" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A49" s="24">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B49" s="20">
         <v>16537</v>
@@ -19627,49 +19592,49 @@
       <c r="X49" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y49" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA49" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB49" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC49" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD49" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE49" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF49" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG49" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH49" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI49" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ49" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK49" s="20" t="s">
-        <v>1</v>
+      <c r="Y49" s="27">
+        <v>19.62</v>
+      </c>
+      <c r="Z49" s="27">
+        <v>5.5</v>
+      </c>
+      <c r="AA49" s="27">
+        <v>21.79</v>
+      </c>
+      <c r="AB49" s="27">
+        <v>45.06</v>
+      </c>
+      <c r="AC49" s="27">
+        <v>27.65</v>
+      </c>
+      <c r="AD49" s="27">
+        <v>3461</v>
+      </c>
+      <c r="AE49" s="28">
+        <v>2944</v>
+      </c>
+      <c r="AF49" s="27">
+        <v>5.92</v>
+      </c>
+      <c r="AG49" s="29">
+        <v>21.69</v>
+      </c>
+      <c r="AH49" s="29">
+        <v>44.86</v>
+      </c>
+      <c r="AI49" s="29">
+        <v>27.53</v>
+      </c>
+      <c r="AJ49" s="29">
+        <v>3446</v>
+      </c>
+      <c r="AK49" s="20">
+        <v>2944</v>
       </c>
     </row>
     <row r="50" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A50" s="24">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B50" s="20">
         <v>16539</v>
@@ -19740,49 +19705,49 @@
       <c r="X50" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y50" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA50" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB50" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC50" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD50" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE50" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF50" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG50" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH50" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI50" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ50" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK50" s="20" t="s">
-        <v>1</v>
+      <c r="Y50" s="27">
+        <v>18.940000000000001</v>
+      </c>
+      <c r="Z50" s="27">
+        <v>6.43</v>
+      </c>
+      <c r="AA50" s="27">
+        <v>23.14</v>
+      </c>
+      <c r="AB50" s="27">
+        <v>39.880000000000003</v>
+      </c>
+      <c r="AC50" s="27">
+        <v>30.55</v>
+      </c>
+      <c r="AD50" s="27">
+        <v>3790</v>
+      </c>
+      <c r="AE50" s="28">
+        <v>3283</v>
+      </c>
+      <c r="AF50" s="27">
+        <v>6.92</v>
+      </c>
+      <c r="AG50" s="29">
+        <v>23.02</v>
+      </c>
+      <c r="AH50" s="29">
+        <v>39.67</v>
+      </c>
+      <c r="AI50" s="29">
+        <v>30.39</v>
+      </c>
+      <c r="AJ50" s="29">
+        <v>3770</v>
+      </c>
+      <c r="AK50" s="20">
+        <v>3283</v>
       </c>
     </row>
     <row r="51" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A51" s="24">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B51" s="20">
         <v>16540</v>
@@ -19853,49 +19818,49 @@
       <c r="X51" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y51" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA51" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB51" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC51" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD51" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF51" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG51" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH51" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI51" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ51" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK51" s="20" t="s">
-        <v>1</v>
+      <c r="Y51" s="27">
+        <v>21.27</v>
+      </c>
+      <c r="Z51" s="27">
+        <v>6.07</v>
+      </c>
+      <c r="AA51" s="27">
+        <v>24.33</v>
+      </c>
+      <c r="AB51" s="27">
+        <v>41.65</v>
+      </c>
+      <c r="AC51" s="27">
+        <v>27.95</v>
+      </c>
+      <c r="AD51" s="27">
+        <v>3854</v>
+      </c>
+      <c r="AE51" s="28">
+        <v>3230</v>
+      </c>
+      <c r="AF51" s="27">
+        <v>6.49</v>
+      </c>
+      <c r="AG51" s="29">
+        <v>24.22</v>
+      </c>
+      <c r="AH51" s="29">
+        <v>41.46</v>
+      </c>
+      <c r="AI51" s="29">
+        <v>27.83</v>
+      </c>
+      <c r="AJ51" s="29">
+        <v>3837</v>
+      </c>
+      <c r="AK51" s="20">
+        <v>3230</v>
       </c>
     </row>
     <row r="52" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A52" s="24">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B52" s="20">
         <v>16541</v>
@@ -19966,49 +19931,49 @@
       <c r="X52" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="Y52" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z52" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA52" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB52" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC52" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD52" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE52" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF52" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG52" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH52" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI52" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ52" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK52" s="20" t="s">
-        <v>1</v>
+      <c r="Y52" s="27">
+        <v>23.91</v>
+      </c>
+      <c r="Z52" s="27">
+        <v>6.05</v>
+      </c>
+      <c r="AA52" s="27">
+        <v>26.11</v>
+      </c>
+      <c r="AB52" s="27">
+        <v>34.270000000000003</v>
+      </c>
+      <c r="AC52" s="27">
+        <v>33.57</v>
+      </c>
+      <c r="AD52" s="27">
+        <v>4274</v>
+      </c>
+      <c r="AE52" s="28">
+        <v>3462</v>
+      </c>
+      <c r="AF52" s="27">
+        <v>7.37</v>
+      </c>
+      <c r="AG52" s="29">
+        <v>25.74</v>
+      </c>
+      <c r="AH52" s="29">
+        <v>33.79</v>
+      </c>
+      <c r="AI52" s="29">
+        <v>33.1</v>
+      </c>
+      <c r="AJ52" s="29">
+        <v>4214</v>
+      </c>
+      <c r="AK52" s="20">
+        <v>3462</v>
       </c>
     </row>
     <row r="53" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A53" s="24">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B53" s="20">
         <v>16543</v>
@@ -20121,7 +20086,7 @@
     </row>
     <row r="54" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A54" s="24">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B54" s="20">
         <v>16545</v>
@@ -20234,7 +20199,7 @@
     </row>
     <row r="55" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A55" s="24">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B55" s="20">
         <v>16547</v>
@@ -20347,7 +20312,7 @@
     </row>
     <row r="56" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A56" s="24">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="B56" s="20">
         <v>16548</v>
@@ -20460,7 +20425,7 @@
     </row>
     <row r="57" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A57" s="24">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B57" s="20">
         <v>16550</v>
@@ -20573,7 +20538,7 @@
     </row>
     <row r="58" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A58" s="24">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B58" s="20">
         <v>16551</v>
@@ -20686,7 +20651,7 @@
     </row>
     <row r="59" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A59" s="24">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B59" s="20">
         <v>16552</v>
@@ -20799,7 +20764,7 @@
     </row>
     <row r="60" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A60" s="24">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B60" s="20">
         <v>16554</v>
@@ -20840,32 +20805,32 @@
       <c r="N60" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O60" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P60" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q60" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R60" s="20" t="s">
-        <v>1</v>
+      <c r="O60" s="20">
+        <v>7.2</v>
+      </c>
+      <c r="P60" s="20">
+        <v>25.78</v>
+      </c>
+      <c r="Q60" s="20">
+        <v>38.58</v>
+      </c>
+      <c r="R60" s="20">
+        <v>3904</v>
       </c>
       <c r="S60" s="7">
         <v>20.399999999999999</v>
       </c>
       <c r="T60" s="7">
-        <v>22.12</v>
+        <v>22.11</v>
       </c>
       <c r="U60" s="7">
         <v>33.090000000000003</v>
       </c>
       <c r="V60" s="7">
-        <v>24.39</v>
+        <v>24.4</v>
       </c>
       <c r="W60" s="26">
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="X60" s="26" t="s">
         <v>1</v>
@@ -20912,7 +20877,7 @@
     </row>
     <row r="61" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A61" s="24">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B61" s="20">
         <v>16555</v>
@@ -20953,17 +20918,17 @@
       <c r="N61" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O61" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P61" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R61" s="20" t="s">
-        <v>1</v>
+      <c r="O61" s="20">
+        <v>6.82</v>
+      </c>
+      <c r="P61" s="20">
+        <v>25.36</v>
+      </c>
+      <c r="Q61" s="20">
+        <v>39.409999999999997</v>
+      </c>
+      <c r="R61" s="20">
+        <v>3858</v>
       </c>
       <c r="S61" s="7">
         <v>21.71</v>
@@ -20978,7 +20943,7 @@
         <v>23.87</v>
       </c>
       <c r="W61" s="26">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="X61" s="26" t="s">
         <v>1</v>
@@ -21025,7 +20990,7 @@
     </row>
     <row r="62" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A62" s="24">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="B62" s="20">
         <v>16556</v>
@@ -21066,17 +21031,17 @@
       <c r="N62" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O62" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P62" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q62" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R62" s="20" t="s">
-        <v>1</v>
+      <c r="O62" s="20">
+        <v>7.57</v>
+      </c>
+      <c r="P62" s="20">
+        <v>26.33</v>
+      </c>
+      <c r="Q62" s="20">
+        <v>36.24</v>
+      </c>
+      <c r="R62" s="20">
+        <v>4095</v>
       </c>
       <c r="S62" s="7">
         <v>20.67</v>
@@ -21085,7 +21050,7 @@
         <v>22.6</v>
       </c>
       <c r="U62" s="7">
-        <v>31.11</v>
+        <v>31.1</v>
       </c>
       <c r="V62" s="7">
         <v>25.63</v>
@@ -21138,7 +21103,7 @@
     </row>
     <row r="63" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A63" s="24">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="B63" s="20">
         <v>16557</v>
@@ -21179,17 +21144,17 @@
       <c r="N63" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O63" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P63" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R63" s="20" t="s">
-        <v>1</v>
+      <c r="O63" s="20">
+        <v>7.56</v>
+      </c>
+      <c r="P63" s="20">
+        <v>25.05</v>
+      </c>
+      <c r="Q63" s="20">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="R63" s="20">
+        <v>3910</v>
       </c>
       <c r="S63" s="7">
         <v>21.36</v>
@@ -21198,10 +21163,10 @@
         <v>21.31</v>
       </c>
       <c r="U63" s="7">
-        <v>33</v>
+        <v>33.01</v>
       </c>
       <c r="V63" s="7">
-        <v>24.33</v>
+        <v>24.32</v>
       </c>
       <c r="W63" s="26">
         <v>3326</v>
@@ -21251,7 +21216,7 @@
     </row>
     <row r="64" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A64" s="24">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B64" s="20">
         <v>16560</v>
@@ -21292,17 +21257,17 @@
       <c r="N64" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O64" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P64" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q64" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R64" s="20" t="s">
-        <v>1</v>
+      <c r="O64" s="20">
+        <v>7.11</v>
+      </c>
+      <c r="P64" s="20">
+        <v>25.68</v>
+      </c>
+      <c r="Q64" s="20">
+        <v>39.770000000000003</v>
+      </c>
+      <c r="R64" s="20">
+        <v>3761</v>
       </c>
       <c r="S64" s="7">
         <v>20.03</v>
@@ -21314,7 +21279,7 @@
         <v>34.24</v>
       </c>
       <c r="V64" s="7">
-        <v>23.63</v>
+        <v>23.62</v>
       </c>
       <c r="W64" s="26">
         <v>3238</v>
@@ -21364,7 +21329,7 @@
     </row>
     <row r="65" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A65" s="24">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B65" s="20">
         <v>16561</v>
@@ -21405,17 +21370,17 @@
       <c r="N65" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O65" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P65" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R65" s="20" t="s">
-        <v>1</v>
+      <c r="O65" s="20">
+        <v>8.27</v>
+      </c>
+      <c r="P65" s="20">
+        <v>27.94</v>
+      </c>
+      <c r="Q65" s="20">
+        <v>26.15</v>
+      </c>
+      <c r="R65" s="20">
+        <v>4867</v>
       </c>
       <c r="S65" s="7">
         <v>23.33</v>
@@ -21477,7 +21442,7 @@
     </row>
     <row r="66" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A66" s="24">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B66" s="20">
         <v>16563</v>
@@ -21518,17 +21483,17 @@
       <c r="N66" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O66" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P66" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q66" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R66" s="20" t="s">
-        <v>1</v>
+      <c r="O66" s="20">
+        <v>7.4</v>
+      </c>
+      <c r="P66" s="20">
+        <v>24.01</v>
+      </c>
+      <c r="Q66" s="20">
+        <v>37.729999999999997</v>
+      </c>
+      <c r="R66" s="20">
+        <v>3930</v>
       </c>
       <c r="S66" s="7">
         <v>23.06</v>
@@ -21590,7 +21555,7 @@
     </row>
     <row r="67" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A67" s="24">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="B67" s="20">
         <v>16564</v>
@@ -21631,29 +21596,29 @@
       <c r="N67" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O67" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P67" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R67" s="20" t="s">
-        <v>1</v>
+      <c r="O67" s="20">
+        <v>6.88</v>
+      </c>
+      <c r="P67" s="20">
+        <v>24.85</v>
+      </c>
+      <c r="Q67" s="20">
+        <v>43.05</v>
+      </c>
+      <c r="R67" s="20">
+        <v>3514</v>
       </c>
       <c r="S67" s="7">
         <v>22.48</v>
       </c>
       <c r="T67" s="7">
-        <v>20.68</v>
+        <v>20.69</v>
       </c>
       <c r="U67" s="7">
-        <v>35.83</v>
+        <v>35.840000000000003</v>
       </c>
       <c r="V67" s="7">
-        <v>21</v>
+        <v>20.99</v>
       </c>
       <c r="W67" s="26">
         <v>2925</v>
@@ -21703,7 +21668,7 @@
     </row>
     <row r="68" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A68" s="24">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B68" s="20">
         <v>16566</v>
@@ -21744,17 +21709,17 @@
       <c r="N68" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O68" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P68" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R68" s="20" t="s">
-        <v>1</v>
+      <c r="O68" s="20">
+        <v>7.15</v>
+      </c>
+      <c r="P68" s="20">
+        <v>24.59</v>
+      </c>
+      <c r="Q68" s="20">
+        <v>41.05</v>
+      </c>
+      <c r="R68" s="20">
+        <v>3666</v>
       </c>
       <c r="S68" s="7">
         <v>22.82</v>
@@ -21816,7 +21781,7 @@
     </row>
     <row r="69" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A69" s="24">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B69" s="20">
         <v>16568</v>
@@ -21857,17 +21822,17 @@
       <c r="N69" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O69" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P69" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q69" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R69" s="20" t="s">
-        <v>1</v>
+      <c r="O69" s="20">
+        <v>7.42</v>
+      </c>
+      <c r="P69" s="20">
+        <v>25.36</v>
+      </c>
+      <c r="Q69" s="20">
+        <v>35.43</v>
+      </c>
+      <c r="R69" s="20">
+        <v>4235</v>
       </c>
       <c r="S69" s="7">
         <v>23.8</v>
@@ -21882,7 +21847,7 @@
         <v>26.17</v>
       </c>
       <c r="W69" s="26">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="X69" s="26" t="s">
         <v>1</v>
@@ -21929,7 +21894,7 @@
     </row>
     <row r="70" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A70" s="24">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="B70" s="20">
         <v>16569</v>
@@ -21970,17 +21935,17 @@
       <c r="N70" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O70" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P70" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R70" s="20" t="s">
-        <v>1</v>
+      <c r="O70" s="20">
+        <v>7.58</v>
+      </c>
+      <c r="P70" s="20">
+        <v>25.78</v>
+      </c>
+      <c r="Q70" s="20">
+        <v>34.93</v>
+      </c>
+      <c r="R70" s="20">
+        <v>4277</v>
       </c>
       <c r="S70" s="7">
         <v>23.1</v>
@@ -22042,7 +22007,7 @@
     </row>
     <row r="71" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A71" s="24">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B71" s="20">
         <v>16570</v>
@@ -22083,17 +22048,17 @@
       <c r="N71" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O71" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P71" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q71" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R71" s="20" t="s">
-        <v>1</v>
+      <c r="O71" s="20">
+        <v>7.26</v>
+      </c>
+      <c r="P71" s="20">
+        <v>24.94</v>
+      </c>
+      <c r="Q71" s="20">
+        <v>38.229999999999997</v>
+      </c>
+      <c r="R71" s="20">
+        <v>4054</v>
       </c>
       <c r="S71" s="7">
         <v>23.75</v>
@@ -22155,7 +22120,7 @@
     </row>
     <row r="72" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A72" s="24">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="B72" s="20">
         <v>16572</v>
@@ -22196,17 +22161,17 @@
       <c r="N72" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O72" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P72" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q72" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R72" s="20" t="s">
-        <v>1</v>
+      <c r="O72" s="20">
+        <v>7.56</v>
+      </c>
+      <c r="P72" s="20">
+        <v>26.99</v>
+      </c>
+      <c r="Q72" s="20">
+        <v>33.78</v>
+      </c>
+      <c r="R72" s="20">
+        <v>4277</v>
       </c>
       <c r="S72" s="7">
         <v>22.5</v>
@@ -22268,7 +22233,7 @@
     </row>
     <row r="73" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A73" s="24">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B73" s="20">
         <v>16573</v>
@@ -22309,17 +22274,17 @@
       <c r="N73" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O73" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P73" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R73" s="20" t="s">
-        <v>1</v>
+      <c r="O73" s="20">
+        <v>7.27</v>
+      </c>
+      <c r="P73" s="20">
+        <v>25.38</v>
+      </c>
+      <c r="Q73" s="20">
+        <v>38.369999999999997</v>
+      </c>
+      <c r="R73" s="20">
+        <v>3908</v>
       </c>
       <c r="S73" s="7">
         <v>21.53</v>
@@ -22331,7 +22296,7 @@
         <v>32.47</v>
       </c>
       <c r="V73" s="7">
-        <v>24.53</v>
+        <v>24.52</v>
       </c>
       <c r="W73" s="26">
         <v>3307</v>
@@ -22381,7 +22346,7 @@
     </row>
     <row r="74" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A74" s="24">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="B74" s="20">
         <v>16576</v>
@@ -22422,29 +22387,29 @@
       <c r="N74" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O74" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P74" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q74" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R74" s="20" t="s">
-        <v>1</v>
+      <c r="O74" s="20">
+        <v>7.69</v>
+      </c>
+      <c r="P74" s="20">
+        <v>26.46</v>
+      </c>
+      <c r="Q74" s="20">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="R74" s="20">
+        <v>4079</v>
       </c>
       <c r="S74" s="7">
         <v>22.91</v>
       </c>
       <c r="T74" s="7">
-        <v>22.09</v>
+        <v>22.1</v>
       </c>
       <c r="U74" s="7">
         <v>30.2</v>
       </c>
       <c r="V74" s="7">
-        <v>24.8</v>
+        <v>24.79</v>
       </c>
       <c r="W74" s="26">
         <v>3406</v>
@@ -22494,7 +22459,7 @@
     </row>
     <row r="75" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A75" s="24">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="B75" s="20">
         <v>16577</v>
@@ -22535,17 +22500,17 @@
       <c r="N75" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O75" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P75" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q75" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R75" s="20" t="s">
-        <v>1</v>
+      <c r="O75" s="20">
+        <v>7.02</v>
+      </c>
+      <c r="P75" s="20">
+        <v>24.17</v>
+      </c>
+      <c r="Q75" s="20">
+        <v>42.97</v>
+      </c>
+      <c r="R75" s="20">
+        <v>3669</v>
       </c>
       <c r="S75" s="7">
         <v>24.49</v>
@@ -22560,7 +22525,7 @@
         <v>20.98</v>
       </c>
       <c r="W75" s="26">
-        <v>2979</v>
+        <v>2980</v>
       </c>
       <c r="X75" s="26" t="s">
         <v>1</v>
@@ -22607,7 +22572,7 @@
     </row>
     <row r="76" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A76" s="24">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="B76" s="20">
         <v>16578</v>
@@ -22648,17 +22613,17 @@
       <c r="N76" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O76" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P76" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q76" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R76" s="20" t="s">
-        <v>1</v>
+      <c r="O76" s="20">
+        <v>7.29</v>
+      </c>
+      <c r="P76" s="20">
+        <v>26.94</v>
+      </c>
+      <c r="Q76" s="20">
+        <v>36.409999999999997</v>
+      </c>
+      <c r="R76" s="20">
+        <v>4115</v>
       </c>
       <c r="S76" s="7">
         <v>24.64</v>
@@ -22720,7 +22685,7 @@
     </row>
     <row r="77" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A77" s="24">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="B77" s="20">
         <v>16580</v>
@@ -22756,22 +22721,22 @@
         <v>3795</v>
       </c>
       <c r="M77" s="20">
-        <v>3901</v>
+        <v>3915.16</v>
       </c>
       <c r="N77" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O77" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P77" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q77" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R77" s="20" t="s">
-        <v>1</v>
+      <c r="O77" s="20">
+        <v>7.87</v>
+      </c>
+      <c r="P77" s="20">
+        <v>26.5</v>
+      </c>
+      <c r="Q77" s="20">
+        <v>30.68</v>
+      </c>
+      <c r="R77" s="20">
+        <v>4602</v>
       </c>
       <c r="S77" s="7">
         <v>24.22</v>
@@ -22780,10 +22745,10 @@
         <v>21.8</v>
       </c>
       <c r="U77" s="7">
-        <v>25.23</v>
+        <v>25.24</v>
       </c>
       <c r="V77" s="7">
-        <v>28.75</v>
+        <v>28.74</v>
       </c>
       <c r="W77" s="26">
         <v>3785</v>
@@ -22833,7 +22798,7 @@
     </row>
     <row r="78" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A78" s="24">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="B78" s="20">
         <v>16581</v>
@@ -22874,17 +22839,17 @@
       <c r="N78" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O78" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P78" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q78" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R78" s="20" t="s">
-        <v>1</v>
+      <c r="O78" s="20">
+        <v>7.4</v>
+      </c>
+      <c r="P78" s="20">
+        <v>25.44</v>
+      </c>
+      <c r="Q78" s="20">
+        <v>38.21</v>
+      </c>
+      <c r="R78" s="20">
+        <v>3983</v>
       </c>
       <c r="S78" s="7">
         <v>24.29</v>
@@ -22899,7 +22864,7 @@
         <v>23.67</v>
       </c>
       <c r="W78" s="26">
-        <v>3256</v>
+        <v>3257</v>
       </c>
       <c r="X78" s="26" t="s">
         <v>1</v>
@@ -22946,7 +22911,7 @@
     </row>
     <row r="79" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A79" s="24">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B79" s="20">
         <v>16582</v>
@@ -22987,23 +22952,23 @@
       <c r="N79" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O79" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P79" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q79" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R79" s="20" t="s">
-        <v>1</v>
+      <c r="O79" s="20">
+        <v>7.63</v>
+      </c>
+      <c r="P79" s="20">
+        <v>25.89</v>
+      </c>
+      <c r="Q79" s="20">
+        <v>33.869999999999997</v>
+      </c>
+      <c r="R79" s="20">
+        <v>4349</v>
       </c>
       <c r="S79" s="7">
         <v>22.85</v>
       </c>
       <c r="T79" s="7">
-        <v>21.63</v>
+        <v>21.62</v>
       </c>
       <c r="U79" s="7">
         <v>28.29</v>
@@ -23059,7 +23024,7 @@
     </row>
     <row r="80" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A80" s="24">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="B80" s="20">
         <v>16583</v>
@@ -23100,17 +23065,17 @@
       <c r="N80" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="O80" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P80" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q80" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R80" s="20" t="s">
-        <v>1</v>
+      <c r="O80" s="20">
+        <v>7.28</v>
+      </c>
+      <c r="P80" s="20">
+        <v>25.93</v>
+      </c>
+      <c r="Q80" s="20">
+        <v>37.96</v>
+      </c>
+      <c r="R80" s="20">
+        <v>3974</v>
       </c>
       <c r="S80" s="7">
         <v>23.1</v>
@@ -23172,7 +23137,7 @@
     </row>
     <row r="81" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A81" s="24">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="B81" s="20">
         <v>16585</v>
@@ -23285,7 +23250,7 @@
     </row>
     <row r="82" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A82" s="24">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="B82" s="20">
         <v>16586</v>
@@ -23398,7 +23363,7 @@
     </row>
     <row r="83" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A83" s="24">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B83" s="20">
         <v>16589</v>
@@ -23511,7 +23476,7 @@
     </row>
     <row r="84" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A84" s="24">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="B84" s="20">
         <v>16592</v>
@@ -23564,20 +23529,20 @@
       <c r="R84" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="S84" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T84" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U84" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V84" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="W84" s="26" t="s">
-        <v>1</v>
+      <c r="S84" s="7">
+        <v>23.19</v>
+      </c>
+      <c r="T84" s="7">
+        <v>19.66</v>
+      </c>
+      <c r="U84" s="7">
+        <v>34.630000000000003</v>
+      </c>
+      <c r="V84" s="7">
+        <v>22.52</v>
+      </c>
+      <c r="W84" s="26">
+        <v>3100</v>
       </c>
       <c r="X84" s="26" t="s">
         <v>1</v>
@@ -23624,7 +23589,7 @@
     </row>
     <row r="85" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A85" s="24">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="B85" s="20">
         <v>16593</v>
@@ -23659,9 +23624,8 @@
       <c r="L85" s="20">
         <v>3701.6</v>
       </c>
-      <c r="M85" s="34">
-        <f>L85</f>
-        <v>3701.6</v>
+      <c r="M85" s="20">
+        <v>3674.2</v>
       </c>
       <c r="N85" s="20" t="s">
         <v>1</v>
@@ -23678,20 +23642,20 @@
       <c r="R85" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="S85" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T85" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U85" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V85" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="W85" s="26" t="s">
-        <v>1</v>
+      <c r="S85" s="7">
+        <v>23.93</v>
+      </c>
+      <c r="T85" s="7">
+        <v>18.77</v>
+      </c>
+      <c r="U85" s="7">
+        <v>37.049999999999997</v>
+      </c>
+      <c r="V85" s="7">
+        <v>20.25</v>
+      </c>
+      <c r="W85" s="26">
+        <v>2775</v>
       </c>
       <c r="X85" s="26" t="s">
         <v>1</v>
@@ -23738,7 +23702,7 @@
     </row>
     <row r="86" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A86" s="24">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="B86" s="20">
         <v>16594</v>
@@ -23791,20 +23755,20 @@
       <c r="R86" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="S86" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T86" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U86" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V86" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="W86" s="26" t="s">
-        <v>1</v>
+      <c r="S86" s="7">
+        <v>24.26</v>
+      </c>
+      <c r="T86" s="7">
+        <v>19.79</v>
+      </c>
+      <c r="U86" s="7">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="V86" s="7">
+        <v>21.15</v>
+      </c>
+      <c r="W86" s="26">
+        <v>2974</v>
       </c>
       <c r="X86" s="26" t="s">
         <v>1</v>
@@ -23846,6 +23810,1136 @@
         <v>1</v>
       </c>
       <c r="AK86" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A87" s="24">
+        <v>83</v>
+      </c>
+      <c r="B87" s="20">
+        <v>16599</v>
+      </c>
+      <c r="C87" s="25">
+        <v>46256</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G87" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H87" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I87" s="20">
+        <v>162011721</v>
+      </c>
+      <c r="J87" s="25">
+        <v>46254</v>
+      </c>
+      <c r="K87" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L87" s="20">
+        <v>3984.5</v>
+      </c>
+      <c r="M87" s="20">
+        <v>4055.6</v>
+      </c>
+      <c r="N87" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O87" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P87" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q87" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R87" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S87" s="7">
+        <v>22.64</v>
+      </c>
+      <c r="T87" s="7">
+        <v>17.940000000000001</v>
+      </c>
+      <c r="U87" s="7">
+        <v>40.03</v>
+      </c>
+      <c r="V87" s="7">
+        <v>19.39</v>
+      </c>
+      <c r="W87" s="26">
+        <v>2585</v>
+      </c>
+      <c r="X87" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y87" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z87" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA87" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB87" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC87" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD87" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE87" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF87" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG87" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH87" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI87" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ87" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK87" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A88" s="24">
+        <v>84</v>
+      </c>
+      <c r="B88" s="20">
+        <v>16604</v>
+      </c>
+      <c r="C88" s="25">
+        <v>46257</v>
+      </c>
+      <c r="D88" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H88" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I88" s="20">
+        <v>162001411</v>
+      </c>
+      <c r="J88" s="25">
+        <v>46255</v>
+      </c>
+      <c r="K88" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L88" s="20">
+        <v>3952.4</v>
+      </c>
+      <c r="M88" s="20">
+        <v>3979.6</v>
+      </c>
+      <c r="N88" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O88" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P88" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R88" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S88" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T88" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U88" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V88" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W88" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X88" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y88" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z88" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA88" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB88" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC88" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD88" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE88" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF88" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG88" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH88" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI88" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ88" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK88" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A89" s="24">
+        <v>85</v>
+      </c>
+      <c r="B89" s="20">
+        <v>16606</v>
+      </c>
+      <c r="C89" s="25">
+        <v>46257</v>
+      </c>
+      <c r="D89" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G89" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H89" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I89" s="20">
+        <v>162011724</v>
+      </c>
+      <c r="J89" s="25">
+        <v>46256</v>
+      </c>
+      <c r="K89" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L89" s="20">
+        <v>3787.7</v>
+      </c>
+      <c r="M89" s="20">
+        <v>3917.2</v>
+      </c>
+      <c r="N89" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O89" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P89" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q89" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R89" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S89" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T89" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U89" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V89" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W89" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X89" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y89" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA89" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB89" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC89" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD89" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE89" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF89" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG89" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH89" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI89" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ89" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK89" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A90" s="24">
+        <v>86</v>
+      </c>
+      <c r="B90" s="20">
+        <v>16609</v>
+      </c>
+      <c r="C90" s="25">
+        <v>46258</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E90" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G90" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H90" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I90" s="20">
+        <v>162006457</v>
+      </c>
+      <c r="J90" s="25">
+        <v>46256</v>
+      </c>
+      <c r="K90" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L90" s="20">
+        <v>4047.9</v>
+      </c>
+      <c r="M90" s="20">
+        <v>4050.4</v>
+      </c>
+      <c r="N90" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O90" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P90" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q90" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R90" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S90" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T90" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U90" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V90" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W90" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X90" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y90" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z90" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA90" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB90" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC90" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD90" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE90" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF90" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG90" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH90" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI90" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ90" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK90" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A91" s="24">
+        <v>87</v>
+      </c>
+      <c r="B91" s="20">
+        <v>16610</v>
+      </c>
+      <c r="C91" s="25">
+        <v>46258</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F91" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G91" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H91" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I91" s="20">
+        <v>162011726</v>
+      </c>
+      <c r="J91" s="25">
+        <v>46256</v>
+      </c>
+      <c r="K91" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L91" s="20">
+        <v>4042.2</v>
+      </c>
+      <c r="M91" s="20">
+        <v>4037.2</v>
+      </c>
+      <c r="N91" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O91" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P91" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R91" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S91" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T91" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U91" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V91" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W91" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X91" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y91" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z91" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA91" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB91" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC91" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD91" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE91" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF91" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG91" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH91" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI91" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ91" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK91" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A92" s="24">
+        <v>88</v>
+      </c>
+      <c r="B92" s="20">
+        <v>16612</v>
+      </c>
+      <c r="C92" s="25">
+        <v>46258</v>
+      </c>
+      <c r="D92" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G92" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H92" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I92" s="20">
+        <v>162003211</v>
+      </c>
+      <c r="J92" s="25">
+        <v>46256</v>
+      </c>
+      <c r="K92" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L92" s="20">
+        <v>4117.2</v>
+      </c>
+      <c r="M92" s="20">
+        <v>4023.4</v>
+      </c>
+      <c r="N92" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O92" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P92" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q92" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R92" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S92" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T92" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U92" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V92" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W92" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X92" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y92" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z92" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA92" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB92" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC92" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD92" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE92" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF92" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG92" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH92" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI92" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ92" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK92" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A93" s="24">
+        <v>89</v>
+      </c>
+      <c r="B93" s="20">
+        <v>16613</v>
+      </c>
+      <c r="C93" s="25">
+        <v>46258</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F93" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H93" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I93" s="20">
+        <v>162004413</v>
+      </c>
+      <c r="J93" s="25">
+        <v>46257</v>
+      </c>
+      <c r="K93" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L93" s="20">
+        <v>3754.9</v>
+      </c>
+      <c r="M93" s="20">
+        <v>3746.2</v>
+      </c>
+      <c r="N93" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O93" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P93" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R93" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S93" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T93" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U93" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V93" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W93" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X93" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y93" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z93" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA93" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB93" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC93" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD93" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE93" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF93" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG93" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH93" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI93" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ93" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK93" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A94" s="24">
+        <v>90</v>
+      </c>
+      <c r="B94" s="20">
+        <v>16615</v>
+      </c>
+      <c r="C94" s="25">
+        <v>46259</v>
+      </c>
+      <c r="D94" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H94" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I94" s="20">
+        <v>162004415</v>
+      </c>
+      <c r="J94" s="25">
+        <v>46258</v>
+      </c>
+      <c r="K94" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L94" s="20">
+        <v>4100.8</v>
+      </c>
+      <c r="M94" s="20">
+        <v>4060.8</v>
+      </c>
+      <c r="N94" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O94" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P94" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q94" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R94" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T94" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U94" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V94" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W94" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X94" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y94" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z94" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA94" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB94" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC94" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD94" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE94" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF94" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG94" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH94" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI94" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ94" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK94" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A95" s="24">
+        <v>91</v>
+      </c>
+      <c r="B95" s="20">
+        <v>16619</v>
+      </c>
+      <c r="C95" s="25">
+        <v>46259</v>
+      </c>
+      <c r="D95" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F95" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G95" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H95" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I95" s="20">
+        <v>162003213</v>
+      </c>
+      <c r="J95" s="25">
+        <v>46257</v>
+      </c>
+      <c r="K95" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L95" s="20">
+        <v>3556.2</v>
+      </c>
+      <c r="M95" s="20">
+        <v>3579.4</v>
+      </c>
+      <c r="N95" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O95" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P95" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R95" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S95" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T95" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U95" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V95" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W95" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X95" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y95" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z95" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA95" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB95" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC95" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD95" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE95" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF95" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG95" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH95" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI95" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ95" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK95" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A96" s="24">
+        <v>92</v>
+      </c>
+      <c r="B96" s="20">
+        <v>16620</v>
+      </c>
+      <c r="C96" s="25">
+        <v>46260</v>
+      </c>
+      <c r="D96" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G96" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H96" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I96" s="20">
+        <v>162006463</v>
+      </c>
+      <c r="J96" s="25">
+        <v>46258</v>
+      </c>
+      <c r="K96" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="L96" s="20">
+        <v>3891.9</v>
+      </c>
+      <c r="M96" s="20">
+        <v>0</v>
+      </c>
+      <c r="N96" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="O96" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P96" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q96" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R96" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S96" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T96" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U96" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V96" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W96" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="X96" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y96" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z96" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA96" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB96" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC96" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD96" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE96" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF96" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG96" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH96" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI96" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ96" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK96" s="20" t="s">
         <v>1</v>
       </c>
     </row>
